--- a/daily/2026-04-05.xlsx
+++ b/daily/2026-04-05.xlsx
@@ -558,7 +558,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Scottie Barnes</t>
+          <t>Jakob Poeltl</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -568,79 +568,79 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.5</v>
+        <v>9.5</v>
       </c>
       <c r="E2" t="n">
-        <v>9.699999999999999</v>
+        <v>13</v>
       </c>
       <c r="F2" t="n">
-        <v>15</v>
+        <v>13.6</v>
       </c>
       <c r="G2" t="n">
-        <v>15.4</v>
+        <v>13.9</v>
       </c>
       <c r="H2" t="n">
-        <v>15.5</v>
+        <v>11.8</v>
       </c>
       <c r="I2" t="n">
-        <v>15.9</v>
+        <v>10.3</v>
       </c>
       <c r="J2" t="n">
-        <v>29.8</v>
+        <v>26</v>
       </c>
       <c r="K2" t="n">
-        <v>32.4</v>
+        <v>25.4</v>
       </c>
       <c r="L2" t="n">
-        <v>56.7</v>
+        <v>63.4</v>
       </c>
       <c r="M2" t="n">
-        <v>51.3</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>6</v>
+        <v>6.9</v>
       </c>
       <c r="O2" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="P2" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.6</v>
+        <v>0.8</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.9</v>
+        <v>3.3</v>
       </c>
       <c r="S2" t="n">
-        <v>5.4</v>
+        <v>-5.5</v>
       </c>
       <c r="T2" t="n">
-        <v>-2.6</v>
+        <v>0.6</v>
       </c>
       <c r="U2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V2" t="n">
         <v>24</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>17.0 (5g)</t>
+          <t>17.0 (4g)</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>-5</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Derrick White</t>
+          <t>Ja'Kobe Walter</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -654,75 +654,75 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.5</v>
+        <v>9.5</v>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>10.4</v>
+        <v>9.4</v>
       </c>
       <c r="G3" t="n">
-        <v>12.8</v>
+        <v>11.8</v>
       </c>
       <c r="H3" t="n">
-        <v>16.1</v>
+        <v>9</v>
       </c>
       <c r="I3" t="n">
-        <v>15.8</v>
+        <v>8.5</v>
       </c>
       <c r="J3" t="n">
-        <v>33.6</v>
+        <v>26.2</v>
       </c>
       <c r="K3" t="n">
-        <v>34.3</v>
+        <v>22.7</v>
       </c>
       <c r="L3" t="n">
-        <v>41.2</v>
+        <v>54.8</v>
       </c>
       <c r="M3" t="n">
-        <v>40.6</v>
+        <v>41.6</v>
       </c>
       <c r="N3" t="n">
-        <v>4.6</v>
+        <v>6.1</v>
       </c>
       <c r="O3" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="P3" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3</v>
+        <v>-1</v>
       </c>
       <c r="R3" t="n">
-        <v>-5.4</v>
+        <v>0.9</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6</v>
+        <v>13.2</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7</v>
+        <v>3.5</v>
       </c>
       <c r="U3" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="V3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>17.4 (7g)</t>
+          <t>7.0 (5g)</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>-2.5</v>
+        <v>-9.300000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jakob Poeltl</t>
+          <t>Payton Pritchard</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -732,79 +732,79 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>9.5</v>
+        <v>15.5</v>
       </c>
       <c r="E4" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>22</v>
+      </c>
+      <c r="G4" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="J4" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="K4" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="L4" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="M4" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="N4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="O4" t="n">
+        <v>70</v>
+      </c>
+      <c r="P4" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="U4" t="n">
         <v>13</v>
       </c>
-      <c r="F4" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="G4" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="H4" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="I4" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="J4" t="n">
-        <v>26</v>
-      </c>
-      <c r="K4" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="L4" t="n">
-        <v>63.4</v>
-      </c>
-      <c r="M4" t="n">
-        <v>68.90000000000001</v>
-      </c>
-      <c r="N4" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="O4" t="n">
-        <v>80</v>
-      </c>
-      <c r="P4" t="n">
-        <v>47</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="R4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="S4" t="n">
-        <v>-5.5</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1</v>
-      </c>
       <c r="V4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>17.0 (4g)</t>
+          <t>20.0 (7g)</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>12.7</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ja'Kobe Walter</t>
+          <t>Jaylen Brown</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -818,75 +818,75 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>9.5</v>
+        <v>27.5</v>
       </c>
       <c r="E5" t="n">
-        <v>6</v>
+        <v>32.7</v>
       </c>
       <c r="F5" t="n">
-        <v>9.4</v>
+        <v>31.6</v>
       </c>
       <c r="G5" t="n">
-        <v>11.8</v>
+        <v>31.1</v>
       </c>
       <c r="H5" t="n">
-        <v>9</v>
+        <v>27.1</v>
       </c>
       <c r="I5" t="n">
-        <v>8.5</v>
+        <v>27.5</v>
       </c>
       <c r="J5" t="n">
-        <v>26.2</v>
+        <v>36.5</v>
       </c>
       <c r="K5" t="n">
-        <v>22.7</v>
+        <v>34.8</v>
       </c>
       <c r="L5" t="n">
-        <v>54.8</v>
+        <v>45.3</v>
       </c>
       <c r="M5" t="n">
-        <v>41.6</v>
+        <v>46.5</v>
       </c>
       <c r="N5" t="n">
-        <v>6.1</v>
+        <v>7.5</v>
       </c>
       <c r="O5" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="P5" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1</v>
+        <v>-0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9</v>
+        <v>4.1</v>
       </c>
       <c r="S5" t="n">
-        <v>13.2</v>
+        <v>-1.2</v>
       </c>
       <c r="T5" t="n">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="U5" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="V5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>7.0 (5g)</t>
+          <t>21.3 (6g)</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>-9.300000000000001</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Payton Pritchard</t>
+          <t>Neemias Queta</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -896,79 +896,79 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.5</v>
+        <v>9.5</v>
       </c>
       <c r="E6" t="n">
-        <v>15.3</v>
+        <v>17.3</v>
       </c>
       <c r="F6" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G6" t="n">
-        <v>19.1</v>
+        <v>12.3</v>
       </c>
       <c r="H6" t="n">
-        <v>15.2</v>
+        <v>11.2</v>
       </c>
       <c r="I6" t="n">
-        <v>17.2</v>
+        <v>9.9</v>
       </c>
       <c r="J6" t="n">
-        <v>31.5</v>
+        <v>28.5</v>
       </c>
       <c r="K6" t="n">
-        <v>31.9</v>
+        <v>26.1</v>
       </c>
       <c r="L6" t="n">
-        <v>48.5</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>43.6</v>
+        <v>61.8</v>
       </c>
       <c r="N6" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="O6" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="P6" t="n">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="R6" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="S6" t="n">
-        <v>4.9</v>
+        <v>9.1</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4</v>
+        <v>2.4</v>
       </c>
       <c r="U6" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="V6" t="n">
         <v>25</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>20.0 (7g)</t>
+          <t>9.0 (7g)</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>7.8</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Brandon Ingram</t>
+          <t>Jamal Shead</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -978,59 +978,59 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>20.5</v>
+        <v>7.5</v>
       </c>
       <c r="E7" t="n">
-        <v>17.3</v>
+        <v>11</v>
       </c>
       <c r="F7" t="n">
-        <v>15.2</v>
+        <v>9</v>
       </c>
       <c r="G7" t="n">
-        <v>20.5</v>
+        <v>6.6</v>
       </c>
       <c r="H7" t="n">
-        <v>19.8</v>
+        <v>6.2</v>
       </c>
       <c r="I7" t="n">
-        <v>20.8</v>
+        <v>5.9</v>
       </c>
       <c r="J7" t="n">
-        <v>33.1</v>
+        <v>25.8</v>
       </c>
       <c r="K7" t="n">
-        <v>33.7</v>
+        <v>22.8</v>
       </c>
       <c r="L7" t="n">
-        <v>51.3</v>
+        <v>34.3</v>
       </c>
       <c r="M7" t="n">
-        <v>47.9</v>
+        <v>33.8</v>
       </c>
       <c r="N7" t="n">
-        <v>8.9</v>
+        <v>5.3</v>
       </c>
       <c r="O7" t="n">
         <v>40</v>
       </c>
       <c r="P7" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3</v>
+        <v>-1.6</v>
       </c>
       <c r="R7" t="n">
-        <v>-5.6</v>
+        <v>3.1</v>
       </c>
       <c r="S7" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6</v>
+        <v>3.1</v>
       </c>
       <c r="U7" t="n">
         <v>2</v>
@@ -1038,15 +1038,19 @@
       <c r="V7" t="n">
         <v>24</v>
       </c>
-      <c r="W7" t="inlineStr"/>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>7.6 (7g)</t>
+        </is>
+      </c>
       <c r="X7" t="n">
-        <v>10</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RJ Barrett</t>
+          <t>Sam Hauser</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1060,75 +1064,75 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>20.5</v>
+        <v>7.5</v>
       </c>
       <c r="E8" t="n">
-        <v>23</v>
+        <v>14.3</v>
       </c>
       <c r="F8" t="n">
-        <v>22.2</v>
+        <v>12</v>
       </c>
       <c r="G8" t="n">
-        <v>20.4</v>
+        <v>7.9</v>
       </c>
       <c r="H8" t="n">
-        <v>21.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>18.9</v>
+        <v>9.1</v>
       </c>
       <c r="J8" t="n">
-        <v>29.5</v>
+        <v>25.1</v>
       </c>
       <c r="K8" t="n">
-        <v>29.9</v>
+        <v>26.7</v>
       </c>
       <c r="L8" t="n">
-        <v>51.9</v>
+        <v>43.7</v>
       </c>
       <c r="M8" t="n">
-        <v>49.3</v>
+        <v>39.8</v>
       </c>
       <c r="N8" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="O8" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="P8" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.6</v>
+        <v>1.6</v>
       </c>
       <c r="R8" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="S8" t="n">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4</v>
+        <v>-1.5</v>
       </c>
       <c r="U8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="V8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>22.0 (4g)</t>
+          <t>10.4 (7g)</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>-4.7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Jaylen Brown</t>
+          <t>Scottie Barnes</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1138,79 +1142,79 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>27.5</v>
+        <v>16.5</v>
       </c>
       <c r="E9" t="n">
-        <v>32.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>31.6</v>
+        <v>15</v>
       </c>
       <c r="G9" t="n">
-        <v>31.1</v>
+        <v>15.4</v>
       </c>
       <c r="H9" t="n">
-        <v>27.1</v>
+        <v>15.5</v>
       </c>
       <c r="I9" t="n">
-        <v>27.5</v>
+        <v>15.9</v>
       </c>
       <c r="J9" t="n">
-        <v>36.5</v>
+        <v>29.8</v>
       </c>
       <c r="K9" t="n">
-        <v>34.8</v>
+        <v>32.4</v>
       </c>
       <c r="L9" t="n">
-        <v>45.3</v>
+        <v>56.7</v>
       </c>
       <c r="M9" t="n">
-        <v>46.5</v>
+        <v>51.3</v>
       </c>
       <c r="N9" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="O9" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="P9" t="n">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0</v>
+        <v>-0.6</v>
       </c>
       <c r="R9" t="n">
-        <v>4.1</v>
+        <v>-0.9</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.2</v>
+        <v>5.4</v>
       </c>
       <c r="T9" t="n">
-        <v>1.8</v>
+        <v>-2.6</v>
       </c>
       <c r="U9" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="V9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>21.3 (6g)</t>
+          <t>17.0 (5g)</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>-0.4</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Neemias Queta</t>
+          <t>Derrick White</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1220,79 +1224,79 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>9.5</v>
+        <v>15.5</v>
       </c>
       <c r="E10" t="n">
-        <v>17.3</v>
+        <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>14</v>
+        <v>10.4</v>
       </c>
       <c r="G10" t="n">
-        <v>12.3</v>
+        <v>12.8</v>
       </c>
       <c r="H10" t="n">
-        <v>11.2</v>
+        <v>16.1</v>
       </c>
       <c r="I10" t="n">
-        <v>9.9</v>
+        <v>15.8</v>
       </c>
       <c r="J10" t="n">
-        <v>28.5</v>
+        <v>33.6</v>
       </c>
       <c r="K10" t="n">
-        <v>26.1</v>
+        <v>34.3</v>
       </c>
       <c r="L10" t="n">
-        <v>70.90000000000001</v>
+        <v>41.2</v>
       </c>
       <c r="M10" t="n">
-        <v>61.8</v>
+        <v>40.6</v>
       </c>
       <c r="N10" t="n">
-        <v>6.8</v>
+        <v>4.6</v>
       </c>
       <c r="O10" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="P10" t="n">
         <v>47</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="R10" t="n">
-        <v>4.1</v>
+        <v>-5.4</v>
       </c>
       <c r="S10" t="n">
-        <v>9.1</v>
+        <v>0.6</v>
       </c>
       <c r="T10" t="n">
-        <v>2.4</v>
+        <v>-0.7</v>
       </c>
       <c r="U10" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="V10" t="n">
         <v>25</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>9.0 (7g)</t>
+          <t>17.4 (7g)</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>7.1</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Jayson Tatum</t>
+          <t>Brandon Ingram</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1306,75 +1310,71 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>22.5</v>
+        <v>20.5</v>
       </c>
       <c r="E11" t="n">
-        <v>26.7</v>
+        <v>17.3</v>
       </c>
       <c r="F11" t="n">
-        <v>25</v>
+        <v>15.2</v>
       </c>
       <c r="G11" t="n">
-        <v>21.9</v>
+        <v>20.5</v>
       </c>
       <c r="H11" t="n">
-        <v>22.2</v>
+        <v>19.8</v>
       </c>
       <c r="I11" t="n">
-        <v>24.8</v>
+        <v>20.8</v>
       </c>
       <c r="J11" t="n">
-        <v>32.8</v>
+        <v>33.1</v>
       </c>
       <c r="K11" t="n">
-        <v>34.3</v>
+        <v>33.7</v>
       </c>
       <c r="L11" t="n">
-        <v>41.1</v>
+        <v>51.3</v>
       </c>
       <c r="M11" t="n">
-        <v>42.8</v>
+        <v>47.9</v>
       </c>
       <c r="N11" t="n">
-        <v>5.4</v>
+        <v>8.9</v>
       </c>
       <c r="O11" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="P11" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.3</v>
+        <v>0.3</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2</v>
+        <v>-5.6</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.7</v>
+        <v>3.4</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.5</v>
+        <v>-0.6</v>
       </c>
       <c r="U11" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="V11" t="n">
-        <v>25</v>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>20.5 (4g)</t>
-        </is>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="W11" t="inlineStr"/>
       <c r="X11" t="n">
-        <v>-2.7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Jamal Shead</t>
+          <t>RJ Barrett</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1384,59 +1384,59 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>7.5</v>
+        <v>19.5</v>
       </c>
       <c r="E12" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F12" t="n">
-        <v>9</v>
+        <v>22.2</v>
       </c>
       <c r="G12" t="n">
-        <v>6.6</v>
+        <v>20.4</v>
       </c>
       <c r="H12" t="n">
-        <v>6.2</v>
+        <v>21.2</v>
       </c>
       <c r="I12" t="n">
-        <v>5.9</v>
+        <v>18.9</v>
       </c>
       <c r="J12" t="n">
-        <v>25.8</v>
+        <v>29.5</v>
       </c>
       <c r="K12" t="n">
-        <v>22.8</v>
+        <v>29.9</v>
       </c>
       <c r="L12" t="n">
-        <v>34.3</v>
+        <v>51.9</v>
       </c>
       <c r="M12" t="n">
-        <v>33.8</v>
+        <v>49.3</v>
       </c>
       <c r="N12" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="O12" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="P12" t="n">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.6</v>
+        <v>-0.6</v>
       </c>
       <c r="R12" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="T12" t="n">
-        <v>3.1</v>
+        <v>-0.4</v>
       </c>
       <c r="U12" t="n">
         <v>2</v>
@@ -1446,17 +1446,17 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>7.6 (7g)</t>
+          <t>22.0 (4g)</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>-0.7</v>
+        <v>-4.7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sandro Mamukelashvili</t>
+          <t>Jayson Tatum</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1470,75 +1470,75 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>9.5</v>
+        <v>22.5</v>
       </c>
       <c r="E13" t="n">
-        <v>14.3</v>
+        <v>26.7</v>
       </c>
       <c r="F13" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G13" t="n">
-        <v>14.2</v>
+        <v>21.9</v>
       </c>
       <c r="H13" t="n">
-        <v>10.8</v>
+        <v>22.2</v>
       </c>
       <c r="I13" t="n">
-        <v>11.3</v>
+        <v>24.8</v>
       </c>
       <c r="J13" t="n">
-        <v>22</v>
+        <v>32.8</v>
       </c>
       <c r="K13" t="n">
-        <v>21.7</v>
+        <v>34.3</v>
       </c>
       <c r="L13" t="n">
-        <v>59.9</v>
+        <v>41.1</v>
       </c>
       <c r="M13" t="n">
-        <v>51</v>
+        <v>42.8</v>
       </c>
       <c r="N13" t="n">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="O13" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="P13" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="R13" t="n">
-        <v>4.7</v>
+        <v>0.2</v>
       </c>
       <c r="S13" t="n">
-        <v>8.9</v>
+        <v>-1.7</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3</v>
+        <v>-1.5</v>
       </c>
       <c r="U13" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="V13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>11.8 (5g)</t>
+          <t>20.5 (4g)</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>13</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sam Hauser</t>
+          <t>Sandro Mamukelashvili</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1552,69 +1552,69 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="E14" t="n">
         <v>14.3</v>
       </c>
       <c r="F14" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G14" t="n">
-        <v>7.9</v>
+        <v>14.2</v>
       </c>
       <c r="H14" t="n">
-        <v>8.699999999999999</v>
+        <v>10.8</v>
       </c>
       <c r="I14" t="n">
-        <v>9.1</v>
+        <v>11.3</v>
       </c>
       <c r="J14" t="n">
-        <v>25.1</v>
+        <v>22</v>
       </c>
       <c r="K14" t="n">
-        <v>26.7</v>
+        <v>21.7</v>
       </c>
       <c r="L14" t="n">
-        <v>43.7</v>
+        <v>59.9</v>
       </c>
       <c r="M14" t="n">
-        <v>39.8</v>
+        <v>51</v>
       </c>
       <c r="N14" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="O14" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="P14" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="R14" t="n">
-        <v>2.9</v>
+        <v>4.7</v>
       </c>
       <c r="S14" t="n">
-        <v>3.9</v>
+        <v>8.9</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.5</v>
+        <v>0.3</v>
       </c>
       <c r="U14" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="V14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>10.4 (7g)</t>
+          <t>11.8 (5g)</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>8.4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -2040,7 +2040,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="E20" t="n">
         <v>13.3</v>
@@ -2073,13 +2073,13 @@
         <v>5.5</v>
       </c>
       <c r="O20" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="P20" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.7</v>
+        <v>-2.7</v>
       </c>
       <c r="R20" t="n">
         <v>-1</v>
@@ -2186,7 +2186,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Alex Sarr</t>
+          <t>Will Riley</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2196,84 +2196,80 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="E22" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F22" t="n">
-        <v>8.800000000000001</v>
+        <v>21</v>
       </c>
       <c r="G22" t="n">
-        <v>11.4</v>
+        <v>18</v>
       </c>
       <c r="H22" t="n">
-        <v>15</v>
+        <v>16.4</v>
       </c>
       <c r="I22" t="n">
-        <v>14.7</v>
+        <v>15.6</v>
       </c>
       <c r="J22" t="n">
-        <v>21.8</v>
+        <v>31.6</v>
       </c>
       <c r="K22" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L22" t="n">
-        <v>38</v>
+        <v>50.8</v>
       </c>
       <c r="M22" t="n">
-        <v>44.9</v>
+        <v>49.1</v>
       </c>
       <c r="N22" t="n">
-        <v>7.3</v>
+        <v>6.3</v>
       </c>
       <c r="O22" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="P22" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.2</v>
+        <v>-0.9</v>
       </c>
       <c r="R22" t="n">
-        <v>-5.9</v>
+        <v>5.4</v>
       </c>
       <c r="S22" t="n">
-        <v>-6.9</v>
+        <v>1.7</v>
       </c>
       <c r="T22" t="n">
-        <v>-4.3</v>
+        <v>1.6</v>
       </c>
       <c r="U22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="V22" t="n">
         <v>30</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>13.3 (3g)</t>
-        </is>
-      </c>
+      <c r="W22" t="inlineStr"/>
       <c r="X22" t="n">
-        <v>-2.2</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Will Riley</t>
+          <t>Royce O'Neale</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>WAS @ BKN</t>
+          <t>PHX @ CHI</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2282,71 +2278,75 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>16.5</v>
+        <v>7.5</v>
       </c>
       <c r="E23" t="n">
-        <v>23</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>21</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>18</v>
+        <v>10.6</v>
       </c>
       <c r="H23" t="n">
-        <v>16.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>15.6</v>
+        <v>9.1</v>
       </c>
       <c r="J23" t="n">
-        <v>31.6</v>
+        <v>25.8</v>
       </c>
       <c r="K23" t="n">
-        <v>30</v>
+        <v>27.9</v>
       </c>
       <c r="L23" t="n">
-        <v>50.8</v>
+        <v>47.2</v>
       </c>
       <c r="M23" t="n">
-        <v>49.1</v>
+        <v>39.5</v>
       </c>
       <c r="N23" t="n">
-        <v>6.3</v>
+        <v>5.8</v>
       </c>
       <c r="O23" t="n">
         <v>60</v>
       </c>
       <c r="P23" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9</v>
+        <v>1.6</v>
       </c>
       <c r="R23" t="n">
-        <v>5.4</v>
+        <v>0.7</v>
       </c>
       <c r="S23" t="n">
-        <v>1.7</v>
+        <v>7.7</v>
       </c>
       <c r="T23" t="n">
-        <v>1.6</v>
+        <v>-2.2</v>
       </c>
       <c r="U23" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="V23" t="n">
-        <v>30</v>
-      </c>
-      <c r="W23" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>3.3 (3g)</t>
+        </is>
+      </c>
       <c r="X23" t="n">
-        <v>3.5</v>
+        <v>-33.1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Royce O'Neale</t>
+          <t>Mark Williams</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2356,73 +2356,73 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="E24" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>9.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="G24" t="n">
-        <v>10.6</v>
+        <v>8.4</v>
       </c>
       <c r="H24" t="n">
-        <v>8.800000000000001</v>
+        <v>10.3</v>
       </c>
       <c r="I24" t="n">
-        <v>9.1</v>
+        <v>10.2</v>
       </c>
       <c r="J24" t="n">
-        <v>25.8</v>
+        <v>21.1</v>
       </c>
       <c r="K24" t="n">
-        <v>27.9</v>
+        <v>23.1</v>
       </c>
       <c r="L24" t="n">
-        <v>47.2</v>
+        <v>53.1</v>
       </c>
       <c r="M24" t="n">
-        <v>39.5</v>
+        <v>59.5</v>
       </c>
       <c r="N24" t="n">
-        <v>5.8</v>
+        <v>3.7</v>
       </c>
       <c r="O24" t="n">
         <v>60</v>
       </c>
       <c r="P24" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="R24" t="n">
-        <v>0.7</v>
+        <v>-3.4</v>
       </c>
       <c r="S24" t="n">
-        <v>7.7</v>
+        <v>-6.4</v>
       </c>
       <c r="T24" t="n">
-        <v>-2.2</v>
+        <v>-2</v>
       </c>
       <c r="U24" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="V24" t="n">
         <v>1</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>3.3 (3g)</t>
+          <t>19.0 (4g)</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>-33.1</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="25">
@@ -3316,7 +3316,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="n">
         <v>9.300000000000001</v>
@@ -3349,13 +3349,13 @@
         <v>3.7</v>
       </c>
       <c r="O36" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="P36" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="Q36" t="n">
-        <v>-3.8</v>
+        <v>-4.8</v>
       </c>
       <c r="R36" t="n">
         <v>1.3</v>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="E51" t="n">
         <v>8</v>
@@ -4547,13 +4547,13 @@
         <v>3.5</v>
       </c>
       <c r="O51" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="P51" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R51" t="n">
         <v>-1.3</v>
@@ -5724,7 +5724,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>25.5</v>
+        <v>24.5</v>
       </c>
       <c r="E66" t="n">
         <v>14.7</v>
@@ -5760,10 +5760,10 @@
         <v>40</v>
       </c>
       <c r="P66" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="Q66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R66" t="n">
         <v>-4.1</v>
@@ -5802,7 +5802,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="E67" t="n">
         <v>16</v>
@@ -5838,10 +5838,10 @@
         <v>40</v>
       </c>
       <c r="P67" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="R67" t="n">
         <v>-4.9</v>
@@ -6810,7 +6810,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Kyle Filipowski</t>
+          <t>Alex Caruso</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6820,79 +6820,79 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>15.5</v>
+        <v>4.5</v>
       </c>
       <c r="E80" t="n">
-        <v>20.7</v>
+        <v>5</v>
       </c>
       <c r="F80" t="n">
-        <v>22.6</v>
+        <v>5.6</v>
       </c>
       <c r="G80" t="n">
-        <v>16.5</v>
+        <v>5.8</v>
       </c>
       <c r="H80" t="n">
-        <v>15.8</v>
+        <v>6.8</v>
       </c>
       <c r="I80" t="n">
-        <v>14.4</v>
+        <v>6.3</v>
       </c>
       <c r="J80" t="n">
-        <v>26</v>
+        <v>19.2</v>
       </c>
       <c r="K80" t="n">
-        <v>24.8</v>
+        <v>18.3</v>
       </c>
       <c r="L80" t="n">
-        <v>48.9</v>
+        <v>40.5</v>
       </c>
       <c r="M80" t="n">
-        <v>54.1</v>
+        <v>41.2</v>
       </c>
       <c r="N80" t="n">
-        <v>7.4</v>
+        <v>4.7</v>
       </c>
       <c r="O80" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="P80" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="Q80" t="n">
-        <v>-1.1</v>
+        <v>1.8</v>
       </c>
       <c r="R80" t="n">
-        <v>8.199999999999999</v>
+        <v>-0.7</v>
       </c>
       <c r="S80" t="n">
-        <v>-5.2</v>
+        <v>-0.7</v>
       </c>
       <c r="T80" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="U80" t="n">
+        <v>30</v>
+      </c>
+      <c r="V80" t="n">
         <v>8</v>
       </c>
-      <c r="V80" t="n">
-        <v>28</v>
-      </c>
       <c r="W80" t="inlineStr">
         <is>
-          <t>11.3 (6g)</t>
+          <t>8.7 (3g)</t>
         </is>
       </c>
       <c r="X80" t="n">
-        <v>0.3</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Alex Caruso</t>
+          <t>Jared McCain</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6906,55 +6906,55 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>5.5</v>
+        <v>8.5</v>
       </c>
       <c r="E81" t="n">
         <v>5</v>
       </c>
       <c r="F81" t="n">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
       <c r="G81" t="n">
-        <v>5.8</v>
+        <v>9.9</v>
       </c>
       <c r="H81" t="n">
-        <v>6.8</v>
+        <v>10.4</v>
       </c>
       <c r="I81" t="n">
-        <v>6.3</v>
+        <v>10.2</v>
       </c>
       <c r="J81" t="n">
-        <v>19.2</v>
+        <v>17.4</v>
       </c>
       <c r="K81" t="n">
-        <v>18.3</v>
+        <v>17.8</v>
       </c>
       <c r="L81" t="n">
-        <v>40.5</v>
+        <v>41.8</v>
       </c>
       <c r="M81" t="n">
-        <v>41.2</v>
+        <v>45.6</v>
       </c>
       <c r="N81" t="n">
-        <v>4.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O81" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="P81" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="R81" t="n">
-        <v>-0.7</v>
+        <v>-6</v>
       </c>
       <c r="S81" t="n">
-        <v>-0.7</v>
+        <v>-3.8</v>
       </c>
       <c r="T81" t="n">
-        <v>0.8</v>
+        <v>-0.4</v>
       </c>
       <c r="U81" t="n">
         <v>30</v>
@@ -6962,19 +6962,15 @@
       <c r="V81" t="n">
         <v>8</v>
       </c>
-      <c r="W81" t="inlineStr">
-        <is>
-          <t>8.7 (3g)</t>
-        </is>
-      </c>
+      <c r="W81" t="inlineStr"/>
       <c r="X81" t="n">
-        <v>23.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Ace Bailey</t>
+          <t>Cody Williams</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6988,55 +6984,55 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="E82" t="n">
-        <v>17.7</v>
+        <v>20.7</v>
       </c>
       <c r="F82" t="n">
-        <v>16.2</v>
+        <v>17.2</v>
       </c>
       <c r="G82" t="n">
-        <v>20.8</v>
+        <v>18.9</v>
       </c>
       <c r="H82" t="n">
-        <v>18.4</v>
+        <v>14</v>
       </c>
       <c r="I82" t="n">
-        <v>17.2</v>
+        <v>11.7</v>
       </c>
       <c r="J82" t="n">
-        <v>31.9</v>
+        <v>33.4</v>
       </c>
       <c r="K82" t="n">
-        <v>31.3</v>
+        <v>30</v>
       </c>
       <c r="L82" t="n">
-        <v>43.8</v>
+        <v>46.8</v>
       </c>
       <c r="M82" t="n">
-        <v>45.2</v>
+        <v>50.7</v>
       </c>
       <c r="N82" t="n">
-        <v>8.5</v>
+        <v>10.7</v>
       </c>
       <c r="O82" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="P82" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="Q82" t="n">
-        <v>-0.3</v>
+        <v>-3.8</v>
       </c>
       <c r="R82" t="n">
-        <v>-1</v>
+        <v>5.5</v>
       </c>
       <c r="S82" t="n">
-        <v>-1.4</v>
+        <v>-3.9</v>
       </c>
       <c r="T82" t="n">
-        <v>0.6</v>
+        <v>3.4</v>
       </c>
       <c r="U82" t="n">
         <v>8</v>
@@ -7046,17 +7042,17 @@
       </c>
       <c r="W82" t="inlineStr">
         <is>
-          <t>10.0 (3g)</t>
+          <t>3.0 (4g)</t>
         </is>
       </c>
       <c r="X82" t="n">
-        <v>5.4</v>
+        <v>-10.9</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Jared McCain</t>
+          <t>John Konchar</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7070,71 +7066,75 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="E83" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F83" t="n">
-        <v>4.2</v>
+        <v>8</v>
       </c>
       <c r="G83" t="n">
-        <v>9.9</v>
+        <v>8.1</v>
       </c>
       <c r="H83" t="n">
-        <v>10.4</v>
+        <v>5.7</v>
       </c>
       <c r="I83" t="n">
-        <v>10.2</v>
+        <v>4.8</v>
       </c>
       <c r="J83" t="n">
-        <v>17.4</v>
+        <v>27.4</v>
       </c>
       <c r="K83" t="n">
-        <v>17.8</v>
+        <v>23.4</v>
       </c>
       <c r="L83" t="n">
-        <v>41.8</v>
+        <v>50.9</v>
       </c>
       <c r="M83" t="n">
-        <v>45.6</v>
+        <v>39</v>
       </c>
       <c r="N83" t="n">
-        <v>8.199999999999999</v>
+        <v>5.9</v>
       </c>
       <c r="O83" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="P83" t="n">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="Q83" t="n">
-        <v>1.7</v>
+        <v>-1.7</v>
       </c>
       <c r="R83" t="n">
-        <v>-6</v>
+        <v>3.2</v>
       </c>
       <c r="S83" t="n">
-        <v>-3.8</v>
+        <v>11.9</v>
       </c>
       <c r="T83" t="n">
-        <v>-0.4</v>
+        <v>4</v>
       </c>
       <c r="U83" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="V83" t="n">
-        <v>8</v>
-      </c>
-      <c r="W83" t="inlineStr"/>
+        <v>28</v>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>1.8 (4g)</t>
+        </is>
+      </c>
       <c r="X83" t="n">
-        <v>0</v>
+        <v>-24.9</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Cody Williams</t>
+          <t>Jalen Williams</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7144,79 +7144,79 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="E84" t="n">
-        <v>20.7</v>
+        <v>16.7</v>
       </c>
       <c r="F84" t="n">
-        <v>17.2</v>
+        <v>15</v>
       </c>
       <c r="G84" t="n">
-        <v>18.9</v>
+        <v>16</v>
       </c>
       <c r="H84" t="n">
-        <v>14</v>
+        <v>16.6</v>
       </c>
       <c r="I84" t="n">
-        <v>11.7</v>
+        <v>17.3</v>
       </c>
       <c r="J84" t="n">
-        <v>33.4</v>
+        <v>24.1</v>
       </c>
       <c r="K84" t="n">
-        <v>30</v>
+        <v>28.3</v>
       </c>
       <c r="L84" t="n">
-        <v>46.8</v>
+        <v>49.8</v>
       </c>
       <c r="M84" t="n">
-        <v>50.7</v>
+        <v>48.9</v>
       </c>
       <c r="N84" t="n">
-        <v>10.7</v>
+        <v>7.7</v>
       </c>
       <c r="O84" t="n">
         <v>60</v>
       </c>
       <c r="P84" t="n">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="Q84" t="n">
-        <v>-3.8</v>
+        <v>0.8</v>
       </c>
       <c r="R84" t="n">
-        <v>5.5</v>
+        <v>-2.3</v>
       </c>
       <c r="S84" t="n">
-        <v>-3.9</v>
+        <v>0.9</v>
       </c>
       <c r="T84" t="n">
-        <v>3.4</v>
+        <v>-4.2</v>
       </c>
       <c r="U84" t="n">
+        <v>30</v>
+      </c>
+      <c r="V84" t="n">
         <v>8</v>
       </c>
-      <c r="V84" t="n">
-        <v>28</v>
-      </c>
       <c r="W84" t="inlineStr">
         <is>
-          <t>3.0 (4g)</t>
+          <t>22.6 (5g)</t>
         </is>
       </c>
       <c r="X84" t="n">
-        <v>-10.9</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Chet Holmgren</t>
+          <t>Luguentz Dort</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7226,79 +7226,79 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>15.5</v>
+        <v>7.5</v>
       </c>
       <c r="E85" t="n">
-        <v>12</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F85" t="n">
-        <v>12.6</v>
+        <v>9</v>
       </c>
       <c r="G85" t="n">
-        <v>14.7</v>
+        <v>6.7</v>
       </c>
       <c r="H85" t="n">
-        <v>15.1</v>
+        <v>7.8</v>
       </c>
       <c r="I85" t="n">
-        <v>15.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J85" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="K85" t="n">
         <v>27.8</v>
       </c>
-      <c r="K85" t="n">
-        <v>29.3</v>
-      </c>
       <c r="L85" t="n">
-        <v>52.1</v>
+        <v>30.8</v>
       </c>
       <c r="M85" t="n">
-        <v>50.6</v>
+        <v>34.9</v>
       </c>
       <c r="N85" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="O85" t="n">
+        <v>30</v>
+      </c>
+      <c r="P85" t="n">
         <v>50</v>
       </c>
-      <c r="P85" t="n">
-        <v>47</v>
-      </c>
       <c r="Q85" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="R85" t="n">
-        <v>-3.1</v>
+        <v>0.7</v>
       </c>
       <c r="S85" t="n">
-        <v>1.5</v>
+        <v>-4.1</v>
       </c>
       <c r="T85" t="n">
-        <v>-1.5</v>
+        <v>-5</v>
       </c>
       <c r="U85" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="V85" t="n">
         <v>8</v>
       </c>
       <c r="W85" t="inlineStr">
         <is>
-          <t>19.8 (4g)</t>
+          <t>6.2 (5g)</t>
         </is>
       </c>
       <c r="X85" t="n">
-        <v>-3.2</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Shai Gilgeous-Alexander</t>
+          <t>Kyle Filipowski</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7308,79 +7308,79 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>29.5</v>
+        <v>15.5</v>
       </c>
       <c r="E86" t="n">
-        <v>35</v>
+        <v>20.7</v>
       </c>
       <c r="F86" t="n">
-        <v>32.6</v>
+        <v>22.6</v>
       </c>
       <c r="G86" t="n">
-        <v>30.5</v>
+        <v>16.5</v>
       </c>
       <c r="H86" t="n">
-        <v>30.4</v>
+        <v>15.8</v>
       </c>
       <c r="I86" t="n">
-        <v>31.2</v>
+        <v>14.4</v>
       </c>
       <c r="J86" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="K86" t="n">
-        <v>33.9</v>
+        <v>24.8</v>
       </c>
       <c r="L86" t="n">
-        <v>57.7</v>
+        <v>48.9</v>
       </c>
       <c r="M86" t="n">
-        <v>56.8</v>
+        <v>54.1</v>
       </c>
       <c r="N86" t="n">
-        <v>9.4</v>
+        <v>7.4</v>
       </c>
       <c r="O86" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="P86" t="n">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="Q86" t="n">
-        <v>1.7</v>
+        <v>-1.1</v>
       </c>
       <c r="R86" t="n">
-        <v>1.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S86" t="n">
-        <v>0.9</v>
+        <v>-5.2</v>
       </c>
       <c r="T86" t="n">
-        <v>-0.9</v>
+        <v>1.2</v>
       </c>
       <c r="U86" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="V86" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="W86" t="inlineStr">
         <is>
-          <t>35.6 (5g)</t>
+          <t>11.3 (6g)</t>
         </is>
       </c>
       <c r="X86" t="n">
-        <v>-0.1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Isaiah Joe</t>
+          <t>Ace Bailey</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7390,79 +7390,79 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D87" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="E87" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="F87" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="G87" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="H87" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="I87" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="J87" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="K87" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="L87" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="M87" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="N87" t="n">
         <v>8.5</v>
       </c>
-      <c r="E87" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="F87" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="G87" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="H87" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="I87" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="J87" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="K87" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="L87" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="M87" t="n">
-        <v>43.4</v>
-      </c>
-      <c r="N87" t="n">
-        <v>6.2</v>
-      </c>
       <c r="O87" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="P87" t="n">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="Q87" t="n">
-        <v>4</v>
+        <v>-0.3</v>
       </c>
       <c r="R87" t="n">
-        <v>-2.7</v>
+        <v>-1</v>
       </c>
       <c r="S87" t="n">
-        <v>1.4</v>
+        <v>-1.4</v>
       </c>
       <c r="T87" t="n">
-        <v>-4.8</v>
+        <v>0.6</v>
       </c>
       <c r="U87" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="V87" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="W87" t="inlineStr">
         <is>
-          <t>17.4 (5g)</t>
+          <t>10.0 (3g)</t>
         </is>
       </c>
       <c r="X87" t="n">
-        <v>32.6</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>John Konchar</t>
+          <t>Chet Holmgren</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7472,79 +7472,79 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>6.5</v>
+        <v>14.5</v>
       </c>
       <c r="E88" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F88" t="n">
-        <v>8</v>
+        <v>12.6</v>
       </c>
       <c r="G88" t="n">
-        <v>8.1</v>
+        <v>14.7</v>
       </c>
       <c r="H88" t="n">
-        <v>5.7</v>
+        <v>15.1</v>
       </c>
       <c r="I88" t="n">
-        <v>4.8</v>
+        <v>15.7</v>
       </c>
       <c r="J88" t="n">
-        <v>27.4</v>
+        <v>27.8</v>
       </c>
       <c r="K88" t="n">
-        <v>23.4</v>
+        <v>29.3</v>
       </c>
       <c r="L88" t="n">
-        <v>50.9</v>
+        <v>52.1</v>
       </c>
       <c r="M88" t="n">
-        <v>39</v>
+        <v>50.6</v>
       </c>
       <c r="N88" t="n">
-        <v>5.9</v>
+        <v>4.5</v>
       </c>
       <c r="O88" t="n">
         <v>50</v>
       </c>
       <c r="P88" t="n">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="Q88" t="n">
-        <v>-1.7</v>
+        <v>1.2</v>
       </c>
       <c r="R88" t="n">
-        <v>3.2</v>
+        <v>-3.1</v>
       </c>
       <c r="S88" t="n">
-        <v>11.9</v>
+        <v>1.5</v>
       </c>
       <c r="T88" t="n">
-        <v>4</v>
+        <v>-1.5</v>
       </c>
       <c r="U88" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="V88" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="W88" t="inlineStr">
         <is>
-          <t>1.8 (4g)</t>
+          <t>19.8 (4g)</t>
         </is>
       </c>
       <c r="X88" t="n">
-        <v>-24.9</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Jalen Williams</t>
+          <t>Shai Gilgeous-Alexander</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7558,55 +7558,55 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>16.5</v>
+        <v>29.5</v>
       </c>
       <c r="E89" t="n">
-        <v>16.7</v>
+        <v>35</v>
       </c>
       <c r="F89" t="n">
-        <v>15</v>
+        <v>32.6</v>
       </c>
       <c r="G89" t="n">
-        <v>16</v>
+        <v>30.5</v>
       </c>
       <c r="H89" t="n">
-        <v>16.6</v>
+        <v>30.4</v>
       </c>
       <c r="I89" t="n">
-        <v>17.3</v>
+        <v>31.2</v>
       </c>
       <c r="J89" t="n">
-        <v>24.1</v>
+        <v>33</v>
       </c>
       <c r="K89" t="n">
-        <v>28.3</v>
+        <v>33.9</v>
       </c>
       <c r="L89" t="n">
-        <v>49.8</v>
+        <v>57.7</v>
       </c>
       <c r="M89" t="n">
-        <v>48.9</v>
+        <v>56.8</v>
       </c>
       <c r="N89" t="n">
-        <v>7.7</v>
+        <v>9.4</v>
       </c>
       <c r="O89" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="P89" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="R89" t="n">
-        <v>-2.3</v>
+        <v>1.4</v>
       </c>
       <c r="S89" t="n">
         <v>0.9</v>
       </c>
       <c r="T89" t="n">
-        <v>-4.2</v>
+        <v>-0.9</v>
       </c>
       <c r="U89" t="n">
         <v>30</v>
@@ -7616,17 +7616,17 @@
       </c>
       <c r="W89" t="inlineStr">
         <is>
-          <t>22.6 (5g)</t>
+          <t>35.6 (5g)</t>
         </is>
       </c>
       <c r="X89" t="n">
-        <v>4.2</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Luguentz Dort</t>
+          <t>Isaiah Joe</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7640,55 +7640,55 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="E90" t="n">
-        <v>9.300000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F90" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G90" t="n">
-        <v>6.7</v>
+        <v>10.5</v>
       </c>
       <c r="H90" t="n">
-        <v>7.8</v>
+        <v>11.6</v>
       </c>
       <c r="I90" t="n">
-        <v>8.300000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="J90" t="n">
-        <v>22.8</v>
+        <v>18.4</v>
       </c>
       <c r="K90" t="n">
-        <v>27.8</v>
+        <v>23.2</v>
       </c>
       <c r="L90" t="n">
-        <v>30.8</v>
+        <v>44.8</v>
       </c>
       <c r="M90" t="n">
-        <v>34.9</v>
+        <v>43.4</v>
       </c>
       <c r="N90" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="O90" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="P90" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.8</v>
+        <v>4</v>
       </c>
       <c r="R90" t="n">
-        <v>0.7</v>
+        <v>-2.7</v>
       </c>
       <c r="S90" t="n">
-        <v>-4.1</v>
+        <v>1.4</v>
       </c>
       <c r="T90" t="n">
-        <v>-5</v>
+        <v>-4.8</v>
       </c>
       <c r="U90" t="n">
         <v>30</v>
@@ -7698,11 +7698,11 @@
       </c>
       <c r="W90" t="inlineStr">
         <is>
-          <t>6.2 (5g)</t>
+          <t>17.4 (5g)</t>
         </is>
       </c>
       <c r="X90" t="n">
-        <v>-0.4</v>
+        <v>32.6</v>
       </c>
     </row>
     <row r="91">
@@ -7886,7 +7886,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="E93" t="n">
         <v>10.7</v>
@@ -7925,7 +7925,7 @@
         <v>60</v>
       </c>
       <c r="Q93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R93" t="n">
         <v>-2.5</v>
@@ -7968,7 +7968,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="E94" t="n">
         <v>6.3</v>
@@ -8004,10 +8004,10 @@
         <v>20</v>
       </c>
       <c r="P94" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="Q94" t="n">
-        <v>-0.7</v>
+        <v>0.3</v>
       </c>
       <c r="R94" t="n">
         <v>-0.8</v>
@@ -11211,7 +11211,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Scottie Barnes</t>
+          <t>Jakob Poeltl</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -11221,7 +11221,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -11230,36 +11230,36 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.615</v>
       </c>
       <c r="F2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>14.6</v>
+        <v>14.2</v>
       </c>
       <c r="I2" t="n">
-        <v>1.9</v>
+        <v>4.7</v>
       </c>
       <c r="J2" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="K2" t="n">
-        <v>1.408</v>
+        <v>1.385</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>Barnes's L30 average of 15.9 pts vs the 16.5 line — supports the UNDER. TS% shifts -5.0% in this matchup; FG% +5.4% trending (L10 vs L30). Opponent is elite defense (#2) at slow pace (#24). 7/10 signals agree — Volume, HR L30, Trend, Context support the UNDER; HR L10, H2H, FG Trend dissent. Projection model targets 14.6 pts (1.9 pts below line; 56% blended confidence [T2]).</t>
+          <t>Poeltl averages 17.0 pts in 4 meetings (+7.5 vs line) — supports the OVER. H2H avg 6.7 pts above season L30; TS% shifts +12.7% in this matchup. Opponent is elite defense (#1) at slow pace (#24). 6/10 signals agree — Volume, HR L10, Trend, Context support the OVER; HR L30, Defense, Pace dissent. Projection model targets 14.2 pts (4.7 pts above line; 61% blended confidence [T2]).</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Derrick White</t>
+          <t>Ja'Kobe Walter</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -11274,40 +11274,40 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.544</v>
+        <v>0.555</v>
       </c>
       <c r="F3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>14.7</v>
+        <v>7.4</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J3" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="K3" t="n">
-        <v>1.4</v>
+        <v>1.385</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending down 5.4 pts (L5 vs L30) — supports the UNDER. H2H avg 1.6 pts above season L30. Opponent is average defense (#13) at slow pace (#25). 7/10 signals agree — HR L30, HR L10, Trend, Context support the UNDER; Volume, H2H, FG Trend dissent. Projection model targets 14.7 pts (0.8 pts below line; 54% blended confidence [T3]).</t>
+          <t>Walter averages 7.0 pts in 5 meetings (-2.5 vs line) — supports the UNDER. H2H avg 1.5 pts below season L30; TS% shifts -9.3% in this matchup. Opponent is elite defense (#2) at slow pace (#24). 6/10 signals agree — Volume, HR L30, Context, Defense support the UNDER; HR L10, Trend, FG Trend dissent. Projection model targets 7.4 pts (2.1 pts below line; 55% blended confidence [T2]).</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jakob Poeltl</t>
+          <t>Payton Pritchard</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -11326,36 +11326,36 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.615</v>
+        <v>0.696</v>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>14.2</v>
+        <v>21.9</v>
       </c>
       <c r="I4" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="K4" t="n">
-        <v>1.385</v>
+        <v>1.4</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>Poeltl averages 17.0 pts in 4 meetings (+7.5 vs line) — supports the OVER. H2H avg 6.7 pts above season L30; TS% shifts +12.7% in this matchup. Opponent is elite defense (#1) at slow pace (#24). 6/10 signals agree — Volume, HR L10, Trend, Context support the OVER; HR L30, Defense, Pace dissent. Projection model targets 14.2 pts (4.7 pts above line; 61% blended confidence [T2]).</t>
+          <t>Pritchard averages 20.0 pts in 7 meetings (+4.5 vs line) — supports the OVER. H2H avg 2.8 pts above season L30; TS% shifts +7.8% in this matchup. Opponent is average defense (#13) at slow pace (#25). 7/10 signals agree — Volume, HR L30, HR L10, Trend support the OVER; Defense, Pace, Min Trend dissent. Projection model targets 21.9 pts (6.4 pts above line; 69% blended confidence [T2]). Risk: high variance (σ=7.6) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ja'Kobe Walter</t>
+          <t>Jaylen Brown</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -11370,40 +11370,40 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.555</v>
+        <v>0.656</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>7.4</v>
+        <v>21.4</v>
       </c>
       <c r="I5" t="n">
-        <v>2.1</v>
+        <v>6.1</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9</v>
+        <v>1.833</v>
       </c>
       <c r="K5" t="n">
-        <v>1.385</v>
+        <v>1.909</v>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>Walter averages 7.0 pts in 5 meetings (-2.5 vs line) — supports the UNDER. H2H avg 1.5 pts below season L30; TS% shifts -9.3% in this matchup. Opponent is elite defense (#2) at slow pace (#24). 6/10 signals agree — Volume, HR L30, Context, Defense support the UNDER; HR L10, Trend, FG Trend dissent. Projection model targets 7.4 pts (2.1 pts below line; 55% blended confidence [T2]).</t>
+          <t>Brown averages 21.3 pts in 6 meetings (-6.2 vs line) — marginally supports the UNDER. H2H avg 6.2 pts below season L30. Opponent is average defense (#13) at slow pace (#25). Mixed signals: 5/10 agree (Context, Defense, H2H); counter-signals: Volume, HR L30, HR L10. Projection model targets 21.4 pts (6.1 pts below line; 65% blended confidence [T3]). Risk: L3 has surged to 32.7 after a 24-pt outing (5.2 above L30) — momentum could push over the under line.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Payton Pritchard</t>
+          <t>Neemias Queta</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -11422,36 +11422,36 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.696</v>
+        <v>0.572</v>
       </c>
       <c r="F6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>21.9</v>
+        <v>12.2</v>
       </c>
       <c r="I6" t="n">
-        <v>6.4</v>
+        <v>2.7</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="K6" t="n">
-        <v>1.364</v>
+        <v>1.417</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Pritchard averages 20.0 pts in 7 meetings (+4.5 vs line) — supports the OVER. H2H avg 2.8 pts above season L30; TS% shifts +7.8% in this matchup. Opponent is average defense (#13) at slow pace (#25). 7/10 signals agree — Volume, HR L30, HR L10, Trend support the OVER; Defense, Pace, Min Trend dissent. Projection model targets 21.9 pts (6.4 pts above line; 69% blended confidence [T2]). Risk: high variance (σ=7.6) makes the outcome difficult to call with confidence.</t>
+          <t>Recent scoring trending up 4.1 pts (L5 vs L30) — supports the OVER. TS% shifts +7.1% in this matchup; FG% +9.1% trending (L10 vs L30). Opponent is strong defense (#9) at slow pace (#25). 6/10 signals agree — Volume, HR L10, Trend, Context support the OVER; HR L30, Defense, H2H dissent. Projection model targets 12.2 pts (2.7 pts above line; 57% blended confidence [T2]).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Brandon Ingram</t>
+          <t>Jamal Shead</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -11461,45 +11461,45 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>LEAN UNDER</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T3_LEAN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.583</v>
+        <v>0.518</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>23.4</v>
+        <v>7.5</v>
       </c>
       <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
         <v>2.9</v>
       </c>
-      <c r="J7" t="n">
-        <v>3.05</v>
-      </c>
       <c r="K7" t="n">
-        <v>1.357</v>
+        <v>1.385</v>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending down 5.6 pts (L5 vs L30) — marginally supports the OVER. FG% +3.4% trending (L10 vs L30). Opponent is elite defense (#2) at slow pace (#24). Mixed signals: 3/10 agree (Volume, Context, FG Trend); counter-signals: HR L30, HR L10, Trend. Projection model targets 23.4 pts (2.9 pts above line; 58% blended confidence [T3]). Risk: high variance (σ=8.9) makes the outcome difficult to call with confidence.</t>
+          <t>[Low conviction — lean only] Recent scoring trending up 3.1 pts (L5 vs L30) — supports the lean UNDER. H2H avg 1.7 pts above season L30; Minutes up 3.0 recently (L10=25.8 vs L30=22.8). Opponent is elite defense (#2) at slow pace (#24). 6/10 signals agree — Volume, HR L30, HR L10, Context support the UNDER; Trend, H2H, FG Trend dissent. Projection model targets 7.5 pts (0.0 pts below line; 51% blended confidence [T3_LEAN]). Risk: L3 has surged to 11.0 after a 13-pt outing (5.1 above L30) — momentum could push over the under line.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RJ Barrett</t>
+          <t>Sam Hauser</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -11509,45 +11509,45 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LEAN UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>T3_LEAN</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.522</v>
+        <v>0.582</v>
       </c>
       <c r="F8" t="n">
         <v>6</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>20.2</v>
+        <v>10.3</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3</v>
+        <v>2.8</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="K8" t="n">
-        <v>1.385</v>
+        <v>1.357</v>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>[Low conviction — lean only] Recent scoring trending up 3.3 pts (L5 vs L30) — supports the lean UNDER. H2H avg 3.1 pts above season L30; TS% shifts -4.7% in this matchup. Opponent is elite defense (#2) at slow pace (#24). 6/10 signals agree — Volume, HR L30, Context, Defense support the UNDER; HR L10, Trend, H2H dissent. Projection model targets 20.2 pts (0.3 pts below line; 52% blended confidence [T3_LEAN]). Risk: L3 has surged to 23.0 after a 21-pt outing (4.1 above L30) — momentum could push over the under line.</t>
+          <t>Hauser averages 10.4 pts in 7 meetings (+2.9 vs line) — supports the OVER. TS% shifts +8.4% in this matchup; FG% +3.9% trending (L10 vs L30). Opponent is strong defense (#6) at slow pace (#25). 6/10 signals agree — Volume, HR L30, Trend, Context support the OVER; HR L10, Defense, Pace dissent. Projection model targets 10.3 pts (2.8 pts above line; 58% blended confidence [T2]).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Jaylen Brown</t>
+          <t>Scottie Barnes</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -11562,40 +11562,40 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.656</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>21.4</v>
+        <v>14.6</v>
       </c>
       <c r="I9" t="n">
-        <v>6.1</v>
+        <v>1.9</v>
       </c>
       <c r="J9" t="n">
-        <v>1.87</v>
+        <v>3.05</v>
       </c>
       <c r="K9" t="n">
-        <v>1.87</v>
+        <v>1.357</v>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>Brown averages 21.3 pts in 6 meetings (-6.2 vs line) — marginally supports the UNDER. H2H avg 6.2 pts below season L30. Opponent is average defense (#13) at slow pace (#25). Mixed signals: 5/10 agree (Context, Defense, H2H); counter-signals: Volume, HR L30, HR L10. Projection model targets 21.4 pts (6.1 pts below line; 65% blended confidence [T3]). Risk: L3 has surged to 32.7 after a 24-pt outing (5.2 above L30) — momentum could push over the under line.</t>
+          <t>Barnes's L30 average of 15.9 pts vs the 16.5 line — supports the UNDER. TS% shifts -5.0% in this matchup; FG% +5.4% trending (L10 vs L30). Opponent is elite defense (#2) at slow pace (#24). 7/10 signals agree — Volume, HR L30, Trend, Context support the UNDER; HR L10, H2H, FG Trend dissent. Projection model targets 14.6 pts (1.9 pts below line; 56% blended confidence [T2]).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Neemias Queta</t>
+          <t>Derrick White</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -11605,28 +11605,28 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.572</v>
+        <v>0.544</v>
       </c>
       <c r="F10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>12.2</v>
+        <v>14.7</v>
       </c>
       <c r="I10" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J10" t="n">
         <v>2.75</v>
@@ -11636,14 +11636,14 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending up 4.1 pts (L5 vs L30) — supports the OVER. TS% shifts +7.1% in this matchup; FG% +9.1% trending (L10 vs L30). Opponent is strong defense (#9) at slow pace (#25). 6/10 signals agree — Volume, HR L10, Trend, Context support the OVER; HR L30, Defense, H2H dissent. Projection model targets 12.2 pts (2.7 pts above line; 57% blended confidence [T2]).</t>
+          <t>Recent scoring trending down 5.4 pts (L5 vs L30) — supports the UNDER. H2H avg 1.6 pts above season L30. Opponent is average defense (#13) at slow pace (#25). 7/10 signals agree — HR L30, HR L10, Trend, Context support the UNDER; Volume, H2H, FG Trend dissent. Projection model targets 14.7 pts (0.8 pts below line; 54% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Jayson Tatum</t>
+          <t>Brandon Ingram</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -11653,7 +11653,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -11662,36 +11662,36 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.623</v>
+        <v>0.583</v>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>17.6</v>
+        <v>23.4</v>
       </c>
       <c r="I11" t="n">
-        <v>4.9</v>
+        <v>2.9</v>
       </c>
       <c r="J11" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="K11" t="n">
-        <v>1.345</v>
+        <v>1.417</v>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>Tatum averages 20.5 pts in 4 meetings (-2.0 vs line) — marginally supports the UNDER. H2H avg 4.3 pts below season L30. Opponent is strong defense (#6) at slow pace (#25). Mixed signals: 5/10 agree (Defense, H2H, Pace); counter-signals: Volume, HR L30, HR L10. Projection model targets 17.6 pts (4.9 pts below line; 62% blended confidence [T3]). Risk: 63% over-rate on L30 suggests scoring tendency that could threaten the under.</t>
+          <t>Recent scoring trending down 5.6 pts (L5 vs L30) — marginally supports the OVER. FG% +3.4% trending (L10 vs L30). Opponent is elite defense (#2) at slow pace (#24). Mixed signals: 3/10 agree (Volume, Context, FG Trend); counter-signals: HR L30, HR L10, Trend. Projection model targets 23.4 pts (2.9 pts above line; 58% blended confidence [T3]). Risk: high variance (σ=8.9) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Jamal Shead</t>
+          <t>RJ Barrett</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -11701,12 +11701,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>LEAN UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>T3_LEAN</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -11719,27 +11719,27 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>7.5</v>
+        <v>20.2</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="J12" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K12" t="n">
-        <v>1.364</v>
+        <v>1.357</v>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>[Low conviction — lean only] Recent scoring trending up 3.1 pts (L5 vs L30) — supports the lean UNDER. H2H avg 1.7 pts above season L30; Minutes up 3.0 recently (L10=25.8 vs L30=22.8). Opponent is elite defense (#2) at slow pace (#24). 6/10 signals agree — Volume, HR L30, HR L10, Context support the UNDER; Trend, H2H, FG Trend dissent. Projection model targets 7.5 pts (0.0 pts below line; 51% blended confidence [T3_LEAN]). Risk: L3 has surged to 11.0 after a 13-pt outing (5.1 above L30) — momentum could push over the under line.</t>
+          <t>Recent scoring trending up 3.3 pts (L5 vs L30) — supports the OVER. H2H avg 3.1 pts above season L30; TS% shifts -4.7% in this matchup. Opponent is elite defense (#2) at slow pace (#24). 6/10 signals agree — HR L30, HR L10, Trend, Context support the OVER; Volume, Defense, Pace dissent. Projection model targets 20.2 pts (0.7 pts above line; 51% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sandro Mamukelashvili</t>
+          <t>Jayson Tatum</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -11749,45 +11749,45 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>T1_PREMIUM</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.677</v>
+        <v>0.623</v>
       </c>
       <c r="F13" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>15.5</v>
+        <v>17.6</v>
       </c>
       <c r="I13" t="n">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="J13" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="K13" t="n">
-        <v>1.408</v>
+        <v>1.333</v>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending up 4.7 pts (L5 vs L30) — supports the OVER. TS% shifts +13.0% in this matchup; FG% +8.9% trending (L10 vs L30). Opponent is elite defense (#2) at slow pace (#24). 8/10 signals agree — Volume, HR L30, HR L10, Trend support the OVER; Defense, Pace dissent. Projection model targets 15.5 pts (6.0 pts above line; 67% blended confidence [T1_PREMIUM]).</t>
+          <t>Tatum averages 20.5 pts in 4 meetings (-2.0 vs line) — marginally supports the UNDER. H2H avg 4.3 pts below season L30. Opponent is strong defense (#6) at slow pace (#25). Mixed signals: 5/10 agree (Defense, H2H, Pace); counter-signals: Volume, HR L30, HR L10. Projection model targets 17.6 pts (4.9 pts below line; 62% blended confidence [T3]). Risk: 63% over-rate on L30 suggests scoring tendency that could threaten the under.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sam Hauser</t>
+          <t>Sandro Mamukelashvili</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -11802,33 +11802,33 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1_PREMIUM</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.582</v>
+        <v>0.677</v>
       </c>
       <c r="F14" t="n">
+        <v>8</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="I14" t="n">
         <v>6</v>
       </c>
-      <c r="G14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="I14" t="n">
-        <v>2.8</v>
-      </c>
       <c r="J14" t="n">
-        <v>3.05</v>
+        <v>2.65</v>
       </c>
       <c r="K14" t="n">
-        <v>1.357</v>
+        <v>1.455</v>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>Hauser averages 10.4 pts in 7 meetings (+2.9 vs line) — supports the OVER. TS% shifts +8.4% in this matchup; FG% +3.9% trending (L10 vs L30). Opponent is strong defense (#6) at slow pace (#25). 6/10 signals agree — Volume, HR L30, Trend, Context support the OVER; HR L10, Defense, Pace dissent. Projection model targets 10.3 pts (2.8 pts above line; 58% blended confidence [T2]).</t>
+          <t>Recent scoring trending up 4.7 pts (L5 vs L30) — supports the OVER. TS% shifts +13.0% in this matchup; FG% +8.9% trending (L10 vs L30). Opponent is elite defense (#2) at slow pace (#24). 8/10 signals agree — Volume, HR L30, HR L10, Trend support the OVER; Defense, Pace dissent. Projection model targets 15.5 pts (6.0 pts above line; 67% blended confidence [T1_PREMIUM]).</t>
         </is>
       </c>
     </row>
@@ -11869,10 +11869,10 @@
         <v>4.4</v>
       </c>
       <c r="J15" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="K15" t="n">
-        <v>1.357</v>
+        <v>1.435</v>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
@@ -11917,10 +11917,10 @@
         <v>3.7</v>
       </c>
       <c r="J16" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="K16" t="n">
-        <v>1.417</v>
+        <v>1.364</v>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
@@ -11965,10 +11965,10 @@
         <v>0.5</v>
       </c>
       <c r="J17" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="K17" t="n">
-        <v>1.4</v>
+        <v>1.417</v>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
@@ -12013,10 +12013,10 @@
         <v>2.2</v>
       </c>
       <c r="J18" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="K18" t="n">
-        <v>1.417</v>
+        <v>1.455</v>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
@@ -12061,10 +12061,10 @@
         <v>0.3</v>
       </c>
       <c r="J19" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="K19" t="n">
-        <v>1.364</v>
+        <v>1.4</v>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
@@ -12094,7 +12094,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.546</v>
+        <v>0.588</v>
       </c>
       <c r="F20" t="n">
         <v>7</v>
@@ -12106,17 +12106,17 @@
         <v>11.6</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J20" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="K20" t="n">
-        <v>1.364</v>
+        <v>1.417</v>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>Traore's L30 average of 10.8 pts vs the 12.5 line — supports the UNDER. FG% -8.0% trending (L10 vs L30); Minutes down 2.1 recently (L10=23.4 vs L30=25.5). Opponent is weak defense (#24) at above-average pace (#11). 7/10 signals agree — Volume, HR L30, HR L10, Trend support the UNDER; Defense, H2H, Pace dissent. Projection model targets 11.6 pts (0.9 pts below line; 54% blended confidence [T3]).</t>
+          <t>Traore's L30 of 10.8 pts sits 2.7 below the 13.5 line — supports the UNDER. FG% -8.0% trending (L10 vs L30); Minutes down 2.1 recently (L10=23.4 vs L30=25.5). Opponent is weak defense (#24) at above-average pace (#11). 7/10 signals agree — Volume, HR L30, HR L10, Trend support the UNDER; Defense, H2H, Pace dissent. Projection model targets 11.6 pts (1.9 pts below line; 58% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
@@ -12157,10 +12157,10 @@
         <v>0.3</v>
       </c>
       <c r="J21" t="n">
-        <v>3.15</v>
+        <v>2.75</v>
       </c>
       <c r="K21" t="n">
-        <v>1.333</v>
+        <v>1.417</v>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
@@ -12171,7 +12171,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Alex Sarr</t>
+          <t>Will Riley</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -12181,93 +12181,93 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1_PREMIUM</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.664</v>
       </c>
       <c r="F22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H22" t="n">
-        <v>11.9</v>
+        <v>22.8</v>
       </c>
       <c r="I22" t="n">
-        <v>1.6</v>
+        <v>6.3</v>
       </c>
       <c r="J22" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="K22" t="n">
-        <v>1.333</v>
+        <v>1.357</v>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending down 5.9 pts (L5 vs L30) — supports the UNDER. FG% -6.9% trending (L10 vs L30); Minutes down 4.2 recently (L10=21.8 vs L30=26.0). Opponent is below-average defense (#19) at slow pace (#30). 6/10 signals agree — HR L10, Trend, H2H, Pace support the UNDER; Volume, HR L30, Context dissent. Projection model targets 11.9 pts (1.6 pts below line; 55% blended confidence [T2]). Risk: high variance (σ=7.3) makes the outcome difficult to call with confidence.</t>
+          <t>Recent scoring trending up 5.4 pts (L5 vs L30) — supports the OVER. Opponent is below-average defense (#20) at slow pace (#30). 7/10 signals agree — HR L30, HR L10, Trend, Context support the OVER; Volume, H2H, Pace dissent. Projection model targets 22.8 pts (6.3 pts above line; 66% blended confidence [T1_PREMIUM]).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Will Riley</t>
+          <t>Royce O'Neale</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>WAS @ BKN</t>
+          <t>PHX @ CHI</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>T1_PREMIUM</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.664</v>
+        <v>0.655</v>
       </c>
       <c r="F23" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>22.8</v>
+        <v>2.4</v>
       </c>
       <c r="I23" t="n">
-        <v>6.3</v>
+        <v>5.1</v>
       </c>
       <c r="J23" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="K23" t="n">
-        <v>1.408</v>
+        <v>1.417</v>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending up 5.4 pts (L5 vs L30) — supports the OVER. Opponent is below-average defense (#20) at slow pace (#30). 7/10 signals agree — HR L30, HR L10, Trend, Context support the OVER; Volume, H2H, Pace dissent. Projection model targets 22.8 pts (6.3 pts above line; 66% blended confidence [T1_PREMIUM]).</t>
+          <t>O'Neale averages 3.3 pts in 3 meetings (-4.2 vs line) — marginally supports the UNDER. H2H avg 5.8 pts below season L30; TS% shifts -33.1% in this matchup. Opponent is weak defense (#28) at fast pace (#1). Mixed signals: 2/10 agree (H2H, Min Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 2.4 pts (5.1 pts below line; 65% blended confidence [T3]). Risk: 63% over-rate on L30 suggests scoring tendency that could threaten the under.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Royce O'Neale</t>
+          <t>Mark Williams</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -12277,38 +12277,38 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.641</v>
+        <v>0.646</v>
       </c>
       <c r="F24" t="n">
+        <v>7</v>
+      </c>
+      <c r="G24" t="n">
         <v>2</v>
       </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
       <c r="H24" t="n">
-        <v>2.4</v>
+        <v>13.2</v>
       </c>
       <c r="I24" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="J24" t="n">
-        <v>2.65</v>
+        <v>1.862</v>
       </c>
       <c r="K24" t="n">
-        <v>1.455</v>
+        <v>1.901</v>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>O'Neale averages 3.3 pts in 3 meetings (-3.2 vs line) — marginally supports the UNDER. H2H avg 5.8 pts below season L30; TS% shifts -33.1% in this matchup. Opponent is weak defense (#28) at fast pace (#1). Mixed signals: 2/10 agree (H2H, Min Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 2.4 pts (4.1 pts below line; 64% blended confidence [T3]). Risk: 67% over-rate on L30 suggests scoring tendency that could threaten the under.</t>
+          <t>Williams averages 19.0 pts in 4 meetings (+10.5 vs line) — supports the OVER. H2H avg 8.8 pts above season L30; TS% shifts +8.8% in this matchup. Opponent is weak defense (#26) at fast pace (#1). 7/10 signals agree — Volume, HR L30, HR L10, Context support the OVER; Trend, FG Trend, Min Trend dissent. Projection model targets 13.2 pts (4.7 pts above line; 64% blended confidence [T1]).</t>
         </is>
       </c>
     </row>
@@ -12349,10 +12349,10 @@
         <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="K25" t="n">
-        <v>1.408</v>
+        <v>1.385</v>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
@@ -12397,10 +12397,10 @@
         <v>1.8</v>
       </c>
       <c r="J26" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="K26" t="n">
-        <v>1.385</v>
+        <v>1.408</v>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
@@ -12445,10 +12445,10 @@
         <v>2.6</v>
       </c>
       <c r="J27" t="n">
-        <v>1.87</v>
+        <v>1.909</v>
       </c>
       <c r="K27" t="n">
-        <v>1.87</v>
+        <v>1.833</v>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
@@ -12541,10 +12541,10 @@
         <v>1</v>
       </c>
       <c r="J29" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="K29" t="n">
-        <v>1.364</v>
+        <v>1.408</v>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
@@ -12589,10 +12589,10 @@
         <v>2.3</v>
       </c>
       <c r="J30" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="K30" t="n">
-        <v>1.465</v>
+        <v>1.408</v>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
@@ -12637,10 +12637,10 @@
         <v>4.7</v>
       </c>
       <c r="J31" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="K31" t="n">
-        <v>1.345</v>
+        <v>1.364</v>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
@@ -12685,10 +12685,10 @@
         <v>0.9</v>
       </c>
       <c r="J32" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="K32" t="n">
-        <v>1.345</v>
+        <v>1.364</v>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
@@ -12733,10 +12733,10 @@
         <v>1.8</v>
       </c>
       <c r="J33" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="K33" t="n">
-        <v>1.4</v>
+        <v>1.385</v>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
@@ -12781,10 +12781,10 @@
         <v>0.1</v>
       </c>
       <c r="J34" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="K34" t="n">
-        <v>1.4</v>
+        <v>1.417</v>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
@@ -12829,10 +12829,10 @@
         <v>11.7</v>
       </c>
       <c r="J35" t="n">
+        <v>1.952</v>
+      </c>
+      <c r="K35" t="n">
         <v>1.8</v>
-      </c>
-      <c r="K35" t="n">
-        <v>1.952</v>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
@@ -12862,7 +12862,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.63</v>
+        <v>0.666</v>
       </c>
       <c r="F36" t="n">
         <v>4</v>
@@ -12874,17 +12874,17 @@
         <v>7.5</v>
       </c>
       <c r="I36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J36" t="n">
-        <v>1.741</v>
+        <v>1.833</v>
       </c>
       <c r="K36" t="n">
-        <v>2</v>
+        <v>1.909</v>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>Jr.'s L30 of 7.7 pts sits 3.8 below the 11.5 line — marginally supports the UNDER. Opponent is weak defense (#24) at moderate pace (#14). Mixed signals: 4/10 agree (Volume, HR L30, HR L10); counter-signals: Trend, Defense, H2H. Projection model targets 7.5 pts (4.0 pts below line; 62% blended confidence [T3]).</t>
+          <t>Jr.'s L30 of 7.7 pts sits 4.8 below the 12.5 line — marginally supports the UNDER. Opponent is weak defense (#24) at moderate pace (#14). Mixed signals: 4/10 agree (Volume, HR L30, HR L10); counter-signals: Trend, Defense, H2H. Projection model targets 7.5 pts (5.0 pts below line; 66% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
@@ -12925,7 +12925,7 @@
         <v>3.6</v>
       </c>
       <c r="J37" t="n">
-        <v>1.901</v>
+        <v>1.909</v>
       </c>
       <c r="K37" t="n">
         <v>1.833</v>
@@ -12973,10 +12973,10 @@
         <v>1.1</v>
       </c>
       <c r="J38" t="n">
-        <v>1.833</v>
+        <v>1.769</v>
       </c>
       <c r="K38" t="n">
-        <v>1.909</v>
+        <v>1.952</v>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
@@ -13021,10 +13021,10 @@
         <v>3.6</v>
       </c>
       <c r="J39" t="n">
-        <v>1.833</v>
+        <v>1.8</v>
       </c>
       <c r="K39" t="n">
-        <v>1.909</v>
+        <v>1.952</v>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
@@ -13069,10 +13069,10 @@
         <v>4.2</v>
       </c>
       <c r="J40" t="n">
+        <v>1.909</v>
+      </c>
+      <c r="K40" t="n">
         <v>1.833</v>
-      </c>
-      <c r="K40" t="n">
-        <v>1.909</v>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
@@ -13117,10 +13117,10 @@
         <v>3.4</v>
       </c>
       <c r="J41" t="n">
-        <v>1.741</v>
+        <v>1.909</v>
       </c>
       <c r="K41" t="n">
-        <v>2</v>
+        <v>1.833</v>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
@@ -13165,10 +13165,10 @@
         <v>6.6</v>
       </c>
       <c r="J42" t="n">
-        <v>1.952</v>
+        <v>1.87</v>
       </c>
       <c r="K42" t="n">
-        <v>1.769</v>
+        <v>1.87</v>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
@@ -13213,10 +13213,10 @@
         <v>2.1</v>
       </c>
       <c r="J43" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="K43" t="n">
-        <v>1.408</v>
+        <v>1.435</v>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
@@ -13261,10 +13261,10 @@
         <v>4.4</v>
       </c>
       <c r="J44" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="K44" t="n">
-        <v>1.417</v>
+        <v>1.4</v>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
@@ -13309,10 +13309,10 @@
         <v>11.2</v>
       </c>
       <c r="J45" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="K45" t="n">
-        <v>1.345</v>
+        <v>1.435</v>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
@@ -13357,10 +13357,10 @@
         <v>0.5</v>
       </c>
       <c r="J46" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="K46" t="n">
-        <v>1.357</v>
+        <v>1.385</v>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
@@ -13405,10 +13405,10 @@
         <v>0.4</v>
       </c>
       <c r="J47" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="K47" t="n">
-        <v>1.408</v>
+        <v>1.455</v>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
@@ -13501,10 +13501,10 @@
         <v>1.2</v>
       </c>
       <c r="J49" t="n">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="K49" t="n">
-        <v>1.455</v>
+        <v>1.345</v>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.575</v>
+        <v>0.617</v>
       </c>
       <c r="F51" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G51" t="n">
         <v>1</v>
@@ -13594,7 +13594,7 @@
         <v>5.7</v>
       </c>
       <c r="I51" t="n">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="J51" t="n">
         <v>2.8</v>
@@ -13604,7 +13604,7 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>Low scoring variance (σ=3.5) — highly predictable output near line — supports the UNDER. TS% shifts -14.7% in this matchup; FG% +3.2% trending (L10 vs L30). Opponent is below-average defense (#22) at above-average pace (#12). 6/10 signals agree — HR L30, HR L10, Trend, Context support the UNDER; Volume, Defense, Pace dissent. Projection model targets 5.7 pts (2.8 pts below line; 57% blended confidence [T2]).</t>
+          <t>Low scoring variance (σ=3.5) — highly predictable output near line — supports the UNDER. TS% shifts -14.7% in this matchup; FG% +3.2% trending (L10 vs L30). Opponent is below-average defense (#22) at above-average pace (#12). 7/10 signals agree — Volume, HR L30, HR L10, Trend support the UNDER; Defense, Pace, FG Trend dissent. Projection model targets 5.7 pts (3.8 pts below line; 61% blended confidence [T2]).</t>
         </is>
       </c>
     </row>
@@ -13693,10 +13693,10 @@
         <v>0.6</v>
       </c>
       <c r="J53" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K53" t="n">
-        <v>1.364</v>
+        <v>1.357</v>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
@@ -13741,10 +13741,10 @@
         <v>4.4</v>
       </c>
       <c r="J54" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="K54" t="n">
-        <v>1.364</v>
+        <v>1.385</v>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
@@ -13837,10 +13837,10 @@
         <v>1.2</v>
       </c>
       <c r="J56" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="K56" t="n">
-        <v>1.408</v>
+        <v>1.435</v>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
@@ -13933,10 +13933,10 @@
         <v>1.3</v>
       </c>
       <c r="J58" t="n">
-        <v>2.85</v>
+        <v>3.05</v>
       </c>
       <c r="K58" t="n">
-        <v>1.4</v>
+        <v>1.357</v>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
@@ -14029,10 +14029,10 @@
         <v>0.2</v>
       </c>
       <c r="J60" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="K60" t="n">
-        <v>1.408</v>
+        <v>1.364</v>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
@@ -14173,10 +14173,10 @@
         <v>3.6</v>
       </c>
       <c r="J63" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="K63" t="n">
-        <v>1.408</v>
+        <v>1.435</v>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
@@ -14221,10 +14221,10 @@
         <v>10.7</v>
       </c>
       <c r="J64" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="K64" t="n">
-        <v>1.385</v>
+        <v>1.357</v>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
@@ -14269,10 +14269,10 @@
         <v>1.3</v>
       </c>
       <c r="J65" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="K65" t="n">
-        <v>1.385</v>
+        <v>1.417</v>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
@@ -14302,7 +14302,7 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.664</v>
+        <v>0.636</v>
       </c>
       <c r="F66" t="n">
         <v>6</v>
@@ -14314,17 +14314,17 @@
         <v>18.4</v>
       </c>
       <c r="I66" t="n">
-        <v>7.1</v>
+        <v>6.1</v>
       </c>
       <c r="J66" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K66" t="n">
-        <v>1.364</v>
+        <v>1.345</v>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending down 4.1 pts (L5 vs L30) — supports the UNDER. Minutes down 2.5 recently (L10=33.1 vs L30=35.6). Opponent is strong defense (#9) at slow pace (#21). 6/10 signals agree — HR L10, Trend, Defense, Pace support the UNDER; Volume, HR L30, Context dissent. Projection model targets 18.4 pts (7.1 pts below line; 66% blended confidence [T3]). Risk: high variance (σ=11.9) makes the outcome difficult to call with confidence.</t>
+          <t>Recent scoring trending down 4.1 pts (L5 vs L30) — supports the UNDER. Minutes down 2.5 recently (L10=33.1 vs L30=35.6). Opponent is strong defense (#9) at slow pace (#21). 6/10 signals agree — HR L10, Trend, Defense, Pace support the UNDER; Volume, HR L30, Context dissent. Projection model targets 18.4 pts (6.1 pts below line; 63% blended confidence [T3]). Risk: high variance (σ=11.9) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
@@ -14346,33 +14346,33 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>T1_PREMIUM</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.762</v>
+        <v>0.754</v>
       </c>
       <c r="F67" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H67" t="n">
         <v>5.6</v>
       </c>
       <c r="I67" t="n">
-        <v>12.9</v>
+        <v>11.9</v>
       </c>
       <c r="J67" t="n">
-        <v>2.85</v>
+        <v>3.05</v>
       </c>
       <c r="K67" t="n">
-        <v>1.4</v>
+        <v>1.357</v>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending down 4.9 pts (L5 vs L30) — supports the UNDER. FG% -3.4% trending (L10 vs L30); Minutes down 2.6 recently (L10=28.4 vs L30=31.0). Opponent is average defense (#14) at moderate pace (#16). 7/10 signals agree — HR L10, Trend, Context, Defense support the UNDER; Volume, HR L30, H2H dissent. Projection model targets 5.6 pts (12.9 pts below line; 76% blended confidence [T1_PREMIUM]).</t>
+          <t>Recent scoring trending down 4.9 pts (L5 vs L30) — supports the UNDER. FG% -3.4% trending (L10 vs L30); Minutes down 2.6 recently (L10=28.4 vs L30=31.0). Opponent is average defense (#14) at moderate pace (#16). 6/10 signals agree — HR L10, Trend, Defense, Pace support the UNDER; Volume, HR L30, Context dissent. Projection model targets 5.6 pts (11.9 pts below line; 75% blended confidence [T2]).</t>
         </is>
       </c>
     </row>
@@ -14413,10 +14413,10 @@
         <v>5.1</v>
       </c>
       <c r="J68" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="K68" t="n">
-        <v>1.385</v>
+        <v>1.357</v>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
@@ -14653,10 +14653,10 @@
         <v>3.2</v>
       </c>
       <c r="J73" t="n">
-        <v>1.87</v>
+        <v>1.952</v>
       </c>
       <c r="K73" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
@@ -14845,10 +14845,10 @@
         <v>2</v>
       </c>
       <c r="J77" t="n">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="K77" t="n">
-        <v>1.455</v>
+        <v>1.364</v>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
@@ -14941,10 +14941,10 @@
         <v>3.7</v>
       </c>
       <c r="J79" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="K79" t="n">
-        <v>1.357</v>
+        <v>1.435</v>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
@@ -14955,7 +14955,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Kyle Filipowski</t>
+          <t>Alex Caruso</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -14970,40 +14970,40 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.533</v>
+        <v>0.597</v>
       </c>
       <c r="F80" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H80" t="n">
-        <v>16</v>
+        <v>7.2</v>
       </c>
       <c r="I80" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J80" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="K80" t="n">
-        <v>1.364</v>
+        <v>1.435</v>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending up 8.2 pts (L5 vs L30) — marginally supports the OVER. H2H avg 3.1 pts below season L30; FG% -5.2% trending (L10 vs L30). Opponent is strong defense (#8) at slow pace (#28). Mixed signals: 3/10 agree (HR L10, Trend, Min Trend); counter-signals: Volume, HR L30, Context. Projection model targets 16.0 pts (0.5 pts above line; 53% blended confidence [T3]). Risk: high variance (σ=7.4) makes the outcome difficult to call with confidence.</t>
+          <t>Caruso averages 8.7 pts in 3 meetings (+4.2 vs line) — supports the OVER. H2H avg 2.4 pts above season L30; TS% shifts +23.7% in this matchup. Opponent is weak defense (#30) at above-average pace (#8). 7/10 signals agree — Volume, HR L30, Context, Defense support the OVER; HR L10, Trend, FG Trend dissent. Projection model targets 7.2 pts (2.7 pts above line; 59% blended confidence [T2]).</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Alex Caruso</t>
+          <t>Jared McCain</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -15013,45 +15013,45 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="F81" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
       <c r="I81" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="J81" t="n">
-        <v>3.15</v>
+        <v>2.85</v>
       </c>
       <c r="K81" t="n">
-        <v>1.333</v>
+        <v>1.4</v>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>Caruso averages 8.7 pts in 3 meetings (+3.2 vs line) — supports the OVER. H2H avg 2.4 pts above season L30; TS% shifts +23.7% in this matchup. Opponent is weak defense (#30) at above-average pace (#8). 6/10 signals agree — Volume, Context, Defense, H2H support the OVER; HR L30, HR L10, Trend dissent. Projection model targets 7.2 pts (1.7 pts above line; 56% blended confidence [T2]).</t>
+          <t>Recent scoring trending down 6.0 pts (L5 vs L30) — marginally supports the UNDER. FG% -3.8% trending (L10 vs L30). Opponent is weak defense (#30) at above-average pace (#8). Mixed signals: 4/10 agree (HR L10, Trend, FG Trend); counter-signals: Volume, HR L30, Context. Projection model targets 5.5 pts (3.0 pts below line; 56% blended confidence [T3]). Risk: high variance (σ=8.2) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Ace Bailey</t>
+          <t>Cody Williams</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -15070,36 +15070,36 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.573</v>
+        <v>0.732</v>
       </c>
       <c r="F82" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>14.9</v>
+        <v>6.9</v>
       </c>
       <c r="I82" t="n">
-        <v>2.6</v>
+        <v>8.6</v>
       </c>
       <c r="J82" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="K82" t="n">
-        <v>1.4</v>
+        <v>1.385</v>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>Bailey averages 10.0 pts in 3 meetings (-7.5 vs line) — supports the UNDER. H2H avg 7.2 pts below season L30; TS% shifts +5.4% in this matchup. Opponent is strong defense (#8) at slow pace (#28). 8/10 signals agree — Volume, HR L30, Trend, Context support the UNDER; HR L10, Min Trend dissent. Projection model targets 14.9 pts (2.6 pts below line; 57% blended confidence [T3]). Risk: high variance (σ=8.5) makes the outcome difficult to call with confidence.</t>
+          <t>Williams averages 3.0 pts in 4 meetings (-12.5 vs line) — supports the UNDER. H2H avg 8.7 pts below season L30; TS% shifts -10.9% in this matchup. Opponent is strong defense (#8) at slow pace (#28). 7/10 signals agree — Volume, HR L30, Context, Defense support the UNDER; HR L10, Trend, Min Trend dissent. Projection model targets 6.9 pts (8.6 pts below line; 73% blended confidence [T3]). Risk: L3 has surged to 20.7 after a 2-pt outing (9.0 above L30) — momentum could push over the under line.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Jared McCain</t>
+          <t>John Konchar</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -15114,40 +15114,40 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.629</v>
       </c>
       <c r="F83" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H83" t="n">
-        <v>5.5</v>
+        <v>1.6</v>
       </c>
       <c r="I83" t="n">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="J83" t="n">
-        <v>2.75</v>
+        <v>1.833</v>
       </c>
       <c r="K83" t="n">
-        <v>1.417</v>
+        <v>1.909</v>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending down 6.0 pts (L5 vs L30) — marginally supports the UNDER. FG% -3.8% trending (L10 vs L30). Opponent is weak defense (#30) at above-average pace (#8). Mixed signals: 4/10 agree (HR L10, Trend, FG Trend); counter-signals: Volume, HR L30, Context. Projection model targets 5.5 pts (3.0 pts below line; 56% blended confidence [T3]). Risk: high variance (σ=8.2) makes the outcome difficult to call with confidence.</t>
+          <t>Konchar averages 1.8 pts in 4 meetings (-4.7 vs line) — supports the UNDER. H2H avg 3.0 pts below season L30; TS% shifts -24.9% in this matchup. Opponent is strong defense (#6) at slow pace (#28). 6/10 signals agree — Volume, HR L30, Context, Defense support the UNDER; HR L10, Trend, FG Trend dissent. Projection model targets 1.6 pts (4.9 pts below line; 62% blended confidence [T2]).</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Cody Williams</t>
+          <t>Jalen Williams</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -15157,45 +15157,45 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.732</v>
+        <v>0.556</v>
       </c>
       <c r="F84" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H84" t="n">
-        <v>6.9</v>
+        <v>18</v>
       </c>
       <c r="I84" t="n">
-        <v>8.6</v>
+        <v>1.5</v>
       </c>
       <c r="J84" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K84" t="n">
-        <v>1.364</v>
+        <v>1.345</v>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>Williams averages 3.0 pts in 4 meetings (-12.5 vs line) — supports the UNDER. H2H avg 8.7 pts below season L30; TS% shifts -10.9% in this matchup. Opponent is strong defense (#8) at slow pace (#28). 7/10 signals agree — Volume, HR L30, Context, Defense support the UNDER; HR L10, Trend, Min Trend dissent. Projection model targets 6.9 pts (8.6 pts below line; 73% blended confidence [T3]). Risk: L3 has surged to 20.7 after a 2-pt outing (9.0 above L30) — momentum could push over the under line.</t>
+          <t>Williams averages 22.6 pts in 5 meetings (+6.1 vs line) — supports the OVER. H2H avg 5.3 pts above season L30; TS% shifts +4.2% in this matchup. Opponent is weak defense (#30) at above-average pace (#8). 8/10 signals agree — Volume, HR L30, HR L10, Context support the OVER; Trend, Min Trend dissent. Projection model targets 18.0 pts (1.5 pts above line; 55% blended confidence [T2]). Risk: high variance (σ=7.7) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Chet Holmgren</t>
+          <t>Luguentz Dort</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -15205,7 +15205,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -15214,19 +15214,19 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="F85" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>17.5</v>
+        <v>4.8</v>
       </c>
       <c r="I85" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="J85" t="n">
         <v>2.8</v>
@@ -15236,14 +15236,14 @@
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>Holmgren averages 19.8 pts in 4 meetings (+4.3 vs line) — supports the OVER. H2H avg 4.1 pts above season L30; TS% shifts -3.2% in this matchup. Opponent is below-average defense (#22) at above-average pace (#8). 6/10 signals agree — Volume, Context, Defense, H2H support the OVER; HR L30, HR L10, Trend dissent. Projection model targets 17.5 pts (2.0 pts above line; 55% blended confidence [T3]).</t>
+          <t>Low scoring variance (σ=4.8) — highly predictable output near line — marginally supports the UNDER. H2H avg 2.1 pts below season L30; FG% -4.1% trending (L10 vs L30). Opponent is weak defense (#30) at above-average pace (#8). Mixed signals: 5/10 agree (HR L10, Context, H2H); counter-signals: Volume, HR L30, Trend. Projection model targets 4.8 pts (2.7 pts below line; 56% blended confidence [T3]). Risk: minutes trending down (22.8 L10 vs 27.8 L30) — role reduction would suppress counting stats.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Shai Gilgeous-Alexander</t>
+          <t>Kyle Filipowski</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -15262,36 +15262,36 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.534</v>
+        <v>0.533</v>
       </c>
       <c r="F86" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>29.8</v>
+        <v>16</v>
       </c>
       <c r="I86" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J86" t="n">
-        <v>1.87</v>
+        <v>2.9</v>
       </c>
       <c r="K86" t="n">
-        <v>1.87</v>
+        <v>1.385</v>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>Gilgeous-Alexander averages 35.6 pts in 5 meetings (+6.1 vs line) — supports the OVER. H2H avg 4.4 pts above season L30. Opponent is weak defense (#30) at above-average pace (#8). 8/10 signals agree — Volume, HR L30, Trend, Context support the OVER; HR L10, Min Trend dissent. Projection model targets 29.8 pts (0.3 pts above line; 53% blended confidence [T3]). Risk: high variance (σ=9.4) makes the outcome difficult to call with confidence.</t>
+          <t>Recent scoring trending up 8.2 pts (L5 vs L30) — marginally supports the OVER. H2H avg 3.1 pts below season L30; FG% -5.2% trending (L10 vs L30). Opponent is strong defense (#8) at slow pace (#28). Mixed signals: 3/10 agree (HR L10, Trend, Min Trend); counter-signals: Volume, HR L30, Context. Projection model targets 16.0 pts (0.5 pts above line; 53% blended confidence [T3]). Risk: high variance (σ=7.4) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Isaiah Joe</t>
+          <t>Ace Bailey</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -15301,45 +15301,45 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>T1_PREMIUM</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.702</v>
+        <v>0.573</v>
       </c>
       <c r="F87" t="n">
         <v>8</v>
       </c>
       <c r="G87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>15.2</v>
+        <v>14.9</v>
       </c>
       <c r="I87" t="n">
-        <v>6.7</v>
+        <v>2.6</v>
       </c>
       <c r="J87" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="K87" t="n">
-        <v>1.465</v>
+        <v>1.364</v>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>Joe averages 17.4 pts in 5 meetings (+8.9 vs line) — supports the OVER. H2H avg 4.9 pts above season L30; TS% shifts +32.6% in this matchup. Opponent is weak defense (#30) at above-average pace (#8). 8/10 signals agree — Volume, HR L30, HR L10, Context support the OVER; Trend, Min Trend dissent. Projection model targets 15.2 pts (6.7 pts above line; 70% blended confidence [T1_PREMIUM]). Risk: minutes trending down (18.4 L10 vs 23.2 L30) — role reduction would suppress counting stats.</t>
+          <t>Bailey averages 10.0 pts in 3 meetings (-7.5 vs line) — supports the UNDER. H2H avg 7.2 pts below season L30; TS% shifts +5.4% in this matchup. Opponent is strong defense (#8) at slow pace (#28). 8/10 signals agree — Volume, HR L30, Trend, Context support the UNDER; HR L10, Min Trend dissent. Projection model targets 14.9 pts (2.6 pts below line; 57% blended confidence [T3]). Risk: high variance (σ=8.5) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>John Konchar</t>
+          <t>Chet Holmgren</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -15349,45 +15349,45 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.629</v>
+        <v>0.594</v>
       </c>
       <c r="F88" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>1.6</v>
+        <v>17.5</v>
       </c>
       <c r="I88" t="n">
-        <v>4.9</v>
+        <v>3</v>
       </c>
       <c r="J88" t="n">
-        <v>1.862</v>
+        <v>3</v>
       </c>
       <c r="K88" t="n">
-        <v>1.901</v>
+        <v>1.364</v>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>Konchar averages 1.8 pts in 4 meetings (-4.7 vs line) — supports the UNDER. H2H avg 3.0 pts below season L30; TS% shifts -24.9% in this matchup. Opponent is strong defense (#6) at slow pace (#28). 6/10 signals agree — Volume, HR L30, Context, Defense support the UNDER; HR L10, Trend, FG Trend dissent. Projection model targets 1.6 pts (4.9 pts below line; 62% blended confidence [T2]).</t>
+          <t>Holmgren averages 19.8 pts in 4 meetings (+5.3 vs line) — supports the OVER. H2H avg 4.1 pts above season L30; TS% shifts -3.2% in this matchup. Opponent is below-average defense (#22) at above-average pace (#8). 7/10 signals agree — Volume, HR L30, Context, Defense support the OVER; HR L10, Trend, Min Trend dissent. Projection model targets 17.5 pts (3.0 pts above line; 59% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Jalen Williams</t>
+          <t>Shai Gilgeous-Alexander</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -15402,40 +15402,40 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.556</v>
+        <v>0.534</v>
       </c>
       <c r="F89" t="n">
         <v>8</v>
       </c>
       <c r="G89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>18</v>
+        <v>29.8</v>
       </c>
       <c r="I89" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="J89" t="n">
-        <v>3.05</v>
+        <v>1.8</v>
       </c>
       <c r="K89" t="n">
-        <v>1.357</v>
+        <v>1.952</v>
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>Williams averages 22.6 pts in 5 meetings (+6.1 vs line) — supports the OVER. H2H avg 5.3 pts above season L30; TS% shifts +4.2% in this matchup. Opponent is weak defense (#30) at above-average pace (#8). 8/10 signals agree — Volume, HR L30, HR L10, Context support the OVER; Trend, Min Trend dissent. Projection model targets 18.0 pts (1.5 pts above line; 55% blended confidence [T2]). Risk: high variance (σ=7.7) makes the outcome difficult to call with confidence.</t>
+          <t>Gilgeous-Alexander averages 35.6 pts in 5 meetings (+6.1 vs line) — supports the OVER. H2H avg 4.4 pts above season L30. Opponent is weak defense (#30) at above-average pace (#8). 8/10 signals agree — Volume, HR L30, Trend, Context support the OVER; HR L10, Min Trend dissent. Projection model targets 29.8 pts (0.3 pts above line; 53% blended confidence [T3]). Risk: high variance (σ=9.4) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Luguentz Dort</t>
+          <t>Isaiah Joe</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -15445,38 +15445,38 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T1_PREMIUM</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.702</v>
       </c>
       <c r="F90" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H90" t="n">
-        <v>4.8</v>
+        <v>15.2</v>
       </c>
       <c r="I90" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="J90" t="n">
         <v>2.7</v>
       </c>
-      <c r="J90" t="n">
-        <v>2.8</v>
-      </c>
       <c r="K90" t="n">
-        <v>1.408</v>
+        <v>1.435</v>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>Low scoring variance (σ=4.8) — highly predictable output near line — marginally supports the UNDER. H2H avg 2.1 pts below season L30; FG% -4.1% trending (L10 vs L30). Opponent is weak defense (#30) at above-average pace (#8). Mixed signals: 5/10 agree (HR L10, Context, H2H); counter-signals: Volume, HR L30, Trend. Projection model targets 4.8 pts (2.7 pts below line; 56% blended confidence [T3]). Risk: minutes trending down (22.8 L10 vs 27.8 L30) — role reduction would suppress counting stats.</t>
+          <t>Joe averages 17.4 pts in 5 meetings (+8.9 vs line) — supports the OVER. H2H avg 4.9 pts above season L30; TS% shifts +32.6% in this matchup. Opponent is weak defense (#30) at above-average pace (#8). 8/10 signals agree — Volume, HR L30, HR L10, Context support the OVER; Trend, Min Trend dissent. Projection model targets 15.2 pts (6.7 pts above line; 70% blended confidence [T1_PREMIUM]). Risk: minutes trending down (18.4 L10 vs 23.2 L30) — role reduction would suppress counting stats.</t>
         </is>
       </c>
     </row>
@@ -15517,10 +15517,10 @@
         <v>4</v>
       </c>
       <c r="J91" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="K91" t="n">
-        <v>1.435</v>
+        <v>1.476</v>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
@@ -15565,10 +15565,10 @@
         <v>5.1</v>
       </c>
       <c r="J92" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="K92" t="n">
-        <v>1.364</v>
+        <v>1.408</v>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
@@ -15598,7 +15598,7 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.546</v>
       </c>
       <c r="F93" t="n">
         <v>4</v>
@@ -15610,17 +15610,17 @@
         <v>10.2</v>
       </c>
       <c r="I93" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J93" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="K93" t="n">
-        <v>1.357</v>
+        <v>1.435</v>
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>Mitchell averages 9.8 pts in 5 meetings (-2.7 vs line) — marginally supports the UNDER. H2H avg 3.7 pts below season L30; TS% shifts -5.5% in this matchup. Opponent is weak defense (#30) at above-average pace (#8). Mixed signals: 4/10 agree (Trend, H2H, FG Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 10.2 pts (2.3 pts below line; 56% blended confidence [T3]). Risk: 60% over-rate on L30 suggests scoring tendency that could threaten the under.</t>
+          <t>Recent scoring trending down 2.5 pts (L5 vs L30) — marginally supports the UNDER. H2H avg 3.7 pts below season L30; TS% shifts -5.5% in this matchup. Opponent is weak defense (#30) at above-average pace (#8). Mixed signals: 4/10 agree (Trend, H2H, FG Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 10.2 pts (1.3 pts below line; 54% blended confidence [T3]). Risk: 60% over-rate on L30 suggests scoring tendency that could threaten the under.</t>
         </is>
       </c>
     </row>
@@ -15642,33 +15642,33 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.606</v>
+        <v>0.572</v>
       </c>
       <c r="F94" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I94" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="J94" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="K94" t="n">
-        <v>1.345</v>
+        <v>1.385</v>
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>Low scoring variance (σ=3.8) — highly predictable output near line — supports the UNDER. TS% shifts -9.1% in this matchup; FG% -14.4% trending (L10 vs L30). Opponent is below-average defense (#22) at above-average pace (#8). 8/10 signals agree — Volume, HR L30, HR L10, Trend support the UNDER; Defense, Pace dissent. Projection model targets 4.5 pts (4.0 pts below line; 60% blended confidence [T2]).</t>
+          <t>Low scoring variance (σ=3.8) — highly predictable output near line — marginally supports the UNDER. TS% shifts -9.1% in this matchup; FG% -14.4% trending (L10 vs L30). Opponent is below-average defense (#22) at above-average pace (#8). Mixed signals: 5/10 agree (HR L10, Trend, Context); counter-signals: Volume, HR L30, Defense. Projection model targets 4.6 pts (2.9 pts below line; 57% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
@@ -15709,10 +15709,10 @@
         <v>6.9</v>
       </c>
       <c r="J95" t="n">
-        <v>3.15</v>
+        <v>2.75</v>
       </c>
       <c r="K95" t="n">
-        <v>1.333</v>
+        <v>1.417</v>
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
@@ -15757,10 +15757,10 @@
         <v>7.7</v>
       </c>
       <c r="J96" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="K96" t="n">
-        <v>1.357</v>
+        <v>1.408</v>
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
@@ -15805,10 +15805,10 @@
         <v>2.8</v>
       </c>
       <c r="J97" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="K97" t="n">
-        <v>1.435</v>
+        <v>1.4</v>
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
@@ -15853,10 +15853,10 @@
         <v>7.7</v>
       </c>
       <c r="J98" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K98" t="n">
-        <v>1.357</v>
+        <v>1.364</v>
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
@@ -15901,10 +15901,10 @@
         <v>2</v>
       </c>
       <c r="J99" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="K99" t="n">
-        <v>1.345</v>
+        <v>1.364</v>
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
@@ -15997,10 +15997,10 @@
         <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>1.847</v>
+        <v>3</v>
       </c>
       <c r="K101" t="n">
-        <v>1.909</v>
+        <v>1.364</v>
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
@@ -16045,10 +16045,10 @@
         <v>0.7</v>
       </c>
       <c r="J102" t="n">
-        <v>1.8</v>
+        <v>3.15</v>
       </c>
       <c r="K102" t="n">
-        <v>1.971</v>
+        <v>1.333</v>
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
@@ -16093,10 +16093,10 @@
         <v>5.1</v>
       </c>
       <c r="J103" t="n">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="K103" t="n">
-        <v>1.357</v>
+        <v>1.4</v>
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
@@ -16141,10 +16141,10 @@
         <v>4.3</v>
       </c>
       <c r="J104" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="K104" t="n">
-        <v>1.417</v>
+        <v>1.455</v>
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
@@ -16189,10 +16189,10 @@
         <v>9.300000000000001</v>
       </c>
       <c r="J105" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="K105" t="n">
-        <v>1.4</v>
+        <v>1.417</v>
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
@@ -16237,10 +16237,10 @@
         <v>7.3</v>
       </c>
       <c r="J106" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="K106" t="n">
-        <v>1.345</v>
+        <v>1.435</v>
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
@@ -16285,10 +16285,10 @@
         <v>3.3</v>
       </c>
       <c r="J107" t="n">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="K107" t="n">
-        <v>1.455</v>
+        <v>1.385</v>
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
@@ -16333,10 +16333,10 @@
         <v>0.8</v>
       </c>
       <c r="J108" t="n">
-        <v>3.15</v>
+        <v>2.75</v>
       </c>
       <c r="K108" t="n">
-        <v>1.333</v>
+        <v>1.417</v>
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
@@ -16381,10 +16381,10 @@
         <v>4.2</v>
       </c>
       <c r="J109" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="K109" t="n">
-        <v>1.435</v>
+        <v>1.408</v>
       </c>
       <c r="L109" s="2" t="inlineStr">
         <is>
@@ -16429,10 +16429,10 @@
         <v>1.2</v>
       </c>
       <c r="J110" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="K110" t="n">
-        <v>1.435</v>
+        <v>1.408</v>
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
@@ -16477,10 +16477,10 @@
         <v>1.7</v>
       </c>
       <c r="J111" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="K111" t="n">
-        <v>1.385</v>
+        <v>1.364</v>
       </c>
       <c r="L111" s="2" t="inlineStr">
         <is>
@@ -16525,10 +16525,10 @@
         <v>1.2</v>
       </c>
       <c r="J112" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="K112" t="n">
-        <v>1.364</v>
+        <v>1.435</v>
       </c>
       <c r="L112" s="2" t="inlineStr">
         <is>
@@ -16621,10 +16621,10 @@
         <v>0.2</v>
       </c>
       <c r="J114" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="K114" t="n">
-        <v>1.408</v>
+        <v>1.435</v>
       </c>
       <c r="L114" s="2" t="inlineStr">
         <is>
@@ -16669,10 +16669,10 @@
         <v>0.6</v>
       </c>
       <c r="J115" t="n">
-        <v>3.1</v>
+        <v>2.65</v>
       </c>
       <c r="K115" t="n">
-        <v>1.345</v>
+        <v>1.455</v>
       </c>
       <c r="L115" s="2" t="inlineStr">
         <is>
@@ -16813,10 +16813,10 @@
         <v>2.3</v>
       </c>
       <c r="J118" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="K118" t="n">
-        <v>1.345</v>
+        <v>1.385</v>
       </c>
       <c r="L118" s="2" t="inlineStr">
         <is>
@@ -16909,10 +16909,10 @@
         <v>3.2</v>
       </c>
       <c r="J120" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="K120" t="n">
-        <v>1.4</v>
+        <v>1.385</v>
       </c>
       <c r="L120" s="2" t="inlineStr">
         <is>
@@ -16957,10 +16957,10 @@
         <v>5</v>
       </c>
       <c r="J121" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="K121" t="n">
-        <v>1.385</v>
+        <v>1.4</v>
       </c>
       <c r="L121" s="2" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         <v>1.9</v>
       </c>
       <c r="J122" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="K122" t="n">
-        <v>1.385</v>
+        <v>1.417</v>
       </c>
       <c r="L122" s="2" t="inlineStr">
         <is>
@@ -17149,10 +17149,10 @@
         <v>2.5</v>
       </c>
       <c r="J125" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="K125" t="n">
-        <v>1.952</v>
+        <v>1.87</v>
       </c>
       <c r="L125" s="2" t="inlineStr">
         <is>
@@ -17197,10 +17197,10 @@
         <v>6</v>
       </c>
       <c r="J126" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="K126" t="n">
-        <v>1.417</v>
+        <v>1.465</v>
       </c>
       <c r="L126" s="2" t="inlineStr">
         <is>
@@ -17245,10 +17245,10 @@
         <v>2.5</v>
       </c>
       <c r="J127" t="n">
-        <v>3.15</v>
+        <v>2.75</v>
       </c>
       <c r="K127" t="n">
-        <v>1.333</v>
+        <v>1.417</v>
       </c>
       <c r="L127" s="2" t="inlineStr">
         <is>
@@ -17293,10 +17293,10 @@
         <v>4.4</v>
       </c>
       <c r="J128" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="K128" t="n">
-        <v>1.385</v>
+        <v>1.364</v>
       </c>
       <c r="L128" s="2" t="inlineStr">
         <is>
@@ -17341,10 +17341,10 @@
         <v>0</v>
       </c>
       <c r="J129" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K129" t="n">
-        <v>1.364</v>
+        <v>1.357</v>
       </c>
       <c r="L129" s="2" t="inlineStr">
         <is>
@@ -17389,10 +17389,10 @@
         <v>8.9</v>
       </c>
       <c r="J130" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="K130" t="n">
-        <v>1.364</v>
+        <v>1.408</v>
       </c>
       <c r="L130" s="2" t="inlineStr">
         <is>
@@ -17437,10 +17437,10 @@
         <v>1.2</v>
       </c>
       <c r="J131" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="K131" t="n">
-        <v>1.435</v>
+        <v>1.357</v>
       </c>
       <c r="L131" s="2" t="inlineStr">
         <is>
@@ -17565,7 +17565,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Scottie Barnes</t>
+          <t>Jakob Poeltl</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -17575,17 +17575,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Derrick White</t>
+          <t>Ja'Kobe Walter</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -17599,13 +17599,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jakob Poeltl</t>
+          <t>Payton Pritchard</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -17619,13 +17619,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>9.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ja'Kobe Walter</t>
+          <t>Jaylen Brown</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -17639,13 +17639,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>9.5</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Payton Pritchard</t>
+          <t>Neemias Queta</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -17659,13 +17659,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Brandon Ingram</t>
+          <t>Jamal Shead</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -17675,17 +17675,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>LEAN UNDER</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>20.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RJ Barrett</t>
+          <t>Sam Hauser</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -17695,17 +17695,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LEAN UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>20.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Jaylen Brown</t>
+          <t>Scottie Barnes</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -17719,13 +17719,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>27.5</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Neemias Queta</t>
+          <t>Derrick White</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -17735,17 +17735,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>9.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Jayson Tatum</t>
+          <t>Brandon Ingram</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -17755,17 +17755,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>22.5</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Jamal Shead</t>
+          <t>RJ Barrett</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -17775,17 +17775,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>LEAN UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>7.5</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sandro Mamukelashvili</t>
+          <t>Jayson Tatum</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -17795,17 +17795,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>9.5</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sam Hauser</t>
+          <t>Sandro Mamukelashvili</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -17819,7 +17819,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="15">
@@ -17939,7 +17939,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="21">
@@ -17965,7 +17965,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Alex Sarr</t>
+          <t>Will Riley</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -17975,37 +17975,37 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Will Riley</t>
+          <t>Royce O'Neale</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>WAS @ BKN</t>
+          <t>PHX @ CHI</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>16.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Royce O'Neale</t>
+          <t>Mark Williams</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -18015,11 +18015,11 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="25">
@@ -18259,7 +18259,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="37">
@@ -18559,7 +18559,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="52">
@@ -18859,7 +18859,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>25.5</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="67">
@@ -18879,7 +18879,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="68">
@@ -19125,7 +19125,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Kyle Filipowski</t>
+          <t>Alex Caruso</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -19139,13 +19139,13 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>15.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Alex Caruso</t>
+          <t>Jared McCain</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -19155,17 +19155,17 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>5.5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Ace Bailey</t>
+          <t>Cody Williams</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -19179,13 +19179,13 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Jared McCain</t>
+          <t>John Konchar</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -19199,13 +19199,13 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Cody Williams</t>
+          <t>Jalen Williams</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -19215,17 +19215,17 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Chet Holmgren</t>
+          <t>Luguentz Dort</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -19235,17 +19235,17 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>15.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Shai Gilgeous-Alexander</t>
+          <t>Kyle Filipowski</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -19259,13 +19259,13 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>29.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Isaiah Joe</t>
+          <t>Ace Bailey</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -19275,17 +19275,17 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>8.5</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>John Konchar</t>
+          <t>Chet Holmgren</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -19295,17 +19295,17 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>6.5</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Jalen Williams</t>
+          <t>Shai Gilgeous-Alexander</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>16.5</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Luguentz Dort</t>
+          <t>Isaiah Joe</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -19335,11 +19335,11 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="91">
@@ -19399,7 +19399,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="94">
@@ -19419,7 +19419,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="95">

--- a/daily/2026-04-05.xlsx
+++ b/daily/2026-04-05.xlsx
@@ -32,7 +32,7 @@
       <color rgb="00E0E0E0"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +42,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001E1E2E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0022C55E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EF4444"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F59E0B"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,7 +72,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -65,6 +80,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -857,7 +875,7 @@
         <v>53</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>4.1</v>
@@ -1366,7 +1384,6 @@
       <c r="V11" t="n">
         <v>24</v>
       </c>
-      <c r="W11" t="inlineStr"/>
       <c r="X11" t="n">
         <v>10</v>
       </c>
@@ -1690,7 +1707,6 @@
       <c r="V15" t="n">
         <v>30</v>
       </c>
-      <c r="W15" t="inlineStr"/>
       <c r="X15" t="n">
         <v>2.1</v>
       </c>
@@ -2096,7 +2112,6 @@
       <c r="V20" t="n">
         <v>11</v>
       </c>
-      <c r="W20" t="inlineStr"/>
       <c r="X20" t="n">
         <v>38.9</v>
       </c>
@@ -2256,7 +2271,6 @@
       <c r="V22" t="n">
         <v>30</v>
       </c>
-      <c r="W22" t="inlineStr"/>
       <c r="X22" t="n">
         <v>3.5</v>
       </c>
@@ -2498,7 +2512,6 @@
       <c r="V25" t="n">
         <v>22</v>
       </c>
-      <c r="W25" t="inlineStr"/>
       <c r="X25" t="n">
         <v>0.4</v>
       </c>
@@ -2576,7 +2589,6 @@
       <c r="V26" t="n">
         <v>22</v>
       </c>
-      <c r="W26" t="inlineStr"/>
       <c r="X26" t="n">
         <v>14</v>
       </c>
@@ -2654,7 +2666,6 @@
       <c r="V27" t="n">
         <v>1</v>
       </c>
-      <c r="W27" t="inlineStr"/>
       <c r="X27" t="n">
         <v>0.3</v>
       </c>
@@ -2732,7 +2743,6 @@
       <c r="V28" t="n">
         <v>1</v>
       </c>
-      <c r="W28" t="inlineStr"/>
       <c r="X28" t="n">
         <v>-24.6</v>
       </c>
@@ -2892,7 +2902,6 @@
       <c r="V30" t="n">
         <v>1</v>
       </c>
-      <c r="W30" t="inlineStr"/>
       <c r="X30" t="n">
         <v>33.5</v>
       </c>
@@ -3134,7 +3143,6 @@
       <c r="V33" t="n">
         <v>22</v>
       </c>
-      <c r="W33" t="inlineStr"/>
       <c r="X33" t="n">
         <v>-0.9</v>
       </c>
@@ -3212,7 +3220,6 @@
       <c r="V34" t="n">
         <v>1</v>
       </c>
-      <c r="W34" t="inlineStr"/>
       <c r="X34" t="n">
         <v>-14.3</v>
       </c>
@@ -3372,7 +3379,6 @@
       <c r="V36" t="n">
         <v>14</v>
       </c>
-      <c r="W36" t="inlineStr"/>
       <c r="X36" t="n">
         <v>0</v>
       </c>
@@ -3450,7 +3456,6 @@
       <c r="V37" t="n">
         <v>14</v>
       </c>
-      <c r="W37" t="inlineStr"/>
       <c r="X37" t="n">
         <v>2.3</v>
       </c>
@@ -3528,7 +3533,6 @@
       <c r="V38" t="n">
         <v>6</v>
       </c>
-      <c r="W38" t="inlineStr"/>
       <c r="X38" t="n">
         <v>-6.7</v>
       </c>
@@ -3688,7 +3692,6 @@
       <c r="V40" t="n">
         <v>14</v>
       </c>
-      <c r="W40" t="inlineStr"/>
       <c r="X40" t="n">
         <v>0</v>
       </c>
@@ -3766,7 +3769,6 @@
       <c r="V41" t="n">
         <v>6</v>
       </c>
-      <c r="W41" t="inlineStr"/>
       <c r="X41" t="n">
         <v>2.7</v>
       </c>
@@ -4008,7 +4010,6 @@
       <c r="V44" t="n">
         <v>10</v>
       </c>
-      <c r="W44" t="inlineStr"/>
       <c r="X44" t="n">
         <v>-0.9</v>
       </c>
@@ -4086,7 +4087,6 @@
       <c r="V45" t="n">
         <v>12</v>
       </c>
-      <c r="W45" t="inlineStr"/>
       <c r="X45" t="n">
         <v>-18.1</v>
       </c>
@@ -4492,7 +4492,6 @@
       <c r="V50" t="n">
         <v>10</v>
       </c>
-      <c r="W50" t="inlineStr"/>
       <c r="X50" t="n">
         <v>36.1</v>
       </c>
@@ -4734,7 +4733,6 @@
       <c r="V53" t="n">
         <v>12</v>
       </c>
-      <c r="W53" t="inlineStr"/>
       <c r="X53" t="n">
         <v>11.4</v>
       </c>
@@ -4812,7 +4810,6 @@
       <c r="V54" t="n">
         <v>12</v>
       </c>
-      <c r="W54" t="inlineStr"/>
       <c r="X54" t="n">
         <v>-5.9</v>
       </c>
@@ -4890,7 +4887,6 @@
       <c r="V55" t="n">
         <v>16</v>
       </c>
-      <c r="W55" t="inlineStr"/>
       <c r="X55" t="n">
         <v>4.2</v>
       </c>
@@ -5460,7 +5456,6 @@
       <c r="V62" t="n">
         <v>21</v>
       </c>
-      <c r="W62" t="inlineStr"/>
       <c r="X62" t="n">
         <v>4.7</v>
       </c>
@@ -5620,7 +5615,6 @@
       <c r="V64" t="n">
         <v>16</v>
       </c>
-      <c r="W64" t="inlineStr"/>
       <c r="X64" t="n">
         <v>-11.2</v>
       </c>
@@ -5780,7 +5774,6 @@
       <c r="V66" t="n">
         <v>21</v>
       </c>
-      <c r="W66" t="inlineStr"/>
       <c r="X66" t="n">
         <v>6.3</v>
       </c>
@@ -5858,7 +5851,6 @@
       <c r="V67" t="n">
         <v>16</v>
       </c>
-      <c r="W67" t="inlineStr"/>
       <c r="X67" t="n">
         <v>-39.1</v>
       </c>
@@ -5936,7 +5928,6 @@
       <c r="V68" t="n">
         <v>5</v>
       </c>
-      <c r="W68" t="inlineStr"/>
       <c r="X68" t="n">
         <v>10.6</v>
       </c>
@@ -6014,7 +6005,6 @@
       <c r="V69" t="n">
         <v>29</v>
       </c>
-      <c r="W69" t="inlineStr"/>
       <c r="X69" t="n">
         <v>1.8</v>
       </c>
@@ -6092,7 +6082,6 @@
       <c r="V70" t="n">
         <v>29</v>
       </c>
-      <c r="W70" t="inlineStr"/>
       <c r="X70" t="n">
         <v>0</v>
       </c>
@@ -6170,7 +6159,6 @@
       <c r="V71" t="n">
         <v>29</v>
       </c>
-      <c r="W71" t="inlineStr"/>
       <c r="X71" t="n">
         <v>0</v>
       </c>
@@ -6330,7 +6318,6 @@
       <c r="V73" t="n">
         <v>29</v>
       </c>
-      <c r="W73" t="inlineStr"/>
       <c r="X73" t="n">
         <v>-0.9</v>
       </c>
@@ -6408,7 +6395,6 @@
       <c r="V74" t="n">
         <v>5</v>
       </c>
-      <c r="W74" t="inlineStr"/>
       <c r="X74" t="n">
         <v>20.2</v>
       </c>
@@ -6486,7 +6472,6 @@
       <c r="V75" t="n">
         <v>5</v>
       </c>
-      <c r="W75" t="inlineStr"/>
       <c r="X75" t="n">
         <v>-16.8</v>
       </c>
@@ -6564,7 +6549,6 @@
       <c r="V76" t="n">
         <v>29</v>
       </c>
-      <c r="W76" t="inlineStr"/>
       <c r="X76" t="n">
         <v>0</v>
       </c>
@@ -6724,7 +6708,6 @@
       <c r="V78" t="n">
         <v>5</v>
       </c>
-      <c r="W78" t="inlineStr"/>
       <c r="X78" t="n">
         <v>10</v>
       </c>
@@ -6802,7 +6785,6 @@
       <c r="V79" t="n">
         <v>5</v>
       </c>
-      <c r="W79" t="inlineStr"/>
       <c r="X79" t="n">
         <v>-7.7</v>
       </c>
@@ -6962,7 +6944,6 @@
       <c r="V81" t="n">
         <v>8</v>
       </c>
-      <c r="W81" t="inlineStr"/>
       <c r="X81" t="n">
         <v>0</v>
       </c>
@@ -8188,7 +8169,6 @@
       <c r="V96" t="n">
         <v>20</v>
       </c>
-      <c r="W96" t="inlineStr"/>
       <c r="X96" t="n">
         <v>-9.5</v>
       </c>
@@ -9004,7 +8984,6 @@
       <c r="V106" t="n">
         <v>2</v>
       </c>
-      <c r="W106" t="inlineStr"/>
       <c r="X106" t="n">
         <v>-44.6</v>
       </c>
@@ -9984,7 +9963,6 @@
       <c r="V118" t="n">
         <v>15</v>
       </c>
-      <c r="W118" t="inlineStr"/>
       <c r="X118" t="n">
         <v>-9.9</v>
       </c>
@@ -10226,7 +10204,6 @@
       <c r="V121" t="n">
         <v>19</v>
       </c>
-      <c r="W121" t="inlineStr"/>
       <c r="X121" t="n">
         <v>14.5</v>
       </c>
@@ -10960,7 +10937,6 @@
       <c r="V130" t="n">
         <v>19</v>
       </c>
-      <c r="W130" t="inlineStr"/>
       <c r="X130" t="n">
         <v>2.5</v>
       </c>
@@ -17563,2623 +17539,5909 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Jakob Poeltl</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>TOR @ BOS</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="3" t="n">
         <v>9.5</v>
       </c>
+      <c r="E2" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Poeltl scored 14 pts vs 9.5 line (+4.5), OVER hit by 4.5 pts. Poeltl played 20 min (-5.9 vs L10 avg of 26.0) — 23% less than expected. Shooting efficiency was hot: 77.8% FG (+14.4% vs L10 avg of 63.4%). 7/9 from the field. Signals that called it correctly: Volume, HR L10, Trend, Context, H2H (6/10 aligned). Counter-signals that were wrong: HR L30, Defense, Pace. Projection model targeted 14.2 pts — actual 14 was 0.2 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Poeltl in this role.</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Ja'Kobe Walter</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>TOR @ BOS</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E3" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Walter scored 16 pts vs 9.5 line (+6.5), UNDER missed by 6.5 pts. Walter played 32 min (+5.8 vs L10 avg of 26.2) — 22% more than expected. Shooting efficiency was hot: 66.7% FG (+11.9% vs L10 avg of 54.8%). 6/9 from the field. Counter-signals that proved correct: HR L10, Trend, FG Trend, Min Trend. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 7.4 pts — actual 16 was 8.6 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Payton Pritchard</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>TOR @ BOS</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E4" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Pritchard scored 17 pts vs 15.5 line (+1.5), OVER hit by 1.5 pts. Minutes were as expected: 30 played vs L10 avg 31.5. Shooting efficiency was hot: 58.3% FG (+9.8% vs L10 avg of 48.5%). 7/12 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (7/10 aligned). Counter-signals that were wrong: Defense, Pace, Min Trend. Projection model targeted 21.9 pts — actual 17 was 4.9 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms Pritchard's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Jaylen Brown</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>TOR @ BOS</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="3" t="n">
         <v>27.5</v>
       </c>
+      <c r="E5" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Brown scored 26 pts vs 27.5 line (-1.5), UNDER hit by 1.5 pts. Minutes were as expected: 35 played vs L10 avg 36.5. Shooting efficiency was hot: 55.0% FG (+9.7% vs L10 avg of 45.3%). 11/20 from the field. Signals that called it correctly: Context, Defense, H2H, Pace, FG Trend (5/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 21.4 pts — actual 26 was 4.6 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms Brown's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Neemias Queta</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>TOR @ BOS</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="3" t="n">
         <v>9.5</v>
       </c>
+      <c r="E6" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Queta scored 18 pts vs 9.5 line (+8.5), OVER hit by 8.5 pts. Queta played 34 min (+5.4 vs L10 avg of 28.5) — 19% more than expected. Shooting efficiency was hot: 90.0% FG (+19.1% vs L10 avg of 70.9%). 9/10 from the field. Signals that called it correctly: Volume, HR L10, Trend, Context, FG Trend (6/10 aligned). Counter-signals that were wrong: HR L30, Defense, H2H. Projection model targeted 12.2 pts — actual 18 was 5.8 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Queta's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Jamal Shead</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>TOR @ BOS</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>LEAN UNDER</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="3" t="n">
         <v>7.5</v>
       </c>
+      <c r="E7" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Shead scored 7 pts vs 7.5 line (-0.5), UNDER hit by 0.5 pts. Minutes were as expected: 26 played vs L10 avg 25.8. Shooting efficiency was cold: 25.0% FG (-9.3% vs L10 avg of 34.3%). 2/8 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, Defense (6/10 aligned). Counter-signals that were wrong: Trend, H2H, FG Trend. Projection model targeted 7.5 pts — actual 7 was 0.5 pts close (wrong direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Shead in this role.</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Sam Hauser</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>TOR @ BOS</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="3" t="n">
         <v>7.5</v>
       </c>
+      <c r="E8" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Hauser scored 8 pts vs 7.5 line (+0.5), OVER hit by 0.5 pts. Minutes were as expected: 26 played vs L10 avg 25.1. Shooting was in line with averages: 42.9% FG (3/7, L10 avg 43.7%). Signals that called it correctly: Volume, HR L30, Trend, Context, H2H (6/10 aligned). Counter-signals that were wrong: HR L10, Defense, Pace. Projection model targeted 10.3 pts — actual 8 was 2.3 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms Hauser's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Scottie Barnes</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>TOR @ BOS</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="3" t="n">
         <v>16.5</v>
       </c>
+      <c r="E9" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Barnes scored 10 pts vs 16.5 line (-6.5), UNDER hit by 6.5 pts. Minutes were as expected: 32 played vs L10 avg 29.8. Shooting efficiency was cold: 35.7% FG (-21.0% vs L10 avg of 56.7%). 5/14 from the field. Signals that called it correctly: Volume, HR L30, Trend, Context, Defense (7/10 aligned). Counter-signals that were wrong: HR L10, H2H, FG Trend. Projection model targeted 14.6 pts — actual 10 was 4.6 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Barnes's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Derrick White</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>TOR @ BOS</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E10" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>WIN — White scored 10 pts vs 15.5 line (-5.5), UNDER hit by 5.5 pts. Minutes were as expected: 35 played vs L10 avg 33.6. Shooting efficiency was hot: 57.1% FG (+15.9% vs L10 avg of 41.2%). 4/7 from the field. Signals that called it correctly: HR L30, HR L10, Trend, Context, Defense (7/10 aligned). Counter-signals that were wrong: Volume, H2H, FG Trend. Projection model targeted 14.7 pts — actual 10 was 4.7 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms White's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Brandon Ingram</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>TOR @ BOS</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="4" t="n">
         <v>20.5</v>
       </c>
+      <c r="E11" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Ingram scored 15 pts vs 20.5 line (-5.5), OVER missed by 5.5 pts. Minutes were as expected: 34 played vs L10 avg 33.1. Shooting efficiency was cold: 46.2% FG (-5.1% vs L10 avg of 51.3%). 6/13 from the field. Counter-signals that proved correct: HR L30, HR L10, Trend, Defense. Signals that were wrong: Volume, Context, FG Trend. Projection model targeted 23.4 pts — actual 15 was 8.4 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>RJ Barrett</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>TOR @ BOS</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="4" t="n">
         <v>19.5</v>
       </c>
+      <c r="E12" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Barrett scored 15 pts vs 19.5 line (-4.5), OVER missed by 4.5 pts. Barrett played 35 min (+5.9 vs L10 avg of 29.5) — 20% more than expected. Shooting efficiency was cold: 35.3% FG (-16.6% vs L10 avg of 51.9%). 6/17 from the field. Counter-signals that proved correct: Volume, Defense, Pace, Min Trend. Signals that were wrong: HR L30, HR L10, Trend. Projection model targeted 20.2 pts — actual 15 was 5.2 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Jayson Tatum</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>TOR @ BOS</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="4" t="n">
         <v>22.5</v>
       </c>
+      <c r="E13" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Tatum scored 23 pts vs 22.5 line (+0.5), UNDER missed by 0.5 pts. Minutes were as expected: 34 played vs L10 avg 32.8. Shooting efficiency was hot: 46.7% FG (+5.6% vs L10 avg of 41.1%). 7/15 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Trend. Signals that were wrong: Defense, H2H, Pace. Projection model targeted 17.6 pts — actual 23 was 5.4 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Sandro Mamukelashvili</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>TOR @ BOS</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="3" t="n">
         <v>9.5</v>
       </c>
+      <c r="E14" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Mamukelashvili scored 10 pts vs 9.5 line (+0.5), OVER hit by 0.5 pts. Minutes were as expected: 24 played vs L10 avg 22.0. Shooting efficiency was cold: 50.0% FG (-9.9% vs L10 avg of 59.9%). 2/4 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (8/10 aligned). Counter-signals that were wrong: Defense, Pace. Projection model targeted 15.5 pts — actual 10 was 5.5 pts off (correct direction). Result classification: CLOSE_CALL. Note: Strong signal alignment (8/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Tre Johnson</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>WAS @ BKN</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="5" t="n">
         <v>12.5</v>
       </c>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="inlineStr"/>
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>Terance Mann</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>WAS @ BKN</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="5" t="n">
         <v>8.5</v>
       </c>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="inlineStr"/>
+      <c r="I16" s="5" t="n"/>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>Noah Clowney</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>WAS @ BKN</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="5" t="n">
         <v>11.5</v>
       </c>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="inlineStr"/>
+      <c r="I17" s="5" t="n"/>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Drake Powell</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>WAS @ BKN</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="4" t="n">
         <v>10.5</v>
       </c>
+      <c r="E18" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Powell scored 13 pts vs 10.5 line (+2.5), UNDER missed by 2.5 pts. Powell played 29 min (+3.4 vs L10 avg of 26.0) — 13% more than expected. Shooting efficiency was hot: 50.0% FG (+11.6% vs L10 avg of 38.4%). 5/10 from the field. Counter-signals that proved correct: Trend, Defense, Pace, FG Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 8.3 pts — actual 13 was 4.7 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>Bilal Coulibaly</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>WAS @ BKN</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="5" t="n">
         <v>11.5</v>
       </c>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="inlineStr"/>
+      <c r="I19" s="5" t="n"/>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Nolan Traore</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>WAS @ BKN</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="4" t="n">
         <v>13.5</v>
       </c>
+      <c r="E20" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Traore scored 23 pts vs 13.5 line (+9.5), UNDER missed by 9.5 pts. Traore played 28 min (+4.8 vs L10 avg of 23.4) — 21% more than expected. Shooting efficiency was hot: 38.9% FG (+8.0% vs L10 avg of 30.9%). 7/18 from the field. Counter-signals that proved correct: Defense, H2H, Pace. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 11.6 pts — actual 23 was 11.4 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>Josh Minott</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>WAS @ BKN</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="3" t="n">
         <v>14.5</v>
       </c>
+      <c r="E21" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Minott scored 15 pts vs 14.5 line (+0.5), OVER hit by 0.5 pts. Minott played 18 min (-5.2 vs L10 avg of 23.5) — 22% less than expected. Shooting was in line with averages: 54.5% FG (6/11, L10 avg 49.9%). Signals that called it correctly: Trend, Defense, Pace, FG Trend, Min Trend (5/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 14.8 pts — actual 15 was 0.2 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Minott in this role.</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>Will Riley</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>WAS @ BKN</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="3" t="n">
         <v>16.5</v>
       </c>
+      <c r="E22" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Riley scored 30 pts vs 16.5 line (+13.5), OVER hit by 13.5 pts. Riley played 35 min (+3.5 vs L10 avg of 31.6) — 11% more than expected. Shooting efficiency was hot: 56.2% FG (+5.4% vs L10 avg of 50.8%). 9/16 from the field. Signals that called it correctly: HR L30, HR L10, Trend, Context, Defense (7/10 aligned). Counter-signals that were wrong: Volume, H2H, Pace. Projection model targeted 22.8 pts — actual 30 was 7.2 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Riley's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>Royce O'Neale</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>PHX @ CHI</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="3" t="n">
         <v>7.5</v>
       </c>
+      <c r="E23" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>WIN — O'Neale scored 3 pts vs 7.5 line (-4.5), UNDER hit by 4.5 pts. O'Neale played 22 min (-3.9 vs L10 avg of 25.8) — 15% less than expected. Shooting was in line with averages: 50.0% FG (1/2, L10 avg 47.2%). Signals that called it correctly: H2H, Min Trend (2/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 2.4 pts — actual 3 was 0.6 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for O'Neale in this role.</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>Mark Williams</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>PHX @ CHI</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" s="3" t="n">
         <v>8.5</v>
       </c>
+      <c r="E24" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Williams scored 14 pts vs 8.5 line (+5.5), OVER hit by 5.5 pts. Williams played 26 min (+4.6 vs L10 avg of 21.1) — 22% more than expected. Shooting efficiency was hot: 75.0% FG (+21.9% vs L10 avg of 53.1%). 6/8 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, Defense (7/10 aligned). Counter-signals that were wrong: Trend, FG Trend, Min Trend. Projection model targeted 13.2 pts — actual 14 was 0.8 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Williams in this role.</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>Isaac Okoro</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>PHX @ CHI</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E25" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Okoro scored 10 pts vs 9.5 line (+0.5), UNDER missed by 0.5 pts. Okoro played 36 min (+7.9 vs L10 avg of 28.6) — 28% more than expected. Shooting was in line with averages: 50.0% FG (5/10, L10 avg 45.1%). Counter-signals that proved correct: Volume, Trend, H2H, FG Trend. Signals that were wrong: HR L30, HR L10, Context. Projection model targeted 8.5 pts — actual 10 was 1.5 pts close (correct direction). Loss classification: CLOSE_CALL. Note: Within 2 pts — direction was sound. Small execution variance, no model adjustment needed.</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>Josh Giddey</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>PHX @ CHI</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" s="5" t="n">
         <v>16.5</v>
       </c>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="inlineStr"/>
+      <c r="I26" s="5" t="n"/>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>Dillon Brooks</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>PHX @ CHI</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="D27" s="3" t="n">
         <v>16.5</v>
       </c>
+      <c r="E27" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Brooks scored 15 pts vs 16.5 line (-1.5), UNDER hit by 1.5 pts. Brooks played 34 min (+6.1 vs L10 avg of 27.4) — 22% more than expected. Shooting was in line with averages: 40.0% FG (6/15, L10 avg 39.8%). Signals that called it correctly: Trend, FG Trend, Min Trend (3/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 13.9 pts — actual 15 was 1.1 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Brooks in this role.</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>Collin Gillespie</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>PHX @ CHI</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="D28" s="3" t="n">
         <v>10.5</v>
       </c>
+      <c r="E28" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Gillespie scored 9 pts vs 10.5 line (-1.5), UNDER hit by 1.5 pts. Gillespie played 24 min (-4.5 vs L10 avg of 28.7) — 16% less than expected. Shooting efficiency was cold: 27.3% FG (-7.7% vs L10 avg of 35.0%). 3/11 from the field. Signals that called it correctly: Trend, FG Trend, Min Trend (3/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 4.1 pts — actual 9 was 4.9 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms Gillespie's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>Jalen Green</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>PHX @ CHI</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" s="4" t="n">
         <v>18.5</v>
       </c>
+      <c r="E29" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Green scored 25 pts vs 18.5 line (+6.5), UNDER missed by 6.5 pts. Green played 36 min (+7.3 vs L10 avg of 28.9) — 25% more than expected. Shooting efficiency was hot: 52.4% FG (+8.7% vs L10 avg of 43.7%). 11/21 from the field. Counter-signals that proved correct: HR L30, HR L10, Trend, Defense. Signals that were wrong: Volume, Context. Projection model targeted 17.5 pts — actual 25 was 7.5 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>Oso Ighodaro</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>PHX @ CHI</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="D30" s="4" t="n">
         <v>7.5</v>
       </c>
+      <c r="E30" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Ighodaro scored 6 pts vs 7.5 line (-1.5), OVER missed by 1.5 pts. Ighodaro played 22 min (-8.3 vs L10 avg of 30.6) — 27% less than expected. Shooting efficiency was hot: 100.0% FG (+29.5% vs L10 avg of 70.5%). 3/3 from the field. Counter-signals that proved correct: H2H. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 9.8 pts — actual 6 was 3.8 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Ighodaro for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>Devin Booker</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>PHX @ CHI</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" s="3" t="n">
         <v>27.5</v>
       </c>
+      <c r="E31" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Booker scored 30 pts vs 27.5 line (+2.5), OVER hit by 2.5 pts. Minutes were as expected: 36 played vs L10 avg 33.1. Shooting efficiency was cold: 40.9% FG (-6.6% vs L10 avg of 47.5%). 9/22 from the field. Signals that called it correctly: Trend, Defense, H2H, Pace, FG Trend (6/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 32.2 pts — actual 30 was 2.2 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Booker's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>Tre Jones</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>PHX @ CHI</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D32" t="n">
+      <c r="D32" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E32" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Jones scored 29 pts vs 15.5 line (+13.5), OVER hit by 13.5 pts. Jones played 31 min (+3.9 vs L10 avg of 27.2) — 14% more than expected. Shooting was in line with averages: 60.0% FG (12/20, L10 avg 57.8%). Signals that called it correctly: Trend, Context, FG Trend (3/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 16.4 pts — actual 29 was 12.6 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Jones's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>Matas Buzelis</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>PHX @ CHI</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D33" t="n">
+      <c r="D33" s="5" t="n">
         <v>17.5</v>
       </c>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="n"/>
+      <c r="H33" s="5" t="inlineStr"/>
+      <c r="I33" s="5" t="n"/>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>Grayson Allen</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>PHX @ CHI</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D34" t="n">
+      <c r="D34" s="4" t="n">
         <v>13.5</v>
       </c>
+      <c r="E34" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Allen scored 6 pts vs 13.5 line (-7.5), OVER missed by 7.5 pts. Allen played 16 min (-10.2 vs L10 avg of 26.4) — 39% less than expected. Shooting efficiency was hot: 50.0% FG (+9.8% vs L10 avg of 40.2%). 1/2 from the field. Counter-signals that proved correct: HR L10, Trend, H2H, Min Trend. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 13.6 pts — actual 6 was 7.6 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Allen for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>Ryan Rollins</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>MEM @ MIL</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D35" t="n">
+      <c r="D35" s="4" t="n">
         <v>22.5</v>
       </c>
+      <c r="E35" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Rollins scored 24 pts vs 22.5 line (+1.5), UNDER missed by 1.5 pts. Minutes were as expected: 32 played vs L10 avg 31.0. Shooting efficiency was hot: 62.5% FG (+9.2% vs L10 avg of 53.3%). 10/16 from the field. Counter-signals that proved correct: Trend, Defense, Pace, FG Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 10.8 pts — actual 24 was 13.2 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>Walter Clayton Jr.</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>MEM @ MIL</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D36" t="n">
+      <c r="D36" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E36" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Jr. scored 20 pts vs 12.5 line (+7.5), UNDER missed by 7.5 pts. Minutes were as expected: 25 played vs L10 avg 25.0. Shooting efficiency was hot: 54.5% FG (+20.0% vs L10 avg of 34.5%). 6/11 from the field. Counter-signals that proved correct: Trend, Defense, H2H, Pace. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 7.5 pts — actual 20 was 12.5 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>Olivier-Maxence Prosper</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>MEM @ MIL</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D37" t="n">
+      <c r="D37" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E37" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Prosper scored 13 pts vs 15.5 line (-2.5), UNDER hit by 2.5 pts. Prosper played 14 min (-10.3 vs L10 avg of 24.6) — 42% less than expected. Shooting was in line with averages: 50.0% FG (5/10, L10 avg 54.8%). Signals that called it correctly: Volume, HR L30, Context (3/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 11.9 pts — actual 13 was 1.1 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Prosper in this role.</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>Taurean Prince</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>MEM @ MIL</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D38" t="n">
+      <c r="D38" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E38" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Prince scored 19 pts vs 9.5 line (+9.5), UNDER missed by 9.5 pts. Minutes were as expected: 24 played vs L10 avg 24.4. Shooting efficiency was hot: 87.5% FG (+42.7% vs L10 avg of 44.8%). 7/8 from the field. Counter-signals that proved correct: Trend, Defense, H2H, Pace. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 8.4 pts — actual 19 was 10.6 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>Myles Turner</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>MEM @ MIL</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D39" t="n">
+      <c r="D39" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E39" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Turner scored 19 pts vs 12.5 line (+6.5), UNDER missed by 6.5 pts. Minutes were as expected: 22 played vs L10 avg 24.1. Shooting was in line with averages: 46.2% FG (6/13, L10 avg 41.5%). Counter-signals that proved correct: Defense, Pace. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 8.9 pts — actual 19 was 10.1 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>Taylor Hendricks</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>MEM @ MIL</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D40" t="n">
+      <c r="D40" s="3" t="n">
         <v>11.5</v>
       </c>
+      <c r="E40" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Hendricks scored 11 pts vs 11.5 line (-0.5), UNDER hit by 0.5 pts. Hendricks played 12 min (-13.1 vs L10 avg of 25.6) — 51% less than expected. Shooting efficiency was hot: 75.0% FG (+35.5% vs L10 avg of 39.5%). 3/4 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (6/10 aligned). Counter-signals that were wrong: Defense, H2H, Pace. Projection model targeted 7.3 pts — actual 11 was 3.7 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms Hendricks's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>Kyle Kuzma</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>MEM @ MIL</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D41" t="n">
+      <c r="D41" s="3" t="n">
         <v>14.5</v>
       </c>
+      <c r="E41" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Kuzma scored 4 pts vs 14.5 line (-10.5), UNDER hit by 10.5 pts. Kuzma played 22 min (-3.1 vs L10 avg of 25.5) — 12% less than expected. Shooting efficiency was hot: 66.7% FG (+20.1% vs L10 avg of 46.6%). 2/3 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (7/10 aligned). Counter-signals that were wrong: Defense, H2H, Pace. Projection model targeted 11.1 pts — actual 4 was 7.1 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Kuzma's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>Ousmane Dieng</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>MEM @ MIL</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D42" t="n">
+      <c r="D42" s="4" t="n">
         <v>14.5</v>
       </c>
+      <c r="E42" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Dieng scored 17 pts vs 14.5 line (+2.5), UNDER missed by 2.5 pts. Minutes were as expected: 31 played vs L10 avg 30.3. Shooting was in line with averages: 40.0% FG (6/15, L10 avg 44.2%). Counter-signals that proved correct: Trend, Defense, Pace, FG Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 7.9 pts — actual 17 was 9.1 pts off (correct direction). Loss classification: MODEL_FAILURE. Note: Model signals were misleading for this matchup — review Dieng's recent role and usage for pattern shifts.</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>Nae'Qwan Tomlin</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>IND @ CLE</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D43" t="n">
+      <c r="D43" s="3" t="n">
         <v>8.5</v>
       </c>
+      <c r="E43" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Tomlin scored 3 pts vs 8.5 line (-5.5), UNDER hit by 5.5 pts. Minutes were as expected: 13 played vs L10 avg 10.9. Shooting efficiency was hot: 50.0% FG (+11.5% vs L10 avg of 38.5%). 1/2 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (6/10 aligned). Counter-signals that were wrong: Defense, H2H, Pace. Projection model targeted 6.4 pts — actual 3 was 3.4 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Tomlin's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>Quenton Jackson</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>IND @ CLE</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D44" t="n">
+      <c r="D44" s="3" t="n">
         <v>12.5</v>
       </c>
+      <c r="E44" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Jackson scored 15 pts vs 12.5 line (+2.5), OVER hit by 2.5 pts. Jackson played 29 min (+12.0 vs L10 avg of 16.9) — 71% more than expected. Shooting efficiency was cold: 35.7% FG (-12.5% vs L10 avg of 48.2%). 5/14 from the field. Signals that called it correctly: Pace, FG Trend (2/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 16.9 pts — actual 15 was 1.9 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Jackson in this role.</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>Thomas Bryant</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>IND @ CLE</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D45" t="n">
+      <c r="D45" s="4" t="n">
         <v>13.5</v>
       </c>
+      <c r="E45" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Bryant scored 14 pts vs 13.5 line (+0.5), UNDER missed by 0.5 pts. Bryant played 26 min (+10.9 vs L10 avg of 15.3) — 71% more than expected. Shooting efficiency was hot: 66.7% FG (+9.7% vs L10 avg of 57.0%). 6/9 from the field. Counter-signals that proved correct: Defense, H2H, Pace, FG Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 2.3 pts — actual 14 was 11.7 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>Donovan Mitchell</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>IND @ CLE</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D46" t="n">
+      <c r="D46" s="3" t="n">
         <v>27.5</v>
       </c>
+      <c r="E46" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Mitchell scored 38 pts vs 27.5 line (+10.5), OVER hit by 10.5 pts. Minutes were as expected: 33 played vs L10 avg 33.4. Shooting efficiency was hot: 59.3% FG (+14.1% vs L10 avg of 45.2%). 16/27 from the field. Signals that called it correctly: Defense, H2H, Pace, FG Trend, Min Trend (5/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 28.0 pts — actual 38 was 10.0 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Mitchell's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>Obi Toppin</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>IND @ CLE</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D47" t="n">
+      <c r="D47" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E47" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Toppin scored 21 pts vs 9.5 line (+11.5), UNDER missed by 11.5 pts. Toppin played 24 min (+6.1 vs L10 avg of 17.4) — 35% more than expected. Shooting efficiency was cold: 40.0% FG (-17.8% vs L10 avg of 57.8%). 4/10 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Trend. Signals that were wrong: Min Trend. Projection model targeted 9.1 pts — actual 21 was 11.9 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="4" t="inlineStr">
         <is>
           <t>Keon Ellis</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>IND @ CLE</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D48" t="n">
+      <c r="D48" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E48" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Ellis scored 13 pts vs 9.5 line (+3.5), UNDER missed by 3.5 pts. Ellis played 33 min (+7.3 vs L10 avg of 26.0) — 28% more than expected. Shooting was in line with averages: 55.6% FG (5/9, L10 avg 51.4%). Counter-signals that proved correct: Trend, Defense, Pace, FG Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 6.2 pts — actual 13 was 6.8 pts off (correct direction). Loss classification: MODEL_FAILURE. Note: Model signals were misleading for this matchup — review Ellis's recent role and usage for pattern shifts.</t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>Jarace Walker</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="5" t="inlineStr">
         <is>
           <t>IND @ CLE</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D49" t="n">
+      <c r="D49" s="5" t="n">
         <v>15.5</v>
       </c>
+      <c r="E49" s="5" t="n"/>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="n"/>
+      <c r="H49" s="5" t="inlineStr"/>
+      <c r="I49" s="5" t="n"/>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>Kobe Brown</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t>IND @ CLE</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D50" t="n">
+      <c r="D50" s="3" t="n">
         <v>11.5</v>
       </c>
+      <c r="E50" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Brown scored 11 pts vs 11.5 line (-0.5), UNDER hit by 0.5 pts. Brown played 40 min (+15.4 vs L10 avg of 24.4) — 63% more than expected. Shooting efficiency was cold: 30.0% FG (-27.0% vs L10 avg of 57.0%). 3/10 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context (4/10 aligned). Counter-signals that were wrong: Trend, Defense, H2H. Projection model targeted 11.0 pts — actual 11 was 0.0 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Brown in this role.</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>Dennis Schröder</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>IND @ CLE</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D51" t="n">
+      <c r="D51" s="3" t="n">
         <v>9.5</v>
       </c>
+      <c r="E51" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Schröder scored 6 pts vs 9.5 line (-3.5), UNDER hit by 3.5 pts. Minutes were as expected: 20 played vs L10 avg 19.1. Shooting efficiency was cold: 33.3% FG (-7.0% vs L10 avg of 40.3%). 2/6 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (7/10 aligned). Counter-signals that were wrong: Defense, Pace, FG Trend. Projection model targeted 5.7 pts — actual 6 was 0.3 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Schröder in this role.</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="4" t="inlineStr">
         <is>
           <t>Jay Huff</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>IND @ CLE</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D52" t="n">
+      <c r="D52" s="4" t="n">
         <v>10.5</v>
       </c>
+      <c r="E52" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Huff scored 6 pts vs 10.5 line (-4.5), OVER missed by 4.5 pts. Huff played 18 min (-4.2 vs L10 avg of 21.8) — 19% less than expected. Shooting was in line with averages: 50.0% FG (3/6, L10 avg 50.8%). Counter-signals that proved correct: HR L10, Trend, H2H, Min Trend. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 14.0 pts — actual 6 was 8.0 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Huff for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I52" s="4" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>James Harden</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>IND @ CLE</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D53" t="n">
+      <c r="D53" s="3" t="n">
         <v>21.5</v>
       </c>
+      <c r="E53" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Harden scored 28 pts vs 21.5 line (+6.5), OVER hit by 6.5 pts. Minutes were as expected: 34 played vs L10 avg 35.7. Shooting was in line with averages: 47.1% FG (8/17, L10 avg 47.4%). Signals that called it correctly: Context, Defense, Pace, FG Trend, Min Trend (5/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 22.1 pts — actual 28 was 5.9 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Harden's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>Max Strus</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t>IND @ CLE</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D54" t="n">
+      <c r="D54" s="3" t="n">
         <v>13.5</v>
       </c>
+      <c r="E54" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Strus scored 4 pts vs 13.5 line (-9.5), UNDER hit by 9.5 pts. Strus played 31 min (+5.4 vs L10 avg of 25.5) — 21% more than expected. Shooting efficiency was cold: 10.0% FG (-36.6% vs L10 avg of 46.6%). 1/10 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, Min Trend (5/10 aligned). Counter-signals that were wrong: Trend, Defense, H2H. Projection model targeted 9.1 pts — actual 4 was 5.1 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Strus's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>Grant Williams</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>CHA @ MIN</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D55" t="n">
+      <c r="D55" s="4" t="n">
         <v>5.5</v>
       </c>
+      <c r="E55" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Williams scored 8 pts vs 5.5 line (+2.5), UNDER missed by 2.5 pts. Minutes were as expected: 19 played vs L10 avg 18.9. Shooting efficiency was hot: 66.7% FG (+29.1% vs L10 avg of 37.6%). 2/3 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Context. Signals that were wrong: Trend, Defense, Pace. Projection model targeted 3.9 pts — actual 8 was 4.1 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="3" t="inlineStr">
         <is>
           <t>Coby White</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="3" t="inlineStr">
         <is>
           <t>CHA @ MIN</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D56" t="n">
+      <c r="D56" s="3" t="n">
         <v>14.5</v>
       </c>
+      <c r="E56" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>WIN — White scored 17 pts vs 14.5 line (+2.5), OVER hit by 2.5 pts. Minutes were as expected: 20 played vs L10 avg 19.8. Shooting was in line with averages: 45.5% FG (5/11, L10 avg 48.6%). Signals that called it correctly: Volume, HR L30, HR L10, Context, H2H (6/10 aligned). Counter-signals that were wrong: Trend, Defense, Pace. Projection model targeted 15.7 pts — actual 17 was 1.3 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for White in this role.</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>Miles Bridges</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>CHA @ MIN</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D57" t="n">
+      <c r="D57" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E57" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Bridges scored 25 pts vs 15.5 line (+9.5), OVER hit by 9.5 pts. Bridges played 34 min (+6.6 vs L10 avg of 27.2) — 24% more than expected. Shooting efficiency was hot: 83.3% FG (+29.6% vs L10 avg of 53.7%). 10/12 from the field. Signals that called it correctly: Trend, Context, H2H, FG Trend (4/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 16.6 pts — actual 25 was 8.4 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Bridges's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="3" t="inlineStr">
         <is>
           <t>Julius Randle</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t>CHA @ MIN</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D58" t="n">
+      <c r="D58" s="3" t="n">
         <v>20.5</v>
       </c>
+      <c r="E58" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Randle scored 26 pts vs 20.5 line (+5.5), OVER hit by 5.5 pts. Minutes were as expected: 32 played vs L10 avg 33.7. Shooting efficiency was hot: 56.2% FG (+7.3% vs L10 avg of 48.9%). 9/16 from the field. Signals that called it correctly: HR L10, Trend, H2H, FG Trend, Min Trend (5/10 aligned). Counter-signals that were wrong: Volume, HR L30, Context. Projection model targeted 21.8 pts — actual 26 was 4.2 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Randle's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="4" t="inlineStr">
         <is>
           <t>Donte DiVincenzo</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>CHA @ MIN</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D59" t="n">
+      <c r="D59" s="4" t="n">
         <v>10.5</v>
       </c>
+      <c r="E59" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — DiVincenzo scored 6 pts vs 10.5 line (-4.5), OVER missed by 4.5 pts. DiVincenzo played 27 min (-3.8 vs L10 avg of 30.8) — 12% less than expected. Shooting efficiency was cold: 22.2% FG (-12.9% vs L10 avg of 35.1%). 2/9 from the field. Counter-signals that proved correct: HR L30, Defense, Pace, FG Trend. Signals that were wrong: Volume, HR L10, Trend. Projection model targeted 13.4 pts — actual 6 was 7.4 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="4" t="inlineStr">
         <is>
           <t>LaMelo Ball</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>CHA @ MIN</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C60" s="4" t="inlineStr">
         <is>
           <t>LEAN UNDER</t>
         </is>
       </c>
-      <c r="D60" t="n">
+      <c r="D60" s="4" t="n">
         <v>20.5</v>
       </c>
+      <c r="E60" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Ball scored 35 pts vs 20.5 line (+14.5), UNDER missed by 14.5 pts. Minutes were as expected: 31 played vs L10 avg 28.7. Shooting efficiency was hot: 59.1% FG (+16.3% vs L10 avg of 42.8%). 13/22 from the field. Counter-signals that proved correct: H2H, FG Trend, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 20.3 pts — actual 35 was 14.7 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="4" t="inlineStr">
         <is>
           <t>Moussa Diabaté</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>CHA @ MIN</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D61" t="n">
+      <c r="D61" s="4" t="n">
         <v>7.5</v>
       </c>
+      <c r="E61" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Diabaté scored 8 pts vs 7.5 line (+0.5), UNDER missed by 0.5 pts. Minutes were as expected: 24 played vs L10 avg 26.5. Shooting efficiency was hot: 75.0% FG (+7.9% vs L10 avg of 67.1%). 3/4 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, FG Trend. Signals that were wrong: Trend, Context, Defense. Projection model targeted 6.3 pts — actual 8 was 1.7 pts close (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I61" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t>Rudy Gobert</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="3" t="inlineStr">
         <is>
           <t>CHA @ MIN</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C62" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D62" t="n">
+      <c r="D62" s="3" t="n">
         <v>10.5</v>
       </c>
+      <c r="E62" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Gobert scored 12 pts vs 10.5 line (+1.5), OVER hit by 1.5 pts. Minutes were as expected: 30 played vs L10 avg 30.4. Shooting efficiency was hot: 66.7% FG (+11.3% vs L10 avg of 55.4%). 6/9 from the field. Signals that called it correctly: Volume, Context (2/10 aligned). Counter-signals that were wrong: HR L30, HR L10, Trend. Projection model targeted 11.4 pts — actual 12 was 0.6 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Gobert in this role.</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="4" t="inlineStr">
         <is>
           <t>Naz Reid</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="4" t="inlineStr">
         <is>
           <t>CHA @ MIN</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D63" t="n">
+      <c r="D63" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E63" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Reid scored 6 pts vs 12.5 line (-6.5), OVER missed by 6.5 pts. Minutes were as expected: 25 played vs L10 avg 26.4. Shooting efficiency was cold: 21.4% FG (-17.6% vs L10 avg of 39.0%). 3/14 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Defense. Signals that were wrong: Trend, Context, H2H. Projection model targeted 16.1 pts — actual 6 was 10.1 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I63" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="3" t="inlineStr">
         <is>
           <t>Brandon Miller</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="3" t="inlineStr">
         <is>
           <t>CHA @ MIN</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D64" t="n">
+      <c r="D64" s="3" t="n">
         <v>20.5</v>
       </c>
+      <c r="E64" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="n">
+        <v>-13.5</v>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Miller scored 7 pts vs 20.5 line (-13.5), UNDER hit by 13.5 pts. Miller played 34 min (+4.1 vs L10 avg of 29.9) — 14% more than expected. Shooting efficiency was cold: 20.0% FG (-29.8% vs L10 avg of 49.8%). 3/15 from the field. Signals that called it correctly: Volume, Context, Defense, Pace, Min Trend (5/10 aligned). Counter-signals that were wrong: HR L30, HR L10, Trend. Projection model targeted 9.8 pts — actual 7 was 2.8 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Miller's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="3" t="inlineStr">
         <is>
           <t>Ayo Dosunmu</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="3" t="inlineStr">
         <is>
           <t>CHA @ MIN</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D65" t="n">
+      <c r="D65" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E65" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Dosunmu scored 12 pts vs 15.5 line (-3.5), UNDER hit by 3.5 pts. Minutes were as expected: 34 played vs L10 avg 31.7. Shooting efficiency was cold: 44.4% FG (-11.1% vs L10 avg of 55.5%). 4/9 from the field. Signals that called it correctly: Volume, Context, Defense, H2H, Pace (5/10 aligned). Counter-signals that were wrong: HR L30, HR L10, Trend. Projection model targeted 14.2 pts — actual 12 was 2.2 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Dosunmu's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="5" t="inlineStr">
         <is>
           <t>Anthony Edwards</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="5" t="inlineStr">
         <is>
           <t>CHA @ MIN</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C66" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D66" t="n">
+      <c r="D66" s="5" t="n">
         <v>24.5</v>
       </c>
+      <c r="E66" s="5" t="n"/>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="n"/>
+      <c r="H66" s="5" t="inlineStr"/>
+      <c r="I66" s="5" t="n"/>
+      <c r="J66" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t>Kon Knueppel</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>CHA @ MIN</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D67" t="n">
+      <c r="D67" s="3" t="n">
         <v>17.5</v>
       </c>
+      <c r="E67" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Knueppel scored 11 pts vs 17.5 line (-6.5), UNDER hit by 6.5 pts. Knueppel played 31 min (+3.0 vs L10 avg of 28.4) — 11% more than expected. Shooting efficiency was cold: 28.6% FG (-15.7% vs L10 avg of 44.3%). 4/14 from the field. Signals that called it correctly: HR L10, Trend, Defense, Pace, FG Trend (6/10 aligned). Counter-signals that were wrong: Volume, HR L30, Context. Projection model targeted 5.6 pts — actual 11 was 5.4 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Knueppel's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="3" t="inlineStr">
         <is>
           <t>Paolo Banchero</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t>ORL @ NOP</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D68" t="n">
+      <c r="D68" s="3" t="n">
         <v>22.5</v>
       </c>
+      <c r="E68" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Banchero scored 23 pts vs 22.5 line (+0.5), OVER hit by 0.5 pts. Banchero played 38 min (+4.1 vs L10 avg of 33.9) — 12% more than expected. Shooting was in line with averages: 42.9% FG (6/14, L10 avg 41.2%). Signals that called it correctly: Volume, Context, Defense, Pace (4/10 aligned). Counter-signals that were wrong: HR L30, HR L10, Trend. Projection model targeted 27.6 pts — actual 23 was 4.6 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms Banchero's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="5" t="inlineStr">
         <is>
           <t>Trey Murphy III</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="5" t="inlineStr">
         <is>
           <t>ORL @ NOP</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C69" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D69" t="n">
+      <c r="D69" s="5" t="n">
         <v>20.5</v>
       </c>
+      <c r="E69" s="5" t="n"/>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="n"/>
+      <c r="H69" s="5" t="inlineStr"/>
+      <c r="I69" s="5" t="n"/>
+      <c r="J69" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="5" t="inlineStr">
         <is>
           <t>Dejounte Murray</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B70" s="5" t="inlineStr">
         <is>
           <t>ORL @ NOP</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C70" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D70" t="n">
+      <c r="D70" s="5" t="n">
         <v>16.5</v>
       </c>
+      <c r="E70" s="5" t="n"/>
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="n"/>
+      <c r="H70" s="5" t="inlineStr"/>
+      <c r="I70" s="5" t="n"/>
+      <c r="J70" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="3" t="inlineStr">
         <is>
           <t>Herbert Jones</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B71" s="3" t="inlineStr">
         <is>
           <t>ORL @ NOP</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C71" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D71" t="n">
+      <c r="D71" s="3" t="n">
         <v>8.5</v>
       </c>
+      <c r="E71" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Jones scored 5 pts vs 8.5 line (-3.5), UNDER hit by 3.5 pts. Jones played 9 min (-18.9 vs L10 avg of 27.6) — 68% less than expected. Shooting efficiency was hot: 50.0% FG (+11.2% vs L10 avg of 38.8%). 2/4 from the field. Signals that called it correctly: Trend, Context, Defense, Pace, Min Trend (5/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 7.2 pts — actual 5 was 2.2 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Jones's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="3" t="inlineStr">
         <is>
           <t>Desmond Bane</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="3" t="inlineStr">
         <is>
           <t>ORL @ NOP</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C72" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D72" t="n">
+      <c r="D72" s="3" t="n">
         <v>20.5</v>
       </c>
+      <c r="E72" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Bane scored 27 pts vs 20.5 line (+6.5), OVER hit by 6.5 pts. Minutes were as expected: 34 played vs L10 avg 33.0. Shooting was in line with averages: 42.1% FG (8/19, L10 avg 46.4%). Signals that called it correctly: Volume, HR L30, Context, Defense, Pace (5/10 aligned). Counter-signals that were wrong: HR L10, Trend, H2H. Projection model targeted 21.8 pts — actual 27 was 5.2 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Bane's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="3" t="inlineStr">
         <is>
           <t>Zion Williamson</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B73" s="3" t="inlineStr">
         <is>
           <t>ORL @ NOP</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C73" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D73" t="n">
+      <c r="D73" s="3" t="n">
         <v>21.5</v>
       </c>
+      <c r="E73" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Williamson scored 17 pts vs 21.5 line (-4.5), UNDER hit by 4.5 pts. Minutes were as expected: 28 played vs L10 avg 30.1. Shooting efficiency was cold: 45.5% FG (-23.6% vs L10 avg of 69.1%). 5/11 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (8/10 aligned). Counter-signals that were wrong: H2H, FG Trend. Projection model targeted 18.3 pts — actual 17 was 1.3 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Strong signal alignment (8/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I73" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="3" t="inlineStr">
         <is>
           <t>Jevon Carter</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B74" s="3" t="inlineStr">
         <is>
           <t>ORL @ NOP</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C74" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D74" t="n">
+      <c r="D74" s="3" t="n">
         <v>6.5</v>
       </c>
+      <c r="E74" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Carter scored 11 pts vs 6.5 line (+4.5), OVER hit by 4.5 pts. Minutes were as expected: 21 played vs L10 avg 20.6. Shooting efficiency was hot: 55.6% FG (+17.9% vs L10 avg of 37.7%). 5/9 from the field. Signals that called it correctly: Volume, HR L10, Context, Defense, Pace (7/10 aligned). Counter-signals that were wrong: HR L30, Trend, H2H. Projection model targeted 7.3 pts — actual 11 was 3.7 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Carter's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="3" t="inlineStr">
         <is>
           <t>Jalen Suggs</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="3" t="inlineStr">
         <is>
           <t>ORL @ NOP</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C75" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D75" t="n">
+      <c r="D75" s="3" t="n">
         <v>14.5</v>
       </c>
+      <c r="E75" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Suggs scored 11 pts vs 14.5 line (-3.5), UNDER hit by 3.5 pts. Suggs played 34 min (+3.0 vs L10 avg of 30.6) — 10% more than expected. Shooting efficiency was cold: 21.1% FG (-22.0% vs L10 avg of 43.1%). 4/19 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, FG Trend (5/10 aligned). Counter-signals that were wrong: Trend, Defense, H2H. Projection model targeted 4.5 pts — actual 11 was 6.5 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Suggs's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I75" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="3" t="inlineStr">
         <is>
           <t>Saddiq Bey</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B76" s="3" t="inlineStr">
         <is>
           <t>ORL @ NOP</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C76" s="3" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D76" t="n">
+      <c r="D76" s="3" t="n">
         <v>18.5</v>
       </c>
+      <c r="E76" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Bey scored 32 pts vs 18.5 line (+13.5), OVER hit by 13.5 pts. Bey played 39 min (+6.2 vs L10 avg of 32.6) — 19% more than expected. Shooting efficiency was cold: 41.7% FG (-5.9% vs L10 avg of 47.6%). 10/24 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, Defense (6/10 aligned). Counter-signals that were wrong: Trend, H2H, Pace. Projection model targeted 18.4 pts — actual 32 was 13.6 pts off (wrong direction). Result classification: MODEL_CORRECT. Note: Result confirms Bey's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I76" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="4" t="inlineStr">
         <is>
           <t>Tristan da Silva</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B77" s="4" t="inlineStr">
         <is>
           <t>ORL @ NOP</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C77" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D77" t="n">
+      <c r="D77" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E77" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G77" s="4" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="H77" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Silva scored 2 pts vs 9.5 line (-7.5), OVER missed by 7.5 pts. Silva played 18 min (-10.3 vs L10 avg of 27.9) — 37% less than expected. Shooting efficiency was cold: 25.0% FG (-21.4% vs L10 avg of 46.4%). 1/4 from the field. Counter-signals that proved correct: H2H, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 11.5 pts — actual 2 was 9.5 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Silva for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I77" s="4" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="4" t="inlineStr">
         <is>
           <t>Franz Wagner</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B78" s="4" t="inlineStr">
         <is>
           <t>ORL @ NOP</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C78" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D78" t="n">
+      <c r="D78" s="4" t="n">
         <v>14.5</v>
       </c>
+      <c r="E78" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Wagner scored 11 pts vs 14.5 line (-3.5), OVER missed by 3.5 pts. Wagner played 20 min (-3.5 vs L10 avg of 23.7) — 15% less than expected. Shooting efficiency was cold: 40.0% FG (-9.9% vs L10 avg of 49.9%). 4/10 from the field. Counter-signals that proved correct: HR L10, Trend, H2H, Min Trend. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 18.5 pts — actual 11 was 7.5 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I78" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="4" t="inlineStr">
         <is>
           <t>Wendell Carter Jr.</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B79" s="4" t="inlineStr">
         <is>
           <t>ORL @ NOP</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C79" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D79" t="n">
+      <c r="D79" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E79" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Jr. scored 13 pts vs 12.5 line (+0.5), UNDER missed by 0.5 pts. Minutes were as expected: 32 played vs L10 avg 29.4. Shooting efficiency was hot: 85.7% FG (+31.9% vs L10 avg of 53.8%). 6/7 from the field. Counter-signals that proved correct: HR L10, Trend, Defense, H2H. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 8.8 pts — actual 13 was 4.2 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I79" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="3" t="inlineStr">
         <is>
           <t>Alex Caruso</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B80" s="3" t="inlineStr">
         <is>
           <t>UTA @ OKC</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C80" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D80" t="n">
+      <c r="D80" s="3" t="n">
         <v>4.5</v>
       </c>
+      <c r="E80" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Caruso scored 5 pts vs 4.5 line (+0.5), OVER hit by 0.5 pts. Caruso played 13 min (-5.9 vs L10 avg of 19.2) — 31% less than expected. Shooting efficiency was hot: 50.0% FG (+9.5% vs L10 avg of 40.5%). 2/4 from the field. Signals that called it correctly: Volume, HR L30, Context, Defense, H2H (7/10 aligned). Counter-signals that were wrong: HR L10, Trend, FG Trend. Projection model targeted 7.2 pts — actual 5 was 2.2 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms Caruso's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I80" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="A81" s="3" t="inlineStr">
         <is>
           <t>Jared McCain</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B81" s="3" t="inlineStr">
         <is>
           <t>UTA @ OKC</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C81" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D81" t="n">
+      <c r="D81" s="3" t="n">
         <v>8.5</v>
       </c>
+      <c r="E81" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>WIN — McCain scored 3 pts vs 8.5 line (-5.5), UNDER hit by 5.5 pts. Minutes were as expected: 15 played vs L10 avg 17.4. Shooting efficiency was cold: 25.0% FG (-16.8% vs L10 avg of 41.8%). 1/4 from the field. Signals that called it correctly: HR L10, Trend, FG Trend, Min Trend (4/10 aligned). Counter-signals that were wrong: Volume, HR L30, Context. Projection model targeted 5.5 pts — actual 3 was 2.5 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms McCain's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I81" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="A82" s="3" t="inlineStr">
         <is>
           <t>Cody Williams</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B82" s="3" t="inlineStr">
         <is>
           <t>UTA @ OKC</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C82" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D82" t="n">
+      <c r="D82" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E82" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Williams scored 8 pts vs 15.5 line (-7.5), UNDER hit by 7.5 pts. Williams played 36 min (+3.0 vs L10 avg of 33.4) — 9% more than expected. Shooting efficiency was cold: 27.3% FG (-19.5% vs L10 avg of 46.8%). 3/11 from the field. Signals that called it correctly: Volume, HR L30, Context, Defense, H2H (7/10 aligned). Counter-signals that were wrong: HR L10, Trend, Min Trend. Projection model targeted 6.9 pts — actual 8 was 1.1 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Williams in this role.</t>
+        </is>
+      </c>
+      <c r="I82" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="A83" s="4" t="inlineStr">
         <is>
           <t>John Konchar</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B83" s="4" t="inlineStr">
         <is>
           <t>UTA @ OKC</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C83" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D83" t="n">
+      <c r="D83" s="4" t="n">
         <v>6.5</v>
       </c>
+      <c r="E83" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H83" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Konchar scored 9 pts vs 6.5 line (+2.5), UNDER missed by 2.5 pts. Minutes were as expected: 26 played vs L10 avg 27.4. Shooting efficiency was cold: 42.9% FG (-8.0% vs L10 avg of 50.9%). 3/7 from the field. Counter-signals that proved correct: HR L10, Trend, FG Trend, Min Trend. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 1.6 pts — actual 9 was 7.4 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I83" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="A84" s="4" t="inlineStr">
         <is>
           <t>Jalen Williams</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B84" s="4" t="inlineStr">
         <is>
           <t>UTA @ OKC</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C84" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D84" t="n">
+      <c r="D84" s="4" t="n">
         <v>16.5</v>
       </c>
+      <c r="E84" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G84" s="4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Williams scored 15 pts vs 16.5 line (-1.5), OVER missed by 1.5 pts. Minutes were as expected: 26 played vs L10 avg 24.1. Shooting efficiency was hot: 55.6% FG (+5.8% vs L10 avg of 49.8%). 5/9 from the field. Counter-signals that proved correct: Trend, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 18.0 pts — actual 15 was 3.0 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I84" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="A85" s="4" t="inlineStr">
         <is>
           <t>Luguentz Dort</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B85" s="4" t="inlineStr">
         <is>
           <t>UTA @ OKC</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C85" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D85" t="n">
+      <c r="D85" s="4" t="n">
         <v>7.5</v>
       </c>
+      <c r="E85" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G85" s="4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H85" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Dort scored 13 pts vs 7.5 line (+5.5), UNDER missed by 5.5 pts. Minutes were as expected: 21 played vs L10 avg 22.8. Shooting efficiency was hot: 71.4% FG (+40.6% vs L10 avg of 30.8%). 5/7 from the field. Counter-signals that proved correct: Volume, HR L30, Trend, Defense. Signals that were wrong: HR L10, Context, H2H. Projection model targeted 4.8 pts — actual 13 was 8.2 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I85" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="A86" s="3" t="inlineStr">
         <is>
           <t>Kyle Filipowski</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B86" s="3" t="inlineStr">
         <is>
           <t>UTA @ OKC</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C86" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D86" t="n">
+      <c r="D86" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E86" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Filipowski scored 20 pts vs 15.5 line (+4.5), OVER hit by 4.5 pts. Filipowski played 38 min (+11.6 vs L10 avg of 26.0) — 45% more than expected. Shooting efficiency was cold: 40.0% FG (-8.9% vs L10 avg of 48.9%). 10/25 from the field. Signals that called it correctly: HR L10, Trend, Min Trend (3/10 aligned). Counter-signals that were wrong: Volume, HR L30, Context. Projection model targeted 16.0 pts — actual 20 was 4.0 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Filipowski's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I86" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
+      <c r="A87" s="3" t="inlineStr">
         <is>
           <t>Ace Bailey</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B87" s="3" t="inlineStr">
         <is>
           <t>UTA @ OKC</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C87" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D87" t="n">
+      <c r="D87" s="3" t="n">
         <v>17.5</v>
       </c>
+      <c r="E87" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G87" s="3" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Bailey scored 14 pts vs 17.5 line (-3.5), UNDER hit by 3.5 pts. Minutes were as expected: 34 played vs L10 avg 31.9. Shooting was in line with averages: 42.9% FG (6/14, L10 avg 43.8%). Signals that called it correctly: Volume, HR L30, Trend, Context, Defense (8/10 aligned). Counter-signals that were wrong: HR L10, Min Trend. Projection model targeted 14.9 pts — actual 14 was 0.9 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Strong signal alignment (8/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I87" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="A88" s="3" t="inlineStr">
         <is>
           <t>Chet Holmgren</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B88" s="3" t="inlineStr">
         <is>
           <t>UTA @ OKC</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C88" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D88" t="n">
+      <c r="D88" s="3" t="n">
         <v>14.5</v>
       </c>
+      <c r="E88" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Holmgren scored 21 pts vs 14.5 line (+6.5), OVER hit by 6.5 pts. Holmgren played 22 min (-5.6 vs L10 avg of 27.8) — 20% less than expected. Shooting efficiency was hot: 72.7% FG (+20.6% vs L10 avg of 52.1%). 8/11 from the field. Signals that called it correctly: Volume, HR L30, Context, Defense, H2H (7/10 aligned). Counter-signals that were wrong: HR L10, Trend, Min Trend. Projection model targeted 17.5 pts — actual 21 was 3.5 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Holmgren's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I88" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
+      <c r="A89" s="4" t="inlineStr">
         <is>
           <t>Shai Gilgeous-Alexander</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B89" s="4" t="inlineStr">
         <is>
           <t>UTA @ OKC</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="C89" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D89" t="n">
+      <c r="D89" s="4" t="n">
         <v>29.5</v>
       </c>
+      <c r="E89" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G89" s="4" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="H89" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Gilgeous-Alexander scored 20 pts vs 29.5 line (-9.5), OVER missed by 9.5 pts. Gilgeous-Alexander played 24 min (-9.4 vs L10 avg of 33.0) — 28% less than expected. Shooting efficiency was hot: 70.0% FG (+12.3% vs L10 avg of 57.7%). 7/10 from the field. Counter-signals that proved correct: HR L10, Min Trend. Signals that were wrong: Volume, HR L30, Trend. Projection model targeted 29.8 pts — actual 20 was 9.8 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Gilgeous-Alexander for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I89" s="4" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
+      <c r="A90" s="3" t="inlineStr">
         <is>
           <t>Isaiah Joe</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B90" s="3" t="inlineStr">
         <is>
           <t>UTA @ OKC</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C90" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D90" t="n">
+      <c r="D90" s="3" t="n">
         <v>8.5</v>
       </c>
+      <c r="E90" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Joe scored 9 pts vs 8.5 line (+0.5), OVER hit by 0.5 pts. Joe played 14 min (-4.0 vs L10 avg of 18.4) — 22% less than expected. Shooting efficiency was hot: 60.0% FG (+15.2% vs L10 avg of 44.8%). 3/5 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, Defense (8/10 aligned). Counter-signals that were wrong: Trend, Min Trend. Projection model targeted 15.2 pts — actual 9 was 6.2 pts off (correct direction). Result classification: CLOSE_CALL. Note: Strong signal alignment (8/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I90" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
+      <c r="A91" s="3" t="inlineStr">
         <is>
           <t>Cason Wallace</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B91" s="3" t="inlineStr">
         <is>
           <t>UTA @ OKC</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="C91" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D91" t="n">
+      <c r="D91" s="3" t="n">
         <v>6.5</v>
       </c>
+      <c r="E91" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H91" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Wallace scored 16 pts vs 6.5 line (+9.5), OVER hit by 9.5 pts. Minutes were as expected: 22 played vs L10 avg 23.1. Shooting efficiency was hot: 60.0% FG (+13.5% vs L10 avg of 46.5%). 6/10 from the field. Signals that called it correctly: Volume, HR L30, Context, Defense, H2H (7/10 aligned). Counter-signals that were wrong: HR L10, Trend, Min Trend. Projection model targeted 10.5 pts — actual 16 was 5.5 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Wallace's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I91" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
+      <c r="A92" s="4" t="inlineStr">
         <is>
           <t>Brice Sensabaugh</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B92" s="4" t="inlineStr">
         <is>
           <t>UTA @ OKC</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C92" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D92" t="n">
+      <c r="D92" s="4" t="n">
         <v>20.5</v>
       </c>
+      <c r="E92" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G92" s="4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H92" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Sensabaugh scored 34 pts vs 20.5 line (+13.5), UNDER missed by 13.5 pts. Sensabaugh played 43 min (+13.1 vs L10 avg of 30.1) — 44% more than expected. Shooting efficiency was hot: 57.9% FG (+5.6% vs L10 avg of 52.3%). 11/19 from the field. Counter-signals that proved correct: HR L10, Trend, FG Trend, Min Trend. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 15.4 pts — actual 34 was 18.6 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I92" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
+      <c r="A93" s="3" t="inlineStr">
         <is>
           <t>Ajay Mitchell</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B93" s="3" t="inlineStr">
         <is>
           <t>UTA @ OKC</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C93" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D93" t="n">
+      <c r="D93" s="3" t="n">
         <v>11.5</v>
       </c>
+      <c r="E93" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Mitchell scored 7 pts vs 11.5 line (-4.5), UNDER hit by 4.5 pts. Mitchell played 19 min (-6.2 vs L10 avg of 25.0) — 25% less than expected. Shooting efficiency was cold: 33.3% FG (-16.7% vs L10 avg of 50.0%). 3/9 from the field. Signals that called it correctly: Trend, H2H, FG Trend, Min Trend (4/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 10.2 pts — actual 7 was 3.2 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Mitchell's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I93" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
+      <c r="A94" s="4" t="inlineStr">
         <is>
           <t>Isaiah Hartenstein</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B94" s="4" t="inlineStr">
         <is>
           <t>UTA @ OKC</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C94" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D94" t="n">
+      <c r="D94" s="4" t="n">
         <v>7.5</v>
       </c>
+      <c r="E94" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G94" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H94" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Hartenstein scored 10 pts vs 7.5 line (+2.5), UNDER missed by 2.5 pts. Minutes were as expected: 19 played vs L10 avg 21.7. Shooting efficiency was hot: 80.0% FG (+41.9% vs L10 avg of 38.1%). 4/5 from the field. Counter-signals that proved correct: Volume, HR L30, Defense, H2H. Signals that were wrong: HR L10, Trend, Context. Projection model targeted 4.6 pts — actual 10 was 5.4 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I94" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
+      <c r="A95" s="4" t="inlineStr">
         <is>
           <t>Luke Kennard</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B95" s="4" t="inlineStr">
         <is>
           <t>LAL @ DAL</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="C95" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D95" t="n">
+      <c r="D95" s="4" t="n">
         <v>13.5</v>
       </c>
+      <c r="E95" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G95" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H95" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Kennard scored 15 pts vs 13.5 line (+1.5), UNDER missed by 1.5 pts. Kennard played 41 min (+19.2 vs L10 avg of 22.0) — 87% more than expected. Shooting efficiency was cold: 29.4% FG (-12.2% vs L10 avg of 41.6%). 5/17 from the field. Counter-signals that proved correct: Defense, Pace, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 6.6 pts — actual 15 was 8.4 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I95" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
+      <c r="A96" s="4" t="inlineStr">
         <is>
           <t>Cooper Flagg</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="B96" s="4" t="inlineStr">
         <is>
           <t>LAL @ DAL</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="C96" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D96" t="n">
+      <c r="D96" s="4" t="n">
         <v>24.5</v>
       </c>
+      <c r="E96" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G96" s="4" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="H96" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Flagg scored 45 pts vs 24.5 line (+20.5), UNDER missed by 20.5 pts. Flagg played 38 min (+3.7 vs L10 avg of 34.8) — 11% more than expected. Shooting was in line with averages: 51.9% FG (14/27, L10 avg 47.7%). Counter-signals that proved correct: Trend, Defense, H2H, FG Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 16.8 pts — actual 45 was 28.2 pts off (correct direction). Loss classification: BLOWOUT_EFFECT. Note: Game script invalidated the prop. Consider blowout probability when DAL is involved.</t>
+        </is>
+      </c>
+      <c r="I96" s="4" t="inlineStr">
+        <is>
+          <t>BLOWOUT_EFFECT</t>
+        </is>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
+      <c r="A97" s="4" t="inlineStr">
         <is>
           <t>Rui Hachimura</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B97" s="4" t="inlineStr">
         <is>
           <t>LAL @ DAL</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="C97" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D97" t="n">
+      <c r="D97" s="4" t="n">
         <v>14.5</v>
       </c>
+      <c r="E97" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G97" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H97" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Hachimura scored 21 pts vs 14.5 line (+6.5), UNDER missed by 6.5 pts. Hachimura played 39 min (+15.9 vs L10 avg of 23.1) — 69% more than expected. Shooting efficiency was hot: 69.2% FG (+15.0% vs L10 avg of 54.2%). 9/13 from the field. Counter-signals that proved correct: Defense, H2H, Pace, FG Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 11.7 pts — actual 21 was 9.3 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I97" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J97" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t>Jake LaRavia</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B98" s="4" t="inlineStr">
         <is>
           <t>LAL @ DAL</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="C98" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D98" t="n">
+      <c r="D98" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E98" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G98" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H98" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — LaRavia scored 14 pts vs 12.5 line (+1.5), UNDER missed by 1.5 pts. LaRavia played 36 min (+12.9 vs L10 avg of 22.8) — 57% more than expected. Shooting efficiency was cold: 27.3% FG (-26.5% vs L10 avg of 53.8%). 3/11 from the field. Counter-signals that proved correct: Defense, Pace, FG Trend, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 4.8 pts — actual 14 was 9.2 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I98" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
+      <c r="A99" s="4" t="inlineStr">
         <is>
           <t>P.J. Washington</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B99" s="4" t="inlineStr">
         <is>
           <t>LAL @ DAL</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="C99" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D99" t="n">
+      <c r="D99" s="4" t="n">
         <v>13.5</v>
       </c>
+      <c r="E99" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G99" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H99" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Washington scored 15 pts vs 13.5 line (+1.5), UNDER missed by 1.5 pts. Minutes were as expected: 30 played vs L10 avg 31.6. Shooting efficiency was hot: 60.0% FG (+15.3% vs L10 avg of 44.7%). 6/10 from the field. Counter-signals that proved correct: HR L10, Trend, Defense, FG Trend. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 11.5 pts — actual 15 was 3.5 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I99" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J99" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
+      <c r="A100" s="4" t="inlineStr">
         <is>
           <t>Naji Marshall</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="B100" s="4" t="inlineStr">
         <is>
           <t>LAL @ DAL</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
+      <c r="C100" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D100" t="n">
+      <c r="D100" s="4" t="n">
         <v>15.5</v>
       </c>
+      <c r="E100" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G100" s="4" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H100" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Marshall scored 13 pts vs 15.5 line (-2.5), OVER missed by 2.5 pts. Minutes were as expected: 32 played vs L10 avg 30.1. Shooting efficiency was hot: 55.6% FG (+12.2% vs L10 avg of 43.4%). 5/9 from the field. Counter-signals that proved correct: Defense, Pace, FG Trend, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 17.0 pts — actual 13 was 4.0 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I100" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J100" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
+      <c r="A101" s="3" t="inlineStr">
         <is>
           <t>Klay Thompson</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B101" s="3" t="inlineStr">
         <is>
           <t>LAL @ DAL</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="C101" s="3" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D101" t="n">
+      <c r="D101" s="3" t="n">
         <v>9.5</v>
       </c>
+      <c r="E101" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G101" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H101" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Thompson scored 11 pts vs 9.5 line (+1.5), OVER hit by 1.5 pts. Thompson played 18 min (-3.3 vs L10 avg of 21.5) — 15% less than expected. Shooting efficiency was hot: 50.0% FG (+10.0% vs L10 avg of 40.0%). 4/8 from the field. Signals that called it correctly: Volume, Context, H2H (3/10 aligned). Counter-signals that were wrong: HR L30, HR L10, Trend. Projection model targeted 9.5 pts — actual 11 was 1.5 pts close (wrong direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Thompson in this role.</t>
+        </is>
+      </c>
+      <c r="I101" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
+      <c r="A102" s="4" t="inlineStr">
         <is>
           <t>Brandon Williams</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="B102" s="4" t="inlineStr">
         <is>
           <t>LAL @ DAL</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="C102" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D102" t="n">
+      <c r="D102" s="4" t="n">
         <v>13.5</v>
       </c>
+      <c r="E102" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G102" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H102" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Williams scored 13 pts vs 13.5 line (-0.5), OVER missed by 0.5 pts. Williams played 25 min (+3.2 vs L10 avg of 21.4) — 15% more than expected. Shooting efficiency was hot: 57.1% FG (+12.7% vs L10 avg of 44.4%). 4/7 from the field. Counter-signals that proved correct: HR L10, Defense, H2H, Pace. Signals that were wrong: Volume, HR L30, Trend. Projection model targeted 14.2 pts — actual 13 was 1.2 pts close (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I102" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J102" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
+      <c r="A103" s="3" t="inlineStr">
         <is>
           <t>Deandre Ayton</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B103" s="3" t="inlineStr">
         <is>
           <t>LAL @ DAL</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="C103" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D103" t="n">
+      <c r="D103" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E103" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G103" s="3" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H103" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Ayton scored 13 pts vs 15.5 line (-2.5), UNDER hit by 2.5 pts. Ayton played 19 min (-7.1 vs L10 avg of 26.5) — 27% less than expected. Shooting efficiency was cold: 55.6% FG (-17.8% vs L10 avg of 73.4%). 5/9 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, H2H (5/10 aligned). Counter-signals that were wrong: Trend, Defense, Pace. Projection model targeted 10.4 pts — actual 13 was 2.6 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Ayton's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I103" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
+      <c r="A104" s="3" t="inlineStr">
         <is>
           <t>Daniel Gafford</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B104" s="3" t="inlineStr">
         <is>
           <t>LAL @ DAL</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="C104" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D104" t="n">
+      <c r="D104" s="3" t="n">
         <v>10.5</v>
       </c>
+      <c r="E104" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F104" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G104" s="3" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H104" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Gafford scored 7 pts vs 10.5 line (-3.5), UNDER hit by 3.5 pts. Gafford played 20 min (-3.5 vs L10 avg of 23.4) — 15% less than expected. Shooting efficiency was cold: 50.0% FG (-23.4% vs L10 avg of 73.4%). 2/4 from the field. Signals that called it correctly: HR L30, Context, H2H, Pace (4/10 aligned). Counter-signals that were wrong: Volume, HR L10, Trend. Projection model targeted 6.2 pts — actual 7 was 0.8 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Gafford in this role.</t>
+        </is>
+      </c>
+      <c r="I104" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
+      <c r="A105" s="4" t="inlineStr">
         <is>
           <t>LeBron James</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B105" s="4" t="inlineStr">
         <is>
           <t>LAL @ DAL</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="C105" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D105" t="n">
+      <c r="D105" s="4" t="n">
         <v>25.5</v>
       </c>
+      <c r="E105" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F105" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G105" s="4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H105" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — James scored 30 pts vs 25.5 line (+4.5), UNDER missed by 4.5 pts. James played 39 min (+4.7 vs L10 avg of 34.0) — 14% more than expected. Shooting was in line with averages: 54.5% FG (12/22, L10 avg 53.3%). Counter-signals that proved correct: Defense, Pace, FG Trend, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 16.2 pts — actual 30 was 13.8 pts off (correct direction). Loss classification: MODEL_FAILURE. Note: Model signals were misleading for this matchup — review James's recent role and usage for pattern shifts.</t>
+        </is>
+      </c>
+      <c r="I105" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J105" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
+      <c r="A106" s="3" t="inlineStr">
         <is>
           <t>Bronny James</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="B106" s="3" t="inlineStr">
         <is>
           <t>LAL @ DAL</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="C106" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D106" t="n">
+      <c r="D106" s="3" t="n">
         <v>6.5</v>
       </c>
+      <c r="E106" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F106" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H106" s="3" t="inlineStr">
+        <is>
+          <t>WIN — James scored 5 pts vs 6.5 line (-1.5), UNDER hit by 1.5 pts. Minutes were as expected: 9 played vs L10 avg 10.8. Shooting efficiency was hot: 66.7% FG (+41.4% vs L10 avg of 25.3%). 2/3 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, H2H (6/10 aligned). Counter-signals that were wrong: Trend, Defense, Pace. Projection model targeted -0.8 pts — actual 5 was 5.8 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms James's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I106" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
+      <c r="A107" s="4" t="inlineStr">
         <is>
           <t>Max Christie</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
+      <c r="B107" s="4" t="inlineStr">
         <is>
           <t>LAL @ DAL</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
+      <c r="C107" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D107" t="n">
+      <c r="D107" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E107" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F107" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G107" s="4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H107" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Christie scored 8 pts vs 9.5 line (-1.5), OVER missed by 1.5 pts. Christie played 25 min (-3.5 vs L10 avg of 28.7) — 12% less than expected. Shooting efficiency was cold: 33.3% FG (-11.7% vs L10 avg of 45.0%). 2/6 from the field. Counter-signals that proved correct: HR L10, Trend, Defense, Pace. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 12.8 pts — actual 8 was 4.8 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I107" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J107" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
+      <c r="A108" s="4" t="inlineStr">
         <is>
           <t>Precious Achiuwa</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="B108" s="4" t="inlineStr">
         <is>
           <t>LAC @ SAC</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
+      <c r="C108" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D108" t="n">
+      <c r="D108" s="4" t="n">
         <v>13.5</v>
       </c>
+      <c r="E108" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F108" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G108" s="4" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H108" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Achiuwa scored 8 pts vs 13.5 line (-5.5), OVER missed by 5.5 pts. Achiuwa played 20 min (-11.1 vs L10 avg of 31.3) — 35% less than expected. Shooting efficiency was cold: 50.0% FG (-8.2% vs L10 avg of 58.2%). 3/6 from the field. Counter-signals that proved correct: Volume, HR L30, Defense, H2H. Signals that were wrong: HR L10, Trend, Context. Projection model targeted 14.3 pts — actual 8 was 6.3 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Achiuwa for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I108" s="4" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J108" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
+      <c r="A109" s="4" t="inlineStr">
         <is>
           <t>Maxime Raynaud</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
+      <c r="B109" s="4" t="inlineStr">
         <is>
           <t>LAC @ SAC</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
+      <c r="C109" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D109" t="n">
+      <c r="D109" s="4" t="n">
         <v>14.5</v>
       </c>
+      <c r="E109" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F109" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G109" s="4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H109" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Raynaud scored 11 pts vs 14.5 line (-3.5), OVER missed by 3.5 pts. Minutes were as expected: 33 played vs L10 avg 32.6. Shooting efficiency was cold: 41.7% FG (-14.5% vs L10 avg of 56.2%). 5/12 from the field. Counter-signals that proved correct: HR L30, Trend, Defense, Pace. Signals that were wrong: Volume, HR L10, Context. Projection model targeted 18.7 pts — actual 11 was 7.7 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I109" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J109" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
+      <c r="A110" s="3" t="inlineStr">
         <is>
           <t>John Collins</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
+      <c r="B110" s="3" t="inlineStr">
         <is>
           <t>LAC @ SAC</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
+      <c r="C110" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D110" t="n">
+      <c r="D110" s="3" t="n">
         <v>12.5</v>
       </c>
+      <c r="E110" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F110" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G110" s="3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H110" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Collins scored 25 pts vs 12.5 line (+12.5), OVER hit by 12.5 pts. Minutes were as expected: 24 played vs L10 avg 26.0. Shooting efficiency was cold: 45.0% FG (-5.2% vs L10 avg of 50.2%). 9/20 from the field. Signals that called it correctly: Volume, HR L30, Context, Defense, H2H (5/10 aligned). Counter-signals that were wrong: HR L10, Trend, Pace. Projection model targeted 13.7 pts — actual 25 was 11.3 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Collins's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I110" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J110" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
+      <c r="A111" s="4" t="inlineStr">
         <is>
           <t>Kawhi Leonard</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
+      <c r="B111" s="4" t="inlineStr">
         <is>
           <t>LAC @ SAC</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
+      <c r="C111" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D111" t="n">
+      <c r="D111" s="4" t="n">
         <v>27.5</v>
       </c>
+      <c r="E111" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="F111" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G111" s="4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H111" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Leonard scored 26 pts vs 27.5 line (-1.5), OVER missed by 1.5 pts. Minutes were as expected: 30 played vs L10 avg 30.4. Shooting was in line with averages: 50.0% FG (9/18, L10 avg 52.3%). Counter-signals that proved correct: HR L10, Trend, Pace, Min Trend. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 29.2 pts — actual 26 was 3.2 pts off (correct direction). Loss classification: CLOSE_CALL. Note: Within 2 pts — direction was sound. Small execution variance, no model adjustment needed.</t>
+        </is>
+      </c>
+      <c r="I111" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J111" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
+      <c r="A112" s="4" t="inlineStr">
         <is>
           <t>Derrick Jones Jr.</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
+      <c r="B112" s="4" t="inlineStr">
         <is>
           <t>LAC @ SAC</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
+      <c r="C112" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D112" t="n">
+      <c r="D112" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E112" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F112" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G112" s="4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H112" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Jr. scored 6 pts vs 9.5 line (-3.5), OVER missed by 3.5 pts. Minutes were as expected: 25 played vs L10 avg 27.4. Shooting efficiency was hot: 75.0% FG (+34.2% vs L10 avg of 40.8%). 3/4 from the field. Counter-signals that proved correct: HR L10, Trend, Pace, FG Trend. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 10.7 pts — actual 6 was 4.7 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I112" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J112" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
+      <c r="A113" s="3" t="inlineStr">
         <is>
           <t>DeMar DeRozan</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
+      <c r="B113" s="3" t="inlineStr">
         <is>
           <t>LAC @ SAC</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
+      <c r="C113" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D113" t="n">
+      <c r="D113" s="3" t="n">
         <v>16.5</v>
       </c>
+      <c r="E113" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F113" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G113" s="3" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="H113" s="3" t="inlineStr">
+        <is>
+          <t>WIN — DeRozan scored 9 pts vs 16.5 line (-7.5), UNDER hit by 7.5 pts. DeRozan played 10 min (-19.9 vs L10 avg of 30.3) — 66% less than expected. Shooting efficiency was hot: 80.0% FG (+30.9% vs L10 avg of 49.1%). 4/5 from the field. Signals that called it correctly: HR L30, Pace (2/10 aligned). Counter-signals that were wrong: Volume, HR L10, Trend. Projection model targeted 12.7 pts — actual 9 was 3.7 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms DeRozan's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I113" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J113" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
+      <c r="A114" s="4" t="inlineStr">
         <is>
           <t>Devin Carter</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
+      <c r="B114" s="4" t="inlineStr">
         <is>
           <t>LAC @ SAC</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
+      <c r="C114" s="4" t="inlineStr">
         <is>
           <t>LEAN UNDER</t>
         </is>
       </c>
-      <c r="D114" t="n">
+      <c r="D114" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E114" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="F114" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G114" s="4" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H114" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Carter scored 21 pts vs 12.5 line (+8.5), UNDER missed by 8.5 pts. Carter played 36 min (+14.6 vs L10 avg of 21.8) — 67% more than expected. Shooting efficiency was hot: 57.1% FG (+18.3% vs L10 avg of 38.8%). 8/14 from the field. Counter-signals that proved correct: HR L10, Trend, Defense, FG Trend. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 12.7 pts — actual 21 was 8.3 pts off (wrong direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I114" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J114" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
+      <c r="A115" s="4" t="inlineStr">
         <is>
           <t>Brook Lopez</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
+      <c r="B115" s="4" t="inlineStr">
         <is>
           <t>LAC @ SAC</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr">
+      <c r="C115" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D115" t="n">
+      <c r="D115" s="4" t="n">
         <v>10.5</v>
       </c>
+      <c r="E115" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G115" s="4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H115" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Lopez scored 9 pts vs 10.5 line (-1.5), OVER missed by 1.5 pts. Lopez played 19 min (-9.4 vs L10 avg of 28.5) — 33% less than expected. Shooting efficiency was cold: 40.0% FG (-8.2% vs L10 avg of 48.2%). 2/5 from the field. Counter-signals that proved correct: HR L30, HR L10, Pace. Signals that were wrong: Volume, Trend, Context. Projection model targeted 11.1 pts — actual 9 was 2.1 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Lopez for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I115" s="4" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J115" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr">
+      <c r="A116" s="3" t="inlineStr">
         <is>
           <t>Nique Clifford</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
+      <c r="B116" s="3" t="inlineStr">
         <is>
           <t>LAC @ SAC</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
+      <c r="C116" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D116" t="n">
+      <c r="D116" s="3" t="n">
         <v>11.5</v>
       </c>
+      <c r="E116" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F116" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G116" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H116" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Clifford scored 18 pts vs 11.5 line (+6.5), OVER hit by 6.5 pts. Clifford played 38 min (+4.6 vs L10 avg of 33.5) — 14% more than expected. Shooting efficiency was hot: 50.0% FG (+7.1% vs L10 avg of 42.9%). 8/16 from the field. Signals that called it correctly: Volume, Context, Defense, H2H, FG Trend (6/10 aligned). Counter-signals that were wrong: HR L30, HR L10, Trend. Projection model targeted 19.5 pts — actual 18 was 1.5 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Clifford in this role.</t>
+        </is>
+      </c>
+      <c r="I116" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J116" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
+      <c r="A117" s="3" t="inlineStr">
         <is>
           <t>Jordan Miller</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
+      <c r="B117" s="3" t="inlineStr">
         <is>
           <t>LAC @ SAC</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
+      <c r="C117" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D117" t="n">
+      <c r="D117" s="3" t="n">
         <v>8.5</v>
       </c>
+      <c r="E117" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F117" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G117" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H117" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Miller scored 13 pts vs 8.5 line (+4.5), OVER hit by 4.5 pts. Minutes were as expected: 24 played vs L10 avg 24.0. Shooting efficiency was hot: 83.3% FG (+30.5% vs L10 avg of 52.8%). 5/6 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, Defense (6/10 aligned). Counter-signals that were wrong: Trend, H2H, Pace. Projection model targeted 9.5 pts — actual 13 was 3.5 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Miller's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I117" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J117" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr">
+      <c r="A118" s="3" t="inlineStr">
         <is>
           <t>Darius Garland</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
+      <c r="B118" s="3" t="inlineStr">
         <is>
           <t>LAC @ SAC</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
+      <c r="C118" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D118" t="n">
+      <c r="D118" s="3" t="n">
         <v>19.5</v>
       </c>
+      <c r="E118" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F118" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G118" s="3" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H118" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Garland scored 17 pts vs 19.5 line (-2.5), UNDER hit by 2.5 pts. Garland played 24 min (-6.2 vs L10 avg of 30.6) — 20% less than expected. Shooting was in line with averages: 50.0% FG (7/14, L10 avg 50.7%). Signals that called it correctly: Trend, Context (2/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 17.2 pts — actual 17 was 0.2 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Garland in this role.</t>
+        </is>
+      </c>
+      <c r="I118" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
+      <c r="A119" s="4" t="inlineStr">
         <is>
           <t>Bennedict Mathurin</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
+      <c r="B119" s="4" t="inlineStr">
         <is>
           <t>LAC @ SAC</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
+      <c r="C119" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D119" t="n">
+      <c r="D119" s="4" t="n">
         <v>16.5</v>
       </c>
+      <c r="E119" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F119" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G119" s="4" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="H119" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Mathurin scored 5 pts vs 16.5 line (-11.5), OVER missed by 11.5 pts. Minutes were as expected: 27 played vs L10 avg 29.1. Shooting was in line with averages: 50.0% FG (2/4, L10 avg 46.0%). Counter-signals that proved correct: Trend, Pace, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 17.4 pts — actual 5 was 12.4 pts off (correct direction). Loss classification: BLOWOUT_EFFECT. Note: Game script invalidated the prop. Consider blowout probability when LAC is involved.</t>
+        </is>
+      </c>
+      <c r="I119" s="4" t="inlineStr">
+        <is>
+          <t>BLOWOUT_EFFECT</t>
+        </is>
+      </c>
+      <c r="J119" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr">
+      <c r="A120" s="4" t="inlineStr">
         <is>
           <t>Amen Thompson</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
+      <c r="B120" s="4" t="inlineStr">
         <is>
           <t>HOU @ GSW</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
+      <c r="C120" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D120" t="n">
+      <c r="D120" s="4" t="n">
         <v>17.5</v>
       </c>
+      <c r="E120" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="F120" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G120" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H120" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Thompson scored 18 pts vs 17.5 line (+0.5), UNDER missed by 0.5 pts. Minutes were as expected: 40 played vs L10 avg 38.3. Shooting efficiency was hot: 72.7% FG (+17.6% vs L10 avg of 55.1%). 8/11 from the field. Counter-signals that proved correct: HR L30, HR L10, Trend, Defense. Signals that were wrong: Volume, Context, H2H. Projection model targeted 14.3 pts — actual 18 was 3.7 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I120" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J120" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
+      <c r="A121" s="3" t="inlineStr">
         <is>
           <t>Kristaps Porziņģis</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
+      <c r="B121" s="3" t="inlineStr">
         <is>
           <t>HOU @ GSW</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
+      <c r="C121" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D121" t="n">
+      <c r="D121" s="3" t="n">
         <v>17.5</v>
       </c>
+      <c r="E121" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F121" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G121" s="3" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="H121" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Porziņģis scored 9 pts vs 17.5 line (-8.5), UNDER hit by 8.5 pts. Minutes were as expected: 23 played vs L10 avg 24.3. Shooting efficiency was cold: 33.3% FG (-10.3% vs L10 avg of 43.6%). 3/9 from the field. Signals that called it correctly: Volume, HR L30, Context, Defense, Pace (5/10 aligned). Counter-signals that were wrong: HR L10, Trend, H2H. Projection model targeted 12.5 pts — actual 9 was 3.5 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Porziņģis's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I121" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J121" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
+      <c r="A122" s="3" t="inlineStr">
         <is>
           <t>Gary Payton II</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
+      <c r="B122" s="3" t="inlineStr">
         <is>
           <t>HOU @ GSW</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
+      <c r="C122" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D122" t="n">
+      <c r="D122" s="3" t="n">
         <v>7.5</v>
       </c>
+      <c r="E122" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F122" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G122" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H122" s="3" t="inlineStr">
+        <is>
+          <t>WIN — II scored 14 pts vs 7.5 line (+6.5), OVER hit by 6.5 pts. Minutes were as expected: 25 played vs L10 avg 23.6. Shooting efficiency was cold: 54.5% FG (-17.1% vs L10 avg of 71.6%). 6/11 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (7/10 aligned). Counter-signals that were wrong: Defense, H2H, Pace. Projection model targeted 9.4 pts — actual 14 was 4.6 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms II's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I122" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J122" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr">
+      <c r="A123" s="4" t="inlineStr">
         <is>
           <t>Stephen Curry</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr">
+      <c r="B123" s="4" t="inlineStr">
         <is>
           <t>HOU @ GSW</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr">
+      <c r="C123" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D123" t="n">
+      <c r="D123" s="4" t="n">
         <v>19.5</v>
       </c>
+      <c r="E123" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="F123" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G123" s="4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H123" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Curry scored 29 pts vs 19.5 line (+9.5), UNDER missed by 9.5 pts. Minutes were as expected: 26 played vs L10 avg 29.0. Shooting efficiency was hot: 52.4% FG (+7.2% vs L10 avg of 45.2%). 11/21 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Context. Signals that were wrong: Trend, Defense, H2H. Projection model targeted 15.6 pts — actual 29 was 13.4 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I123" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J123" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr">
+      <c r="A124" s="3" t="inlineStr">
         <is>
           <t>Tari Eason</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr">
+      <c r="B124" s="3" t="inlineStr">
         <is>
           <t>HOU @ GSW</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr">
+      <c r="C124" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D124" t="n">
+      <c r="D124" s="3" t="n">
         <v>10.5</v>
       </c>
+      <c r="E124" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F124" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G124" s="3" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="H124" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Eason scored 2 pts vs 10.5 line (-8.5), UNDER hit by 8.5 pts. Eason played 19 min (-4.6 vs L10 avg of 23.9) — 19% less than expected. Shooting efficiency was cold: 11.1% FG (-25.1% vs L10 avg of 36.2%). 1/9 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, Defense (7/10 aligned). Counter-signals that were wrong: Trend, H2H, Pace. Projection model targeted 9.8 pts — actual 2 was 7.8 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Eason's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I124" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr">
+      <c r="A125" s="4" t="inlineStr">
         <is>
           <t>Alperen Sengun</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
+      <c r="B125" s="4" t="inlineStr">
         <is>
           <t>HOU @ GSW</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr">
+      <c r="C125" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D125" t="n">
+      <c r="D125" s="4" t="n">
         <v>18.5</v>
       </c>
+      <c r="E125" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="F125" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G125" s="4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H125" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Sengun scored 24 pts vs 18.5 line (+5.5), UNDER missed by 5.5 pts. Sengun played 37 min (+3.5 vs L10 avg of 33.4) — 10% more than expected. Shooting efficiency was cold: 52.6% FG (-12.6% vs L10 avg of 65.2%). 10/19 from the field. Counter-signals that proved correct: Volume, HR L10, Trend, Context. Signals that were wrong: HR L30, H2H. Projection model targeted 16.0 pts — actual 24 was 8.0 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I125" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J125" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr">
+      <c r="A126" s="3" t="inlineStr">
         <is>
           <t>Brandin Podziemski</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
+      <c r="B126" s="3" t="inlineStr">
         <is>
           <t>HOU @ GSW</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr">
+      <c r="C126" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D126" t="n">
+      <c r="D126" s="3" t="n">
         <v>12.5</v>
       </c>
+      <c r="E126" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F126" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G126" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H126" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Podziemski scored 18 pts vs 12.5 line (+5.5), OVER hit by 5.5 pts. Podziemski played 37 min (+6.5 vs L10 avg of 30.3) — 21% more than expected. Shooting efficiency was hot: 63.6% FG (+20.2% vs L10 avg of 43.4%). 7/11 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (7/10 aligned). Counter-signals that were wrong: Defense, Pace, Min Trend. Projection model targeted 18.5 pts — actual 18 was 0.5 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Podziemski in this role.</t>
+        </is>
+      </c>
+      <c r="I126" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J126" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
+      <c r="A127" s="4" t="inlineStr">
         <is>
           <t>Reed Sheppard</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
+      <c r="B127" s="4" t="inlineStr">
         <is>
           <t>HOU @ GSW</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr">
+      <c r="C127" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D127" t="n">
+      <c r="D127" s="4" t="n">
         <v>14.5</v>
       </c>
+      <c r="E127" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F127" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G127" s="4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H127" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Sheppard scored 11 pts vs 14.5 line (-3.5), OVER missed by 3.5 pts. Sheppard played 26 min (-3.4 vs L10 avg of 29.5) — 12% less than expected. Shooting efficiency was hot: 50.0% FG (+5.8% vs L10 avg of 44.2%). 4/8 from the field. Counter-signals that proved correct: HR L30, HR L10, H2H. Signals that were wrong: Volume, Trend, Context. Projection model targeted 17.0 pts — actual 11 was 6.0 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I127" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J127" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
+      <c r="A128" s="4" t="inlineStr">
         <is>
           <t>Kevin Durant</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
+      <c r="B128" s="4" t="inlineStr">
         <is>
           <t>HOU @ GSW</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr">
+      <c r="C128" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D128" t="n">
+      <c r="D128" s="4" t="n">
         <v>24.5</v>
       </c>
+      <c r="E128" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="F128" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G128" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H128" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Durant scored 31 pts vs 24.5 line (+6.5), UNDER missed by 6.5 pts. Minutes were as expected: 37 played vs L10 avg 35.6. Shooting was in line with averages: 58.8% FG (10/17, L10 avg 54.9%). Counter-signals that proved correct: Volume, HR L30, HR L10, Pace. Signals that were wrong: Trend, Context, Defense. Projection model targeted 20.1 pts — actual 31 was 10.9 pts off (correct direction). Loss classification: MODEL_FAILURE. Note: Model signals were misleading for this matchup — review Durant's recent role and usage for pattern shifts.</t>
+        </is>
+      </c>
+      <c r="I128" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J128" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr">
+      <c r="A129" s="3" t="inlineStr">
         <is>
           <t>Gui Santos</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr">
+      <c r="B129" s="3" t="inlineStr">
         <is>
           <t>HOU @ GSW</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr">
+      <c r="C129" s="3" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D129" t="n">
+      <c r="D129" s="3" t="n">
         <v>11.5</v>
       </c>
+      <c r="E129" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F129" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G129" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H129" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Santos scored 15 pts vs 11.5 line (+3.5), OVER hit by 3.5 pts. Minutes were as expected: 32 played vs L10 avg 30.9. Shooting efficiency was cold: 33.3% FG (-16.0% vs L10 avg of 49.3%). 5/15 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (6/10 aligned). Counter-signals that were wrong: Defense, H2H, Pace. Projection model targeted 11.5 pts — actual 15 was 3.5 pts off (wrong direction). Result classification: MODEL_CORRECT. Note: Result confirms Santos's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I129" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J129" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr">
+      <c r="A130" s="4" t="inlineStr">
         <is>
           <t>De'Anthony Melton</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr">
+      <c r="B130" s="4" t="inlineStr">
         <is>
           <t>HOU @ GSW</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr">
+      <c r="C130" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D130" t="n">
+      <c r="D130" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E130" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F130" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G130" s="4" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H130" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Melton scored 6 pts vs 12.5 line (-6.5), OVER missed by 6.5 pts. Minutes were as expected: 23 played vs L10 avg 24.4. Shooting efficiency was hot: 50.0% FG (+18.6% vs L10 avg of 31.4%). 2/4 from the field. Counter-signals that proved correct: HR L30, HR L10, Trend, Defense. Signals that were wrong: Volume, Context, Min Trend. Projection model targeted 21.4 pts — actual 6 was 15.4 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I130" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J130" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr">
+      <c r="A131" s="4" t="inlineStr">
         <is>
           <t>Draymond Green</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
+      <c r="B131" s="4" t="inlineStr">
         <is>
           <t>HOU @ GSW</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr">
+      <c r="C131" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D131" t="n">
+      <c r="D131" s="4" t="n">
         <v>8.5</v>
       </c>
+      <c r="E131" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F131" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G131" s="4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H131" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Green scored 7 pts vs 8.5 line (-1.5), OVER missed by 1.5 pts. Green played 34 min (+4.2 vs L10 avg of 29.8) — 14% more than expected. Shooting efficiency was hot: 75.0% FG (+35.8% vs L10 avg of 39.2%). 3/4 from the field. Counter-signals that proved correct: HR L30, HR L10, Defense, Pace. Signals that were wrong: Volume, Trend, Context. Projection model targeted 9.7 pts — actual 7 was 2.7 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I131" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J131" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
+      </c>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr">
+      <c r="A132" s="4" t="inlineStr">
         <is>
           <t>Jabari Smith Jr.</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
+      <c r="B132" s="4" t="inlineStr">
         <is>
           <t>HOU @ GSW</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr">
+      <c r="C132" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D132" t="n">
+      <c r="D132" s="4" t="n">
         <v>14.5</v>
+      </c>
+      <c r="E132" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="F132" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G132" s="4" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H132" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Jr. scored 23 pts vs 14.5 line (+8.5), UNDER missed by 8.5 pts. Jr. played 32 min (-4.5 vs L10 avg of 36.1) — 12% less than expected. Shooting efficiency was hot: 75.0% FG (+34.5% vs L10 avg of 40.5%). 9/12 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Trend. Signals that were wrong: Defense, H2H, FG Trend. Projection model targeted 13.1 pts — actual 23 was 9.9 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Jr. for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I132" s="4" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J132" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:28</t>
+        </is>
       </c>
     </row>
   </sheetData>
